--- a/BTI.xlsx
+++ b/BTI.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{36A235FE-1561-4472-8AAC-31159F80EEB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2112E6C8-6B35-4F7D-9851-E5729C9A9BC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="4" xr2:uid="{398237C1-CA6F-4F70-A6D1-46181DBC5386}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{398237C1-CA6F-4F70-A6D1-46181DBC5386}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -1336,13 +1336,13 @@
     <t>03-06-25: H1 on track to slightly beat expectations -&gt; around 1-2% rev growth</t>
   </si>
   <si>
-    <t>Q425</t>
-  </si>
-  <si>
     <t>H126</t>
   </si>
   <si>
     <t>H226</t>
+  </si>
+  <si>
+    <t>Q226</t>
   </si>
 </sst>
 </file>
@@ -1361,13 +1361,19 @@
     <numFmt numFmtId="172" formatCode="#,##0;[Red]#,##0"/>
     <numFmt numFmtId="173" formatCode="#,##0.0"/>
   </numFmts>
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -1700,182 +1706,184 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="110">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="16" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="16" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="6" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="8" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="11" xfId="2" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="170" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="170" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="170" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="171" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="171" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="172" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="172" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="169" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="10" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="4" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="3" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="4" fillId="2" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="173" fontId="3" fillId="2" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="173" fontId="4" fillId="2" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="3" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="4" fillId="2" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="9" fontId="3" fillId="2" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="9" fontId="4" fillId="2" borderId="14" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="167" fontId="3" fillId="2" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="9" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="167" fontId="3" fillId="2" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="9" fontId="15" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="167" fontId="4" fillId="2" borderId="14" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="9" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="9" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="166" fontId="9" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="9" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="9" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="9" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="9" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="9" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="9" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="170" fontId="9" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="10" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="10" fillId="5" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" xfId="2" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="10" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="10" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="10" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="10" fillId="5" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="10" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="10" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="10" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="170" fontId="10" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="15" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="8" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="167" fontId="8" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="169" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="16" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="9" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="167" fontId="9" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="169" fontId="10" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="170" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="170" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" textRotation="90"/>
     </xf>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="170" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -1931,6 +1939,55 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>4305301</xdr:colOff>
+      <xdr:row>47</xdr:row>
+      <xdr:rowOff>119062</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>181216</xdr:colOff>
+      <xdr:row>56</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{28CF966A-9E16-B974-BA3C-E2FF4802E4D4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="6715126" y="7729537"/>
+          <a:ext cx="3886440" cy="1423988"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2085,20 +2142,20 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>587354</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>6329</xdr:colOff>
       <xdr:row>0</xdr:row>
-      <xdr:rowOff>73025</xdr:rowOff>
+      <xdr:rowOff>53975</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>3154</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>31729</xdr:colOff>
       <xdr:row>64</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -2113,7 +2170,7 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipH="1">
-          <a:off x="6511904" y="73025"/>
+          <a:off x="7150079" y="53975"/>
           <a:ext cx="25400" cy="10309225"/>
         </a:xfrm>
         <a:prstGeom prst="line">
@@ -2531,7 +2588,7 @@
         <v>383</v>
       </c>
       <c r="H2" s="2">
-        <v>60.8</v>
+        <v>63.6</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
@@ -2539,7 +2596,7 @@
         <v>24</v>
       </c>
       <c r="H3" s="3">
-        <v>46.15</v>
+        <v>47.45</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
@@ -2553,11 +2610,11 @@
       <c r="G4" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="H4" s="5">
-        <v>2187</v>
-      </c>
-      <c r="I4" s="101" t="s">
-        <v>388</v>
+      <c r="H4" s="3">
+        <v>2194</v>
+      </c>
+      <c r="I4" s="110" t="s">
+        <v>390</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
@@ -2573,7 +2630,7 @@
       </c>
       <c r="H5" s="5">
         <f>+H3*H4</f>
-        <v>100930.05</v>
+        <v>104105.3</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
@@ -2587,10 +2644,10 @@
         <v>3</v>
       </c>
       <c r="H6" s="5">
-        <v>3827</v>
-      </c>
-      <c r="I6" s="101" t="s">
-        <v>388</v>
+        <v>2518</v>
+      </c>
+      <c r="I6" s="110" t="s">
+        <v>390</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
@@ -2598,11 +2655,11 @@
         <v>4</v>
       </c>
       <c r="H7" s="5">
-        <f>31708+3362</f>
-        <v>35070</v>
-      </c>
-      <c r="I7" s="101" t="s">
-        <v>388</v>
+        <f>4018+31045</f>
+        <v>35063</v>
+      </c>
+      <c r="I7" s="110" t="s">
+        <v>390</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
@@ -2617,7 +2674,7 @@
       </c>
       <c r="H8" s="5">
         <f>H5-H6+H7</f>
-        <v>132173.04999999999</v>
+        <v>136650.29999999999</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
@@ -3095,6 +3152,7 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId3"/>
+  <drawing r:id="rId4"/>
 </worksheet>
 </file>
 
@@ -3344,11 +3402,11 @@
       <c r="H2" s="6" t="s">
         <v>363</v>
       </c>
-      <c r="I2" s="109" t="s">
+      <c r="I2" s="102" t="s">
+        <v>388</v>
+      </c>
+      <c r="J2" s="102" t="s">
         <v>389</v>
-      </c>
-      <c r="J2" s="109" t="s">
-        <v>390</v>
       </c>
       <c r="L2" s="6" t="s">
         <v>339</v>
@@ -3685,10 +3743,12 @@
       </c>
       <c r="F6" s="37"/>
       <c r="G6" s="37">
-        <v>30.5</v>
+        <v>34.1</v>
       </c>
       <c r="H6" s="37"/>
-      <c r="I6" s="5"/>
+      <c r="I6" s="5">
+        <v>35</v>
+      </c>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
       <c r="L6" s="5"/>
@@ -3721,40 +3781,40 @@
         <v>35</v>
       </c>
       <c r="X6" s="5">
-        <f t="shared" ref="X6:AF6" si="4">X5*9%</f>
-        <v>26.235610361100004</v>
+        <f>+W6*(1+9%)</f>
+        <v>38.150000000000006</v>
       </c>
       <c r="Y6" s="5">
-        <f t="shared" si="4"/>
-        <v>27.022678671933004</v>
+        <f t="shared" ref="Y6:AF6" si="4">+X6*(1+9%)</f>
+        <v>41.583500000000008</v>
       </c>
       <c r="Z6" s="5">
         <f t="shared" si="4"/>
-        <v>27.833359032090996</v>
+        <v>45.326015000000012</v>
       </c>
       <c r="AA6" s="5">
         <f t="shared" si="4"/>
-        <v>28.668359803053729</v>
+        <v>49.405356350000019</v>
       </c>
       <c r="AB6" s="5">
         <f t="shared" si="4"/>
-        <v>29.528410597145342</v>
+        <v>53.851838421500027</v>
       </c>
       <c r="AC6" s="5">
         <f t="shared" si="4"/>
-        <v>30.414262915059702</v>
+        <v>58.69850387943503</v>
       </c>
       <c r="AD6" s="5">
         <f t="shared" si="4"/>
-        <v>31.326690802511493</v>
+        <v>63.981369228584185</v>
       </c>
       <c r="AE6" s="5">
         <f t="shared" si="4"/>
-        <v>32.266491526586833</v>
+        <v>69.739692459156771</v>
       </c>
       <c r="AF6" s="5">
         <f t="shared" si="4"/>
-        <v>33.234486272384437</v>
+        <v>76.016264780480881</v>
       </c>
       <c r="AG6" s="5"/>
       <c r="AH6" s="5"/>
@@ -3975,7 +4035,9 @@
         <f t="shared" ref="H10:H15" si="7">+W10-G10</f>
         <v>0.28500000000000003</v>
       </c>
-      <c r="I10" s="3"/>
+      <c r="I10" s="3">
+        <v>0.26300000000000001</v>
+      </c>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
       <c r="L10" s="3"/>
@@ -4053,7 +4115,9 @@
         <f t="shared" si="7"/>
         <v>9.9</v>
       </c>
-      <c r="I11" s="3"/>
+      <c r="I11" s="3">
+        <v>8.9</v>
+      </c>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
       <c r="L11" s="3"/>
@@ -4131,7 +4195,9 @@
         <f t="shared" si="7"/>
         <v>7.1999999999999993</v>
       </c>
-      <c r="I12" s="3"/>
+      <c r="I12" s="3">
+        <v>7.9</v>
+      </c>
       <c r="J12" s="3"/>
       <c r="K12" s="3"/>
       <c r="L12" s="3"/>
@@ -4209,7 +4275,9 @@
         <f t="shared" si="7"/>
         <v>2.6</v>
       </c>
-      <c r="I13" s="3"/>
+      <c r="I13" s="3">
+        <v>2.5</v>
+      </c>
       <c r="J13" s="3"/>
       <c r="K13" s="3"/>
       <c r="L13" s="3"/>
@@ -4287,7 +4355,9 @@
         <f t="shared" si="7"/>
         <v>242.9</v>
       </c>
-      <c r="I14" s="3"/>
+      <c r="I14" s="3">
+        <v>223</v>
+      </c>
       <c r="J14" s="3"/>
       <c r="K14" s="3"/>
       <c r="L14" s="3"/>
@@ -4349,7 +4419,7 @@
         <v>315.96699999999998</v>
       </c>
       <c r="D15" s="40">
-        <f t="shared" ref="D15:G15" si="8">SUM(D10:D14)</f>
+        <f t="shared" ref="D15:I15" si="8">SUM(D10:D14)</f>
         <v>290.34700000000004</v>
       </c>
       <c r="E15" s="40">
@@ -4368,7 +4438,10 @@
         <f t="shared" si="7"/>
         <v>262.88500000000005</v>
       </c>
-      <c r="I15" s="3"/>
+      <c r="I15" s="40">
+        <f t="shared" si="8"/>
+        <v>242.56299999999999</v>
+      </c>
       <c r="J15" s="3"/>
       <c r="K15" s="3"/>
       <c r="L15" s="40">
@@ -4644,7 +4717,7 @@
         <v>5378</v>
       </c>
       <c r="F19" s="37">
-        <f>+V19-E19</f>
+        <f t="shared" ref="F19:F32" si="26">+V19-E19</f>
         <v>5900</v>
       </c>
       <c r="G19" s="5">
@@ -4654,7 +4727,9 @@
         <f>+W19-G19</f>
         <v>6102</v>
       </c>
-      <c r="I19" s="5"/>
+      <c r="I19" s="5">
+        <v>5687</v>
+      </c>
       <c r="J19" s="5"/>
       <c r="K19" s="5"/>
       <c r="L19" s="5">
@@ -4725,17 +4800,19 @@
         <v>4376</v>
       </c>
       <c r="F20" s="37">
-        <f>+V20-E20</f>
+        <f t="shared" si="26"/>
         <v>4865</v>
       </c>
       <c r="G20" s="5">
         <v>4281</v>
       </c>
       <c r="H20" s="5">
-        <f t="shared" ref="H20:H44" si="26">+W20-G20</f>
+        <f t="shared" ref="H20:H44" si="27">+W20-G20</f>
         <v>5028</v>
       </c>
-      <c r="I20" s="5"/>
+      <c r="I20" s="5">
+        <v>4402</v>
+      </c>
       <c r="J20" s="5"/>
       <c r="K20" s="5"/>
       <c r="L20" s="5">
@@ -4815,17 +4892,19 @@
         <v>2586</v>
       </c>
       <c r="F21" s="37">
-        <f>+V21-E21</f>
+        <f t="shared" si="26"/>
         <v>2762</v>
       </c>
       <c r="G21" s="5">
         <v>2356</v>
       </c>
       <c r="H21" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>2411</v>
       </c>
-      <c r="I21" s="5"/>
+      <c r="I21" s="5">
+        <v>2146</v>
+      </c>
       <c r="J21" s="5"/>
       <c r="K21" s="5"/>
       <c r="L21" s="5">
@@ -4901,17 +4980,19 @@
         <v>869</v>
       </c>
       <c r="F22" s="37">
-        <f>+V22-E22</f>
+        <f t="shared" si="26"/>
         <v>852</v>
       </c>
       <c r="G22" s="5">
         <v>737</v>
       </c>
       <c r="H22" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>805</v>
       </c>
-      <c r="I22" s="5"/>
+      <c r="I22" s="5">
+        <v>763</v>
+      </c>
       <c r="J22" s="5"/>
       <c r="K22" s="5"/>
       <c r="L22" s="5"/>
@@ -4979,17 +5060,19 @@
         <v>441</v>
       </c>
       <c r="F23" s="37">
-        <f>+V23-E23</f>
+        <f t="shared" si="26"/>
         <v>480</v>
       </c>
       <c r="G23" s="5">
         <v>444</v>
       </c>
       <c r="H23" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>470</v>
       </c>
-      <c r="I23" s="5"/>
+      <c r="I23" s="5">
+        <v>381</v>
+      </c>
       <c r="J23" s="5"/>
       <c r="K23" s="5"/>
       <c r="L23" s="5"/>
@@ -5057,17 +5140,19 @@
         <v>341</v>
       </c>
       <c r="F24" s="37">
-        <f>+V24-E24</f>
+        <f t="shared" si="26"/>
         <v>449</v>
       </c>
       <c r="G24" s="5">
         <v>470</v>
       </c>
       <c r="H24" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>695</v>
       </c>
-      <c r="I24" s="5"/>
+      <c r="I24" s="5">
+        <v>784</v>
+      </c>
       <c r="J24" s="5"/>
       <c r="K24" s="5"/>
       <c r="L24" s="5"/>
@@ -5135,17 +5220,19 @@
         <v>555</v>
       </c>
       <c r="F25" s="37">
-        <f>+V25-E25</f>
+        <f t="shared" si="26"/>
         <v>537</v>
       </c>
       <c r="G25" s="5">
         <v>542</v>
       </c>
       <c r="H25" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>501</v>
       </c>
-      <c r="I25" s="5"/>
+      <c r="I25" s="5">
+        <v>494</v>
+      </c>
       <c r="J25" s="5"/>
       <c r="K25" s="5"/>
       <c r="L25" s="5"/>
@@ -5207,25 +5294,27 @@
         <v>2227</v>
       </c>
       <c r="D26" s="5">
-        <f t="shared" ref="D26:E26" si="27">SUM(D22:D25)</f>
+        <f t="shared" ref="D26:E26" si="28">SUM(D22:D25)</f>
         <v>2283</v>
       </c>
       <c r="E26" s="5">
-        <f t="shared" si="27"/>
+        <f t="shared" si="28"/>
         <v>2206</v>
       </c>
       <c r="F26" s="37">
-        <f>+V26-E26</f>
+        <f t="shared" si="26"/>
         <v>2318</v>
       </c>
       <c r="G26" s="5">
         <v>2193</v>
       </c>
       <c r="H26" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>2471</v>
       </c>
-      <c r="I26" s="5"/>
+      <c r="I26" s="5">
+        <v>2422</v>
+      </c>
       <c r="J26" s="5"/>
       <c r="K26" s="5"/>
       <c r="L26" s="5"/>
@@ -5233,31 +5322,31 @@
       <c r="N26" s="5"/>
       <c r="O26" s="5"/>
       <c r="P26" s="5">
-        <f t="shared" ref="P26:V26" si="28">SUM(P22:P25)</f>
+        <f t="shared" ref="P26:V26" si="29">SUM(P22:P25)</f>
         <v>1800</v>
       </c>
       <c r="Q26" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>2336</v>
       </c>
       <c r="R26" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>2603</v>
       </c>
       <c r="S26" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>3172</v>
       </c>
       <c r="T26" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>4103</v>
       </c>
       <c r="U26" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>4510</v>
       </c>
       <c r="V26" s="5">
-        <f t="shared" si="28"/>
+        <f t="shared" si="29"/>
         <v>4524</v>
       </c>
       <c r="W26" s="5">
@@ -5265,40 +5354,40 @@
         <v>4664</v>
       </c>
       <c r="X26" s="5">
-        <f t="shared" ref="X26:AE26" si="29">X7*X6</f>
-        <v>3548.523715000942</v>
+        <f t="shared" ref="X26:AE26" si="30">X7*X6</f>
+        <v>5160.0164000000004</v>
       </c>
       <c r="Y26" s="5">
-        <f t="shared" si="29"/>
-        <v>3709.8041178477342</v>
+        <f t="shared" si="30"/>
+        <v>5708.7841441399996</v>
       </c>
       <c r="Z26" s="5">
-        <f t="shared" si="29"/>
-        <v>3878.4147150039139</v>
+        <f t="shared" si="30"/>
+        <v>6315.9133378692886</v>
       </c>
       <c r="AA26" s="5">
-        <f t="shared" si="29"/>
-        <v>4054.6886638008414</v>
+        <f t="shared" si="30"/>
+        <v>6987.610721351688</v>
       </c>
       <c r="AB26" s="5">
-        <f t="shared" si="29"/>
-        <v>4238.9742635705898</v>
+        <f t="shared" si="30"/>
+        <v>7730.7431215674396</v>
       </c>
       <c r="AC26" s="5">
-        <f t="shared" si="29"/>
-        <v>4431.6356438498724</v>
+        <f t="shared" si="30"/>
+        <v>8552.9076525461369</v>
       </c>
       <c r="AD26" s="5">
-        <f t="shared" si="29"/>
-        <v>6265.3381605022987</v>
+        <f t="shared" si="30"/>
+        <v>12796.273845716838</v>
       </c>
       <c r="AE26" s="5">
-        <f t="shared" si="29"/>
-        <v>6453.2983053173666</v>
+        <f t="shared" si="30"/>
+        <v>13947.938491831354</v>
       </c>
       <c r="AF26" s="5">
-        <f t="shared" ref="AF26" si="30">AF7*AF6</f>
-        <v>6646.8972544768876</v>
+        <f t="shared" ref="AF26" si="31">AF7*AF6</f>
+        <v>15203.252956096176</v>
       </c>
       <c r="AG26" s="5"/>
       <c r="AH26" s="5"/>
@@ -5321,24 +5410,26 @@
         <v>10967</v>
       </c>
       <c r="D27" s="5">
-        <f>U27-C27</f>
+        <f t="shared" ref="D27:D32" si="32">U27-C27</f>
         <v>11141</v>
       </c>
       <c r="E27" s="5">
         <v>9856</v>
       </c>
       <c r="F27" s="37">
-        <f>+V27-E27</f>
+        <f t="shared" si="26"/>
         <v>10829</v>
       </c>
       <c r="G27" s="5">
         <v>9515</v>
       </c>
       <c r="H27" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>10686</v>
       </c>
-      <c r="I27" s="5"/>
+      <c r="I27" s="5">
+        <v>9561</v>
+      </c>
       <c r="J27" s="5"/>
       <c r="K27" s="5"/>
       <c r="L27" s="5"/>
@@ -5370,27 +5461,27 @@
         <v>20201</v>
       </c>
       <c r="X27" s="5">
-        <f t="shared" ref="X27:AC27" si="31">W27*(1-1%)</f>
+        <f t="shared" ref="X27:AC27" si="33">W27*(1-1%)</f>
         <v>19998.990000000002</v>
       </c>
       <c r="Y27" s="5">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>19799.000100000001</v>
       </c>
       <c r="Z27" s="5">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>19601.010098999999</v>
       </c>
       <c r="AA27" s="5">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>19404.99999801</v>
       </c>
       <c r="AB27" s="5">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>19210.949998029901</v>
       </c>
       <c r="AC27" s="5">
-        <f t="shared" si="31"/>
+        <f t="shared" si="33"/>
         <v>19018.840498049602</v>
       </c>
       <c r="AD27" s="5">
@@ -5426,24 +5517,26 @@
         <v>247</v>
       </c>
       <c r="D28" s="5">
-        <f>U28-C28</f>
+        <f t="shared" si="32"/>
         <v>418</v>
       </c>
       <c r="E28" s="5">
         <v>278</v>
       </c>
       <c r="F28" s="37">
-        <f>+V28-E28</f>
+        <f t="shared" si="26"/>
         <v>380</v>
       </c>
       <c r="G28" s="5">
         <v>361</v>
       </c>
       <c r="H28" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>395</v>
       </c>
-      <c r="I28" s="5"/>
+      <c r="I28" s="5">
+        <v>252</v>
+      </c>
       <c r="J28" s="5"/>
       <c r="K28" s="5"/>
       <c r="L28" s="5"/>
@@ -5475,39 +5568,39 @@
         <v>756</v>
       </c>
       <c r="X28" s="5">
-        <f t="shared" ref="X28:AF28" si="32">W28*(1+1%)</f>
+        <f t="shared" ref="X28:AF28" si="34">W28*(1+1%)</f>
         <v>763.56000000000006</v>
       </c>
       <c r="Y28" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>771.19560000000001</v>
       </c>
       <c r="Z28" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>778.907556</v>
       </c>
       <c r="AA28" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>786.69663156000001</v>
       </c>
       <c r="AB28" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>794.56359787560007</v>
       </c>
       <c r="AC28" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>802.50923385435613</v>
       </c>
       <c r="AD28" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>810.5343261928997</v>
       </c>
       <c r="AE28" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>818.63966945482866</v>
       </c>
       <c r="AF28" s="5">
-        <f t="shared" si="32"/>
+        <f t="shared" si="34"/>
         <v>826.82606614937697</v>
       </c>
       <c r="AG28" s="5"/>
@@ -5531,24 +5624,26 @@
         <v>13441</v>
       </c>
       <c r="D29" s="41">
-        <f>U29-C29</f>
+        <f t="shared" si="32"/>
         <v>13842</v>
       </c>
       <c r="E29" s="41">
         <v>12340</v>
       </c>
       <c r="F29" s="42">
-        <f>+V29-E29</f>
+        <f t="shared" si="26"/>
         <v>13527</v>
       </c>
       <c r="G29" s="41">
         <v>12069</v>
       </c>
       <c r="H29" s="41">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>13541</v>
       </c>
-      <c r="I29" s="41"/>
+      <c r="I29" s="41">
+        <v>12235</v>
+      </c>
       <c r="J29" s="41"/>
       <c r="K29" s="41"/>
       <c r="L29" s="41">
@@ -5589,40 +5684,40 @@
         <v>25610</v>
       </c>
       <c r="X29" s="41">
-        <f t="shared" ref="X29:AE29" si="33">SUM(X22:X28)</f>
-        <v>24311.073715000945</v>
+        <f t="shared" ref="X29:AE29" si="35">SUM(X22:X28)</f>
+        <v>25922.566400000003</v>
       </c>
       <c r="Y29" s="41">
-        <f t="shared" si="33"/>
-        <v>24279.999817847733</v>
+        <f t="shared" si="35"/>
+        <v>26278.979844139998</v>
       </c>
       <c r="Z29" s="41">
-        <f t="shared" si="33"/>
-        <v>24258.332370003911</v>
+        <f t="shared" si="35"/>
+        <v>26695.830992869287</v>
       </c>
       <c r="AA29" s="41">
-        <f t="shared" si="33"/>
-        <v>24246.38529337084</v>
+        <f t="shared" si="35"/>
+        <v>27179.307350921688</v>
       </c>
       <c r="AB29" s="41">
-        <f t="shared" si="33"/>
-        <v>24244.487859476092</v>
+        <f t="shared" si="35"/>
+        <v>27736.256717472941</v>
       </c>
       <c r="AC29" s="41">
-        <f t="shared" si="33"/>
-        <v>24252.985375753829</v>
+        <f t="shared" si="35"/>
+        <v>28374.257384450095</v>
       </c>
       <c r="AD29" s="41">
-        <f t="shared" si="33"/>
-        <v>25714.33617478381</v>
+        <f t="shared" si="35"/>
+        <v>32245.271859998349</v>
       </c>
       <c r="AE29" s="41">
-        <f t="shared" si="33"/>
-        <v>25537.632389099032</v>
+        <f t="shared" si="35"/>
+        <v>33032.272575613024</v>
       </c>
       <c r="AF29" s="41">
-        <f t="shared" ref="AF29" si="34">SUM(AF22:AF28)</f>
-        <v>25374.103846666563</v>
+        <f t="shared" ref="AF29" si="36">SUM(AF22:AF28)</f>
+        <v>33930.459548285849</v>
       </c>
       <c r="AG29" s="5"/>
       <c r="AH29" s="5"/>
@@ -5645,24 +5740,26 @@
         <v>2251</v>
       </c>
       <c r="D30" s="5">
-        <f>U30-C30</f>
+        <f t="shared" si="32"/>
         <v>2294</v>
       </c>
       <c r="E30" s="5">
         <v>2304</v>
       </c>
       <c r="F30" s="37">
-        <f>+V30-E30</f>
+        <f t="shared" si="26"/>
         <v>2261</v>
       </c>
       <c r="G30" s="5">
         <v>2166</v>
       </c>
       <c r="H30" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>2299</v>
       </c>
-      <c r="I30" s="5"/>
+      <c r="I30" s="5">
+        <v>2112</v>
+      </c>
       <c r="J30" s="5"/>
       <c r="K30" s="5"/>
       <c r="L30" s="5">
@@ -5702,39 +5799,39 @@
         <v>4465</v>
       </c>
       <c r="X30" s="5">
-        <f t="shared" ref="X30:AF30" si="35">W30*(1-0.1%)</f>
+        <f t="shared" ref="X30:AF30" si="37">W30*(1-0.1%)</f>
         <v>4460.5349999999999</v>
       </c>
       <c r="Y30" s="5">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>4456.0744649999997</v>
       </c>
       <c r="Z30" s="5">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>4451.6183905349999</v>
       </c>
       <c r="AA30" s="5">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>4447.1667721444646</v>
       </c>
       <c r="AB30" s="5">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>4442.7196053723201</v>
       </c>
       <c r="AC30" s="5">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>4438.276885766948</v>
       </c>
       <c r="AD30" s="5">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>4433.8386088811812</v>
       </c>
       <c r="AE30" s="5">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>4429.4047702723001</v>
       </c>
       <c r="AF30" s="5">
-        <f t="shared" si="35"/>
+        <f t="shared" si="37"/>
         <v>4424.9753655020277</v>
       </c>
       <c r="AG30" s="5"/>
@@ -5758,24 +5855,26 @@
         <v>7</v>
       </c>
       <c r="D31" s="5">
-        <f>U31-C31</f>
+        <f t="shared" si="32"/>
         <v>-103</v>
       </c>
       <c r="E31" s="5">
         <v>140</v>
       </c>
       <c r="F31" s="37">
-        <f>+V31-E31</f>
+        <f t="shared" si="26"/>
         <v>-11</v>
       </c>
       <c r="G31" s="5">
         <v>185</v>
       </c>
       <c r="H31" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>54</v>
       </c>
-      <c r="I31" s="5"/>
+      <c r="I31" s="5">
+        <v>119</v>
+      </c>
       <c r="J31" s="5"/>
       <c r="K31" s="5"/>
       <c r="L31" s="5">
@@ -5815,39 +5914,39 @@
         <v>239</v>
       </c>
       <c r="X31" s="5">
-        <f t="shared" ref="X31:AF34" si="36">W31*(1-0.1%)</f>
+        <f t="shared" ref="X31:AF34" si="38">W31*(1-0.1%)</f>
         <v>238.761</v>
       </c>
       <c r="Y31" s="5">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>238.52223899999998</v>
       </c>
       <c r="Z31" s="5">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>238.28371676099999</v>
       </c>
       <c r="AA31" s="5">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>238.04543304423899</v>
       </c>
       <c r="AB31" s="5">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>237.80738761119474</v>
       </c>
       <c r="AC31" s="5">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>237.56958022358356</v>
       </c>
       <c r="AD31" s="5">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>237.33201064335998</v>
       </c>
       <c r="AE31" s="5">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>237.09467863271661</v>
       </c>
       <c r="AF31" s="5">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>236.85758395408388</v>
       </c>
       <c r="AG31" s="5"/>
@@ -5871,24 +5970,26 @@
         <v>1389</v>
       </c>
       <c r="D32" s="5">
-        <f>U32-C32</f>
+        <f t="shared" si="32"/>
         <v>1275</v>
       </c>
       <c r="E32" s="5">
         <v>1375</v>
       </c>
       <c r="F32" s="37">
-        <f>+V32-E32</f>
+        <f t="shared" si="26"/>
         <v>1456</v>
       </c>
       <c r="G32" s="5">
         <v>1463</v>
       </c>
       <c r="H32" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>1662</v>
       </c>
-      <c r="I32" s="5"/>
+      <c r="I32" s="5">
+        <v>1651</v>
+      </c>
       <c r="J32" s="5"/>
       <c r="K32" s="5"/>
       <c r="L32" s="5">
@@ -5928,39 +6029,39 @@
         <v>3125</v>
       </c>
       <c r="X32" s="5">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>3121.875</v>
       </c>
       <c r="Y32" s="5">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>3118.7531250000002</v>
       </c>
       <c r="Z32" s="5">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>3115.6343718750004</v>
       </c>
       <c r="AA32" s="5">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>3112.5187375031255</v>
       </c>
       <c r="AB32" s="5">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>3109.4062187656223</v>
       </c>
       <c r="AC32" s="5">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>3106.2968125468565</v>
       </c>
       <c r="AD32" s="5">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>3103.1905157343094</v>
       </c>
       <c r="AE32" s="5">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>3100.0873252185752</v>
       </c>
       <c r="AF32" s="5">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>3096.9872378933565</v>
       </c>
       <c r="AG32" s="5"/>
@@ -5982,11 +6083,11 @@
         <v>31</v>
       </c>
       <c r="C33" s="5">
-        <f t="shared" ref="C33:D33" si="37">C29-C30+C31-C32</f>
+        <f t="shared" ref="C33:D33" si="39">C29-C30+C31-C32</f>
         <v>9808</v>
       </c>
       <c r="D33" s="5">
-        <f t="shared" si="37"/>
+        <f t="shared" si="39"/>
         <v>10170</v>
       </c>
       <c r="E33" s="5">
@@ -6005,92 +6106,95 @@
         <f>H29-H30+H31-H32</f>
         <v>9634</v>
       </c>
-      <c r="I33" s="5"/>
+      <c r="I33" s="5">
+        <f>I29-I30+I31-I32</f>
+        <v>8591</v>
+      </c>
       <c r="J33" s="5"/>
       <c r="K33" s="5"/>
       <c r="L33" s="5">
-        <f t="shared" ref="L33:AE33" si="38">L29-L30+L31-L32</f>
+        <f t="shared" ref="L33:AE33" si="40">L29-L30+L31-L32</f>
         <v>8747</v>
       </c>
       <c r="M33" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>8032</v>
       </c>
       <c r="N33" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>8744</v>
       </c>
       <c r="O33" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>12580</v>
       </c>
       <c r="P33" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>16937</v>
       </c>
       <c r="Q33" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>18219</v>
       </c>
       <c r="R33" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>18894</v>
       </c>
       <c r="S33" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>18585</v>
       </c>
       <c r="T33" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>20129</v>
       </c>
       <c r="U33" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>19978</v>
       </c>
       <c r="V33" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>18600</v>
       </c>
       <c r="W33" s="5">
-        <f t="shared" si="38"/>
+        <f t="shared" si="40"/>
         <v>18259</v>
       </c>
       <c r="X33" s="5">
-        <f t="shared" si="38"/>
-        <v>16967.424715000943</v>
+        <f t="shared" si="40"/>
+        <v>18578.917400000002</v>
       </c>
       <c r="Y33" s="5">
-        <f t="shared" si="38"/>
-        <v>16943.694466847737</v>
+        <f t="shared" si="40"/>
+        <v>18942.674493140003</v>
       </c>
       <c r="Z33" s="5">
-        <f t="shared" si="38"/>
-        <v>16929.363324354912</v>
+        <f t="shared" si="40"/>
+        <v>19366.861947220288</v>
       </c>
       <c r="AA33" s="5">
-        <f t="shared" si="38"/>
-        <v>16924.745216767493</v>
+        <f t="shared" si="40"/>
+        <v>19857.667274318337</v>
       </c>
       <c r="AB33" s="5">
-        <f t="shared" si="38"/>
-        <v>16930.169422949344</v>
+        <f t="shared" si="40"/>
+        <v>20421.938280946193</v>
       </c>
       <c r="AC33" s="5">
-        <f t="shared" si="38"/>
-        <v>16945.981257663607</v>
+        <f t="shared" si="40"/>
+        <v>21067.253266359872</v>
       </c>
       <c r="AD33" s="5">
-        <f t="shared" si="38"/>
-        <v>18414.639060811678</v>
+        <f t="shared" si="40"/>
+        <v>24945.574746026217</v>
       </c>
       <c r="AE33" s="5">
-        <f t="shared" si="38"/>
-        <v>18245.234972240873</v>
+        <f t="shared" si="40"/>
+        <v>25739.875158754865</v>
       </c>
       <c r="AF33" s="5">
-        <f t="shared" ref="AF33" si="39">AF29-AF30+AF31-AF32</f>
-        <v>18088.998827225259</v>
+        <f t="shared" ref="AF33" si="41">AF29-AF30+AF31-AF32</f>
+        <v>26645.354528844546</v>
       </c>
       <c r="AG33" s="5"/>
       <c r="AH33" s="5"/>
@@ -6127,10 +6231,12 @@
         <v>1192</v>
       </c>
       <c r="H34" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>1355</v>
       </c>
-      <c r="I34" s="5"/>
+      <c r="I34" s="5">
+        <v>1364</v>
+      </c>
       <c r="J34" s="5"/>
       <c r="K34" s="5"/>
       <c r="L34" s="5">
@@ -6170,39 +6276,39 @@
         <v>2547</v>
       </c>
       <c r="X34" s="5">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>2544.453</v>
       </c>
       <c r="Y34" s="5">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>2541.908547</v>
       </c>
       <c r="Z34" s="5">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>2539.3666384530002</v>
       </c>
       <c r="AA34" s="5">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>2536.8272718145472</v>
       </c>
       <c r="AB34" s="5">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>2534.2904445427325</v>
       </c>
       <c r="AC34" s="5">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>2531.7561540981897</v>
       </c>
       <c r="AD34" s="5">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>2529.2243979440914</v>
       </c>
       <c r="AE34" s="5">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>2526.6951735461471</v>
       </c>
       <c r="AF34" s="5">
-        <f t="shared" si="36"/>
+        <f t="shared" si="38"/>
         <v>2524.1684783726009</v>
       </c>
       <c r="AG34" s="5"/>
@@ -6240,10 +6346,12 @@
         <v>54</v>
       </c>
       <c r="H35" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>138</v>
       </c>
-      <c r="I35" s="5"/>
+      <c r="I35" s="5">
+        <v>92</v>
+      </c>
       <c r="J35" s="5"/>
       <c r="K35" s="5"/>
       <c r="L35" s="5">
@@ -6283,39 +6391,39 @@
         <v>192</v>
       </c>
       <c r="X35" s="5">
-        <f t="shared" ref="X35:AF35" si="40">W35*(1-0.1%)</f>
+        <f t="shared" ref="X35:AF35" si="42">W35*(1-0.1%)</f>
         <v>191.80799999999999</v>
       </c>
       <c r="Y35" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>191.61619199999998</v>
       </c>
       <c r="Z35" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>191.42457580799999</v>
       </c>
       <c r="AA35" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>191.23315123219197</v>
       </c>
       <c r="AB35" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>191.04191808095979</v>
       </c>
       <c r="AC35" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>190.85087616287882</v>
       </c>
       <c r="AD35" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>190.66002528671595</v>
       </c>
       <c r="AE35" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>190.46936526142923</v>
       </c>
       <c r="AF35" s="5">
-        <f t="shared" si="40"/>
+        <f t="shared" si="42"/>
         <v>190.2788958961678</v>
       </c>
       <c r="AG35" s="5"/>
@@ -6353,10 +6461,12 @@
         <v>5</v>
       </c>
       <c r="H36" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>7</v>
       </c>
-      <c r="I36" s="5"/>
+      <c r="I36" s="5">
+        <v>5</v>
+      </c>
       <c r="J36" s="5"/>
       <c r="K36" s="5"/>
       <c r="L36" s="5">
@@ -6396,39 +6506,39 @@
         <v>12</v>
       </c>
       <c r="X36" s="5">
-        <f t="shared" ref="X36:AF36" si="41">W36*(1-0.1%)</f>
+        <f t="shared" ref="X36:AF36" si="43">W36*(1-0.1%)</f>
         <v>11.988</v>
       </c>
       <c r="Y36" s="5">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>11.976011999999999</v>
       </c>
       <c r="Z36" s="5">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>11.964035987999999</v>
       </c>
       <c r="AA36" s="5">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>11.952071952011998</v>
       </c>
       <c r="AB36" s="5">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>11.940119880059987</v>
       </c>
       <c r="AC36" s="5">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>11.928179760179926</v>
       </c>
       <c r="AD36" s="5">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>11.916251580419747</v>
       </c>
       <c r="AE36" s="5">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>11.904335328839327</v>
       </c>
       <c r="AF36" s="5">
-        <f t="shared" si="41"/>
+        <f t="shared" si="43"/>
         <v>11.892430993510487</v>
       </c>
       <c r="AG36" s="5"/>
@@ -6466,10 +6576,12 @@
         <v>2413</v>
       </c>
       <c r="H37" s="5">
-        <f t="shared" si="26"/>
+        <f>+W37-G37</f>
         <v>3482</v>
       </c>
-      <c r="I37" s="5"/>
+      <c r="I37" s="5">
+        <v>3048</v>
+      </c>
       <c r="J37" s="5"/>
       <c r="K37" s="5"/>
       <c r="L37" s="5">
@@ -6509,39 +6621,39 @@
         <v>5895</v>
       </c>
       <c r="X37" s="5">
-        <f t="shared" ref="X37:AF37" si="42">W37*(1-0.1%)</f>
+        <f t="shared" ref="X37:AF37" si="44">W37*(1-0.1%)</f>
         <v>5889.1049999999996</v>
       </c>
       <c r="Y37" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>5883.2158949999994</v>
       </c>
       <c r="Z37" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>5877.3326791049994</v>
       </c>
       <c r="AA37" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>5871.4553464258943</v>
       </c>
       <c r="AB37" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>5865.5838910794682</v>
       </c>
       <c r="AC37" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>5859.7183071883892</v>
       </c>
       <c r="AD37" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>5853.8585888812004</v>
       </c>
       <c r="AE37" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>5848.0047302923194</v>
       </c>
       <c r="AF37" s="5">
-        <f t="shared" si="42"/>
+        <f t="shared" si="44"/>
         <v>5842.1567255620275</v>
       </c>
       <c r="AG37" s="5"/>
@@ -6562,11 +6674,11 @@
         <v>35</v>
       </c>
       <c r="C38" s="5">
-        <f t="shared" ref="C38:D38" si="43">C33-C34+C35-C36-C37</f>
+        <f t="shared" ref="C38:D38" si="45">C33-C34+C35-C36-C37</f>
         <v>5935</v>
       </c>
       <c r="D38" s="5">
-        <f t="shared" si="43"/>
+        <f t="shared" si="45"/>
         <v>-21686</v>
       </c>
       <c r="E38" s="5">
@@ -6585,47 +6697,50 @@
         <f>H33-H34+H35-H36-H37</f>
         <v>4928</v>
       </c>
-      <c r="I38" s="5"/>
+      <c r="I38" s="5">
+        <f>I33-I34+I35-I36-I37</f>
+        <v>4266</v>
+      </c>
       <c r="J38" s="5"/>
       <c r="K38" s="5"/>
       <c r="L38" s="5">
-        <f t="shared" ref="L38:O38" si="44">L33-L34+L35-L36-L37</f>
+        <f t="shared" ref="L38:O38" si="46">L33-L34+L35-L36-L37</f>
         <v>4546</v>
       </c>
       <c r="M38" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>4557</v>
       </c>
       <c r="N38" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>4655</v>
       </c>
       <c r="O38" s="5">
-        <f t="shared" si="44"/>
+        <f t="shared" si="46"/>
         <v>6476</v>
       </c>
       <c r="P38" s="5">
-        <f t="shared" ref="P38:U38" si="45">P33-P34+P35-P36-P37</f>
+        <f t="shared" ref="P38:U38" si="47">P33-P34+P35-P36-P37</f>
         <v>9313</v>
       </c>
       <c r="Q38" s="5">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>9016</v>
       </c>
       <c r="R38" s="5">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>9962</v>
       </c>
       <c r="S38" s="5">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>10234</v>
       </c>
       <c r="T38" s="5">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>10523</v>
       </c>
       <c r="U38" s="5">
-        <f t="shared" si="45"/>
+        <f t="shared" si="47"/>
         <v>-15751</v>
       </c>
       <c r="V38" s="5">
@@ -6637,40 +6752,40 @@
         <v>9997</v>
       </c>
       <c r="X38" s="5">
-        <f t="shared" ref="X38:AF38" si="46">39%*X29</f>
-        <v>9481.3187488503681</v>
+        <f t="shared" ref="X38:AF38" si="48">39%*X29</f>
+        <v>10109.800896000002</v>
       </c>
       <c r="Y38" s="5">
-        <f t="shared" si="46"/>
-        <v>9469.1999289606156</v>
+        <f t="shared" si="48"/>
+        <v>10248.8021392146</v>
       </c>
       <c r="Z38" s="5">
-        <f t="shared" si="46"/>
-        <v>9460.7496243015248</v>
+        <f t="shared" si="48"/>
+        <v>10411.374087219023</v>
       </c>
       <c r="AA38" s="5">
-        <f t="shared" si="46"/>
-        <v>9456.0902644146281</v>
+        <f t="shared" si="48"/>
+        <v>10599.929866859458</v>
       </c>
       <c r="AB38" s="5">
-        <f t="shared" si="46"/>
-        <v>9455.3502651956769</v>
+        <f t="shared" si="48"/>
+        <v>10817.140119814447</v>
       </c>
       <c r="AC38" s="5">
-        <f t="shared" si="46"/>
-        <v>9458.6642965439933</v>
+        <f t="shared" si="48"/>
+        <v>11065.960379935537</v>
       </c>
       <c r="AD38" s="5">
-        <f t="shared" si="46"/>
-        <v>10028.591108165687</v>
+        <f t="shared" si="48"/>
+        <v>12575.656025399356</v>
       </c>
       <c r="AE38" s="5">
-        <f t="shared" si="46"/>
-        <v>9959.6766317486235</v>
+        <f t="shared" si="48"/>
+        <v>12882.586304489079</v>
       </c>
       <c r="AF38" s="5">
-        <f t="shared" si="46"/>
-        <v>9895.9005001999594</v>
+        <f t="shared" si="48"/>
+        <v>13232.879223831482</v>
       </c>
       <c r="AG38" s="5"/>
       <c r="AH38" s="5"/>
@@ -6707,10 +6822,12 @@
         <v>-969</v>
       </c>
       <c r="H39" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>-850</v>
       </c>
-      <c r="I39" s="5"/>
+      <c r="I39" s="5">
+        <v>-403</v>
+      </c>
       <c r="J39" s="5"/>
       <c r="K39" s="5"/>
       <c r="L39" s="5">
@@ -6750,39 +6867,39 @@
         <v>-1819</v>
       </c>
       <c r="X39" s="5">
-        <f t="shared" ref="X39:AF39" si="47">W39*(1-0.1%)</f>
+        <f t="shared" ref="X39:AF39" si="49">W39*(1-0.1%)</f>
         <v>-1817.181</v>
       </c>
       <c r="Y39" s="5">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>-1815.3638190000001</v>
       </c>
       <c r="Z39" s="5">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>-1813.5484551810002</v>
       </c>
       <c r="AA39" s="5">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>-1811.7349067258192</v>
       </c>
       <c r="AB39" s="5">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>-1809.9231718190933</v>
       </c>
       <c r="AC39" s="5">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>-1808.1132486472743</v>
       </c>
       <c r="AD39" s="5">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>-1806.305135398627</v>
       </c>
       <c r="AE39" s="5">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>-1804.4988302632285</v>
       </c>
       <c r="AF39" s="5">
-        <f t="shared" si="47"/>
+        <f t="shared" si="49"/>
         <v>-1802.6943314329653</v>
       </c>
       <c r="AG39" s="5"/>
@@ -6820,10 +6937,12 @@
         <v>1474</v>
       </c>
       <c r="H40" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>207</v>
       </c>
-      <c r="I40" s="5"/>
+      <c r="I40" s="5">
+        <v>189</v>
+      </c>
       <c r="J40" s="5"/>
       <c r="K40" s="5"/>
       <c r="L40" s="5">
@@ -6863,39 +6982,39 @@
         <v>1681</v>
       </c>
       <c r="X40" s="5">
-        <f t="shared" ref="X40:AF40" si="48">W40*(1-0.1%)</f>
+        <f t="shared" ref="X40:AF40" si="50">W40*(1-0.1%)</f>
         <v>1679.319</v>
       </c>
       <c r="Y40" s="5">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>1677.6396809999999</v>
       </c>
       <c r="Z40" s="5">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>1675.9620413189998</v>
       </c>
       <c r="AA40" s="5">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>1674.2860792776808</v>
       </c>
       <c r="AB40" s="5">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>1672.6117931984031</v>
       </c>
       <c r="AC40" s="5">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>1670.9391814052046</v>
       </c>
       <c r="AD40" s="5">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>1669.2682422237995</v>
       </c>
       <c r="AE40" s="5">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>1667.5989739815757</v>
       </c>
       <c r="AF40" s="5">
-        <f t="shared" si="48"/>
+        <f t="shared" si="50"/>
         <v>1665.9313750075942</v>
       </c>
       <c r="AG40" s="5"/>
@@ -6916,11 +7035,11 @@
         <v>38</v>
       </c>
       <c r="C41" s="5">
-        <f t="shared" ref="C41:D41" si="49">C38+SUM(C39:C40)</f>
+        <f t="shared" ref="C41:D41" si="51">C38+SUM(C39:C40)</f>
         <v>5303</v>
       </c>
       <c r="D41" s="5">
-        <f t="shared" si="49"/>
+        <f t="shared" si="51"/>
         <v>-22364</v>
       </c>
       <c r="E41" s="5">
@@ -6928,54 +7047,57 @@
         <v>5600</v>
       </c>
       <c r="F41" s="5">
-        <f t="shared" ref="F41:H41" si="50">F38+SUM(F39:F40)</f>
+        <f t="shared" ref="F41:I41" si="52">F38+SUM(F39:F40)</f>
         <v>-2062</v>
       </c>
       <c r="G41" s="5">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>5574</v>
       </c>
       <c r="H41" s="5">
-        <f t="shared" si="50"/>
+        <f t="shared" si="52"/>
         <v>4285</v>
       </c>
-      <c r="I41" s="5"/>
+      <c r="I41" s="5">
+        <f t="shared" si="52"/>
+        <v>4052</v>
+      </c>
       <c r="J41" s="5"/>
       <c r="K41" s="5"/>
       <c r="L41" s="5">
-        <f t="shared" ref="L41:P41" si="51">L38+SUM(L39:L40)</f>
+        <f t="shared" ref="L41:P41" si="53">L38+SUM(L39:L40)</f>
         <v>4848</v>
       </c>
       <c r="M41" s="5">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>5855</v>
       </c>
       <c r="N41" s="5">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>6245</v>
       </c>
       <c r="O41" s="5">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>29591</v>
       </c>
       <c r="P41" s="5">
-        <f t="shared" si="51"/>
+        <f t="shared" si="53"/>
         <v>8351</v>
       </c>
       <c r="Q41" s="5">
-        <f t="shared" ref="Q41" si="52">Q38+SUM(Q39:Q40)</f>
+        <f t="shared" ref="Q41" si="54">Q38+SUM(Q39:Q40)</f>
         <v>7912</v>
       </c>
       <c r="R41" s="5">
-        <f t="shared" ref="R41" si="53">R38+SUM(R39:R40)</f>
+        <f t="shared" ref="R41" si="55">R38+SUM(R39:R40)</f>
         <v>8672</v>
       </c>
       <c r="S41" s="5">
-        <f t="shared" ref="S41" si="54">S38+SUM(S39:S40)</f>
+        <f t="shared" ref="S41" si="56">S38+SUM(S39:S40)</f>
         <v>9163</v>
       </c>
       <c r="T41" s="5">
-        <f t="shared" ref="T41" si="55">T38+SUM(T39:T40)</f>
+        <f t="shared" ref="T41" si="57">T38+SUM(T39:T40)</f>
         <v>9324</v>
       </c>
       <c r="U41" s="5">
@@ -6991,40 +7113,40 @@
         <v>9859</v>
       </c>
       <c r="X41" s="5">
-        <f t="shared" ref="X41:AE41" si="56">X38+SUM(X39:X40)</f>
-        <v>9343.4567488503671</v>
+        <f t="shared" ref="X41:AE41" si="58">X38+SUM(X39:X40)</f>
+        <v>9971.9388960000033</v>
       </c>
       <c r="Y41" s="5">
-        <f t="shared" si="56"/>
-        <v>9331.475790960616</v>
+        <f t="shared" si="58"/>
+        <v>10111.078001214601</v>
       </c>
       <c r="Z41" s="5">
-        <f t="shared" si="56"/>
-        <v>9323.1632104395248</v>
+        <f t="shared" si="58"/>
+        <v>10273.787673357023</v>
       </c>
       <c r="AA41" s="5">
-        <f t="shared" si="56"/>
-        <v>9318.641436966489</v>
+        <f t="shared" si="58"/>
+        <v>10462.481039411319</v>
       </c>
       <c r="AB41" s="5">
-        <f t="shared" si="56"/>
-        <v>9318.0388865749865</v>
+        <f t="shared" si="58"/>
+        <v>10679.828741193756</v>
       </c>
       <c r="AC41" s="5">
-        <f t="shared" si="56"/>
-        <v>9321.490229301924</v>
+        <f t="shared" si="58"/>
+        <v>10928.786312693468</v>
       </c>
       <c r="AD41" s="5">
-        <f t="shared" si="56"/>
-        <v>9891.5542149908597</v>
+        <f t="shared" si="58"/>
+        <v>12438.619132224529</v>
       </c>
       <c r="AE41" s="5">
-        <f t="shared" si="56"/>
-        <v>9822.7767754669712</v>
+        <f t="shared" si="58"/>
+        <v>12745.686448207427</v>
       </c>
       <c r="AF41" s="5">
-        <f t="shared" ref="AF41" si="57">AF38+SUM(AF39:AF40)</f>
-        <v>9759.1375437745883</v>
+        <f t="shared" ref="AF41" si="59">AF38+SUM(AF39:AF40)</f>
+        <v>13096.116267406111</v>
       </c>
       <c r="AG41" s="5"/>
       <c r="AH41" s="5"/>
@@ -7061,10 +7183,12 @@
         <v>1009</v>
       </c>
       <c r="H42" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>1085</v>
       </c>
-      <c r="I42" s="5"/>
+      <c r="I42" s="5">
+        <v>824</v>
+      </c>
       <c r="J42" s="5"/>
       <c r="K42" s="5"/>
       <c r="L42" s="5">
@@ -7104,40 +7228,40 @@
         <v>2094</v>
       </c>
       <c r="X42" s="5">
-        <f t="shared" ref="X42:AF42" si="58">X41*X64</f>
-        <v>2024.1913379383836</v>
+        <f t="shared" ref="X42:AF42" si="60">X41*X64</f>
+        <v>2160.3473830194225</v>
       </c>
       <c r="Y42" s="5">
-        <f t="shared" si="58"/>
-        <v>2062.0276663601685</v>
+        <f t="shared" si="60"/>
+        <v>2234.3006660775868</v>
       </c>
       <c r="Z42" s="5">
-        <f t="shared" si="58"/>
-        <v>2101.3946053925633</v>
+        <f t="shared" si="60"/>
+        <v>2315.660630028086</v>
       </c>
       <c r="AA42" s="5">
-        <f t="shared" si="58"/>
-        <v>2142.3829285502702</v>
+        <f t="shared" si="60"/>
+        <v>2405.354999517222</v>
       </c>
       <c r="AB42" s="5">
-        <f t="shared" si="58"/>
-        <v>2185.0892884615191</v>
+        <f t="shared" si="60"/>
+        <v>2504.4303494599017</v>
       </c>
       <c r="AC42" s="5">
-        <f t="shared" si="58"/>
-        <v>2229.61660436188</v>
+        <f t="shared" si="60"/>
+        <v>2614.0673678664593</v>
       </c>
       <c r="AD42" s="5">
-        <f t="shared" si="58"/>
-        <v>2413.29019692464</v>
+        <f t="shared" si="60"/>
+        <v>3034.709911369016</v>
       </c>
       <c r="AE42" s="5">
-        <f t="shared" si="58"/>
-        <v>2444.4404378985737</v>
+        <f t="shared" si="60"/>
+        <v>3171.8191378010756</v>
       </c>
       <c r="AF42" s="5">
-        <f t="shared" si="58"/>
-        <v>2477.1756109545036</v>
+        <f t="shared" si="60"/>
+        <v>3324.2056145153415</v>
       </c>
       <c r="AG42" s="5"/>
       <c r="AH42" s="5"/>
@@ -7157,11 +7281,11 @@
         <v>40</v>
       </c>
       <c r="C43" s="5">
-        <f t="shared" ref="C43:D43" si="59">C41-C42</f>
+        <f t="shared" ref="C43:D43" si="61">C41-C42</f>
         <v>4035</v>
       </c>
       <c r="D43" s="5">
-        <f t="shared" si="59"/>
+        <f t="shared" si="61"/>
         <v>-18224</v>
       </c>
       <c r="E43" s="5">
@@ -7180,92 +7304,95 @@
         <f>H41-H42</f>
         <v>3200</v>
       </c>
-      <c r="I43" s="5"/>
+      <c r="I43" s="5">
+        <f>I41-I42</f>
+        <v>3228</v>
+      </c>
       <c r="J43" s="5"/>
       <c r="K43" s="5"/>
       <c r="L43" s="5">
-        <f t="shared" ref="L43:O43" si="60">L41-L42</f>
+        <f t="shared" ref="L43:O43" si="62">L41-L42</f>
         <v>3393</v>
       </c>
       <c r="M43" s="5">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>4522</v>
       </c>
       <c r="N43" s="5">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>4839</v>
       </c>
       <c r="O43" s="5">
-        <f t="shared" si="60"/>
+        <f t="shared" si="62"/>
         <v>21478</v>
       </c>
       <c r="P43" s="5">
-        <f t="shared" ref="P43:AE43" si="61">P41-P42</f>
+        <f t="shared" ref="P43:AE43" si="63">P41-P42</f>
         <v>6210</v>
       </c>
       <c r="Q43" s="5">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v>5849</v>
       </c>
       <c r="R43" s="5">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v>6564</v>
       </c>
       <c r="S43" s="5">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v>6974</v>
       </c>
       <c r="T43" s="5">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v>6846</v>
       </c>
       <c r="U43" s="5">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v>-14189</v>
       </c>
       <c r="V43" s="5">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v>3181</v>
       </c>
       <c r="W43" s="5">
-        <f t="shared" si="61"/>
+        <f t="shared" si="63"/>
         <v>7765</v>
       </c>
       <c r="X43" s="5">
-        <f t="shared" si="61"/>
-        <v>7319.2654109119831</v>
+        <f t="shared" si="63"/>
+        <v>7811.5915129805808</v>
       </c>
       <c r="Y43" s="5">
-        <f t="shared" si="61"/>
-        <v>7269.448124600447</v>
+        <f t="shared" si="63"/>
+        <v>7876.7773351370142</v>
       </c>
       <c r="Z43" s="5">
-        <f t="shared" si="61"/>
-        <v>7221.768605046962</v>
+        <f t="shared" si="63"/>
+        <v>7958.1270433289374</v>
       </c>
       <c r="AA43" s="5">
-        <f t="shared" si="61"/>
-        <v>7176.2585084162183</v>
+        <f t="shared" si="63"/>
+        <v>8057.1260398940976</v>
       </c>
       <c r="AB43" s="5">
-        <f t="shared" si="61"/>
-        <v>7132.9495981134678</v>
+        <f t="shared" si="63"/>
+        <v>8175.3983917338546</v>
       </c>
       <c r="AC43" s="5">
-        <f t="shared" si="61"/>
-        <v>7091.8736249400445</v>
+        <f t="shared" si="63"/>
+        <v>8314.7189448270092</v>
       </c>
       <c r="AD43" s="5">
-        <f t="shared" si="61"/>
-        <v>7478.2640180662202</v>
+        <f t="shared" si="63"/>
+        <v>9403.9092208555121</v>
       </c>
       <c r="AE43" s="5">
-        <f t="shared" si="61"/>
-        <v>7378.3363375683975</v>
+        <f t="shared" si="63"/>
+        <v>9573.867310406351</v>
       </c>
       <c r="AF43" s="5">
-        <f t="shared" ref="AF43" si="62">AF41-AF42</f>
-        <v>7281.9619328200843</v>
+        <f t="shared" ref="AF43" si="64">AF41-AF42</f>
+        <v>9771.9106528907687</v>
       </c>
       <c r="AG43" s="5"/>
       <c r="AH43" s="5"/>
@@ -7302,10 +7429,12 @@
         <v>53</v>
       </c>
       <c r="H44" s="5">
-        <f t="shared" si="26"/>
+        <f t="shared" si="27"/>
         <v>-52</v>
       </c>
-      <c r="I44" s="5"/>
+      <c r="I44" s="5">
+        <v>38</v>
+      </c>
       <c r="J44" s="5"/>
       <c r="K44" s="5"/>
       <c r="L44" s="5">
@@ -7371,66 +7500,69 @@
         <v>42</v>
       </c>
       <c r="C45" s="5">
-        <f>C43-C44</f>
+        <f t="shared" ref="C45:I45" si="65">C43-C44</f>
         <v>3959</v>
       </c>
       <c r="D45" s="5">
-        <f>D43-D44</f>
+        <f t="shared" si="65"/>
         <v>-18326</v>
       </c>
       <c r="E45" s="5">
-        <f>E43-E44</f>
+        <f t="shared" si="65"/>
         <v>4492</v>
       </c>
       <c r="F45" s="5">
-        <f>F43-F44</f>
+        <f t="shared" si="65"/>
         <v>-1424</v>
       </c>
       <c r="G45" s="5">
-        <f>G43-G44</f>
+        <f t="shared" si="65"/>
         <v>4512</v>
       </c>
       <c r="H45" s="5">
-        <f>H43-H44</f>
+        <f t="shared" si="65"/>
         <v>3252</v>
       </c>
-      <c r="I45" s="5"/>
+      <c r="I45" s="5">
+        <f t="shared" si="65"/>
+        <v>3190</v>
+      </c>
       <c r="J45" s="5"/>
       <c r="K45" s="5"/>
       <c r="L45" s="5">
-        <f t="shared" ref="L45:O45" si="63">L43-L44</f>
+        <f t="shared" ref="L45:O45" si="66">L43-L44</f>
         <v>3115</v>
       </c>
       <c r="M45" s="5">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v>4290</v>
       </c>
       <c r="N45" s="5">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v>4648</v>
       </c>
       <c r="O45" s="5">
-        <f t="shared" si="63"/>
+        <f t="shared" si="66"/>
         <v>21307</v>
       </c>
       <c r="P45" s="5">
-        <f t="shared" ref="P45:T45" si="64">P43-P44</f>
+        <f t="shared" ref="P45:T45" si="67">P43-P44</f>
         <v>6032</v>
       </c>
       <c r="Q45" s="5">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v>5704</v>
       </c>
       <c r="R45" s="5">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v>6400</v>
       </c>
       <c r="S45" s="5">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v>6801</v>
       </c>
       <c r="T45" s="5">
-        <f t="shared" si="64"/>
+        <f t="shared" si="67"/>
         <v>6666</v>
       </c>
       <c r="U45" s="5">
@@ -7537,54 +7669,57 @@
         <f>+H45/H48</f>
         <v>1.4869684499314129</v>
       </c>
-      <c r="I47" s="3"/>
+      <c r="I47" s="43">
+        <f>+I45/I48</f>
+        <v>1.4539653600729261</v>
+      </c>
       <c r="J47" s="3"/>
       <c r="K47" s="3"/>
       <c r="L47" s="43">
         <v>1.671</v>
       </c>
       <c r="M47" s="43">
-        <f t="shared" ref="M47:W47" si="65">+M45/M48</f>
+        <f t="shared" ref="M47:W47" si="68">+M45/M48</f>
         <v>2.3027375201288245</v>
       </c>
       <c r="N47" s="43">
-        <f t="shared" si="65"/>
+        <f t="shared" si="68"/>
         <v>2.4922252010723862</v>
       </c>
       <c r="O47" s="43">
-        <f t="shared" si="65"/>
+        <f t="shared" si="68"/>
         <v>10.424168297455969</v>
       </c>
       <c r="P47" s="43">
-        <f t="shared" si="65"/>
+        <f t="shared" si="68"/>
         <v>2.639824945295405</v>
       </c>
       <c r="Q47" s="43">
-        <f t="shared" si="65"/>
+        <f t="shared" si="68"/>
         <v>2.4897424705368834</v>
       </c>
       <c r="R47" s="43">
-        <f t="shared" si="65"/>
+        <f t="shared" si="68"/>
         <v>2.7886710239651418</v>
       </c>
       <c r="S47" s="43">
-        <f t="shared" si="65"/>
+        <f t="shared" si="68"/>
         <v>2.9737647573240054</v>
       </c>
       <c r="T47" s="43">
-        <f t="shared" si="65"/>
+        <f t="shared" si="68"/>
         <v>2.9547872340425534</v>
       </c>
       <c r="U47" s="43">
-        <f t="shared" si="65"/>
+        <f t="shared" si="68"/>
         <v>-6.4454912516823688</v>
       </c>
       <c r="V47" s="43">
-        <f t="shared" si="65"/>
+        <f t="shared" si="68"/>
         <v>1.3857271906052393</v>
       </c>
       <c r="W47" s="43">
-        <f t="shared" si="65"/>
+        <f t="shared" si="68"/>
         <v>3.5500685871056241</v>
       </c>
       <c r="X47" s="43"/>
@@ -7635,11 +7770,13 @@
       <c r="H48" s="5">
         <v>2187</v>
       </c>
-      <c r="I48" s="3"/>
+      <c r="I48" s="3">
+        <v>2194</v>
+      </c>
       <c r="J48" s="3"/>
       <c r="K48" s="3"/>
       <c r="L48" s="5">
-        <f t="shared" ref="L48" si="66">L43/L47</f>
+        <f t="shared" ref="L48" si="69">L43/L47</f>
         <v>2030.5206463195691</v>
       </c>
       <c r="M48" s="5">
@@ -7796,7 +7933,7 @@
       <c r="C51" s="3"/>
       <c r="D51" s="44"/>
       <c r="E51" s="44" t="e">
-        <f t="shared" ref="E51:E60" si="67">+E19/C19-1</f>
+        <f t="shared" ref="E51:E60" si="70">+E19/C19-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="F51" s="44" t="e">
@@ -7807,8 +7944,14 @@
         <f>+G19/E19-1</f>
         <v>1.0040907400520549E-2</v>
       </c>
-      <c r="H51" s="3"/>
-      <c r="I51" s="3"/>
+      <c r="H51" s="44">
+        <f t="shared" ref="H51:I60" si="71">+H19/F19-1</f>
+        <v>3.4237288135593236E-2</v>
+      </c>
+      <c r="I51" s="44">
+        <f t="shared" si="71"/>
+        <v>4.6944035346097257E-2</v>
+      </c>
       <c r="J51" s="3"/>
       <c r="K51" s="3"/>
       <c r="L51" s="45" t="s">
@@ -7824,35 +7967,35 @@
         <v>216</v>
       </c>
       <c r="P51" s="44">
-        <f t="shared" ref="P51" si="68">P19/O19-1</f>
+        <f t="shared" ref="P51" si="72">P19/O19-1</f>
         <v>1.2494669509594885</v>
       </c>
       <c r="Q51" s="44">
-        <f t="shared" ref="Q51:W53" si="69">Q19/P19-1</f>
+        <f t="shared" ref="Q51:W53" si="73">Q19/P19-1</f>
         <v>9.2469720905739905E-2</v>
       </c>
       <c r="R51" s="44">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>0.10604453870625652</v>
       </c>
       <c r="S51" s="44">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>1.900113309509277E-2</v>
       </c>
       <c r="T51" s="44">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>8.108801642288932E-2</v>
       </c>
       <c r="U51" s="44">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>-8.2838832186090672E-2</v>
       </c>
       <c r="V51" s="44">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>-2.7087646652864006E-2</v>
       </c>
       <c r="W51" s="44">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>2.2699060117042036E-2</v>
       </c>
       <c r="X51" s="3"/>
@@ -7873,66 +8016,72 @@
       <c r="C52" s="3"/>
       <c r="D52" s="44"/>
       <c r="E52" s="44" t="e">
-        <f t="shared" si="67"/>
+        <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
       <c r="F52" s="44" t="e">
-        <f t="shared" ref="F52:G60" si="70">+F20/D20-1</f>
+        <f t="shared" ref="F52:G60" si="74">+F20/D20-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="G52" s="44">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>-2.1709323583181006E-2</v>
       </c>
-      <c r="H52" s="3"/>
-      <c r="I52" s="3"/>
+      <c r="H52" s="44">
+        <f t="shared" si="71"/>
+        <v>3.3504624871531385E-2</v>
+      </c>
+      <c r="I52" s="44">
+        <f t="shared" si="71"/>
+        <v>2.8264424199953231E-2</v>
+      </c>
       <c r="J52" s="3"/>
       <c r="K52" s="3"/>
       <c r="L52" s="45" t="s">
         <v>216</v>
       </c>
       <c r="M52" s="44">
-        <f t="shared" ref="M52:P52" si="71">M20/L20-1</f>
+        <f t="shared" ref="M52:P52" si="75">M20/L20-1</f>
         <v>0.16236201907619763</v>
       </c>
       <c r="N52" s="44">
-        <f t="shared" si="71"/>
+        <f t="shared" si="75"/>
         <v>-3.3284160059007917E-2</v>
       </c>
       <c r="O52" s="44">
-        <f t="shared" si="71"/>
+        <f t="shared" si="75"/>
         <v>0.10367191225560335</v>
       </c>
       <c r="P52" s="44">
-        <f t="shared" si="71"/>
+        <f t="shared" si="75"/>
         <v>-0.12590736259937785</v>
       </c>
       <c r="Q52" s="44">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>2.3331685615422648E-2</v>
       </c>
       <c r="R52" s="44">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>-5.6516278620423188E-2</v>
       </c>
       <c r="S52" s="44">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>3.6862584476755611E-3</v>
       </c>
       <c r="T52" s="44">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>7.6208936951642547E-2</v>
       </c>
       <c r="U52" s="44">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>-7.4414636458432049E-2</v>
       </c>
       <c r="V52" s="44">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>-5.3564113068414576E-2</v>
       </c>
       <c r="W52" s="44">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>7.358510983659805E-3</v>
       </c>
       <c r="X52" s="3"/>
@@ -7953,66 +8102,72 @@
       <c r="C53" s="3"/>
       <c r="D53" s="44"/>
       <c r="E53" s="44" t="e">
-        <f t="shared" si="67"/>
-        <v>#DIV/0!</v>
-      </c>
-      <c r="F53" s="44" t="e">
         <f t="shared" si="70"/>
         <v>#DIV/0!</v>
       </c>
+      <c r="F53" s="44" t="e">
+        <f t="shared" si="74"/>
+        <v>#DIV/0!</v>
+      </c>
       <c r="G53" s="44">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>-8.89404485692189E-2</v>
       </c>
-      <c r="H53" s="3"/>
-      <c r="I53" s="3"/>
+      <c r="H53" s="44">
+        <f t="shared" si="71"/>
+        <v>-0.12708182476466334</v>
+      </c>
+      <c r="I53" s="44">
+        <f t="shared" si="71"/>
+        <v>-8.9134125636672334E-2</v>
+      </c>
       <c r="J53" s="3"/>
       <c r="K53" s="3"/>
       <c r="L53" s="45" t="s">
         <v>216</v>
       </c>
       <c r="M53" s="44">
-        <f t="shared" ref="M53:P53" si="72">M21/L21-1</f>
+        <f t="shared" ref="M53:P53" si="76">M21/L21-1</f>
         <v>-2.5819777949909639E-2</v>
       </c>
       <c r="N53" s="44">
-        <f t="shared" si="72"/>
+        <f t="shared" si="76"/>
         <v>0.13066525311423272</v>
       </c>
       <c r="O53" s="44">
-        <f t="shared" si="72"/>
+        <f t="shared" si="76"/>
         <v>5.6962025316455778E-2</v>
       </c>
       <c r="P53" s="44">
-        <f t="shared" si="72"/>
+        <f t="shared" si="76"/>
         <v>8.2723442004879022E-2</v>
       </c>
       <c r="Q53" s="44">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>5.5510036870135115E-2</v>
       </c>
       <c r="R53" s="44">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>-0.11954201436056666</v>
       </c>
       <c r="S53" s="44">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>-7.6261847035485997E-2</v>
       </c>
       <c r="T53" s="44">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>6.5855404438081688E-2</v>
       </c>
       <c r="U53" s="44">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>0.29729124692187159</v>
       </c>
       <c r="V53" s="44">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>-7.7135461604831757E-2</v>
       </c>
       <c r="W53" s="44">
-        <f t="shared" si="69"/>
+        <f t="shared" si="73"/>
         <v>-0.1086387434554974</v>
       </c>
       <c r="X53" s="3"/>
@@ -8033,19 +8188,25 @@
       <c r="C54" s="3"/>
       <c r="D54" s="44"/>
       <c r="E54" s="44">
-        <f t="shared" si="67"/>
+        <f t="shared" si="70"/>
         <v>3.4642032332563577E-3</v>
       </c>
       <c r="F54" s="44">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>-9.9365750528541241E-2</v>
       </c>
       <c r="G54" s="44">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>-0.15189873417721522</v>
       </c>
-      <c r="H54" s="3"/>
-      <c r="I54" s="3"/>
+      <c r="H54" s="44">
+        <f t="shared" si="71"/>
+        <v>-5.5164319248826255E-2</v>
+      </c>
+      <c r="I54" s="44">
+        <f t="shared" si="71"/>
+        <v>3.5278154681139817E-2</v>
+      </c>
       <c r="J54" s="3"/>
       <c r="K54" s="3"/>
       <c r="L54" s="45" t="s">
@@ -8064,31 +8225,31 @@
         <v>216</v>
       </c>
       <c r="Q54" s="44">
-        <f t="shared" ref="Q54:W57" si="73">Q22/P22-1</f>
+        <f t="shared" ref="Q54:W57" si="77">Q22/P22-1</f>
         <v>0.26100628930817615</v>
       </c>
       <c r="R54" s="44">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>0.52369077306733169</v>
       </c>
       <c r="S54" s="44">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>0.51718494271685755</v>
       </c>
       <c r="T54" s="44">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>0.54908306364617054</v>
       </c>
       <c r="U54" s="44">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>0.26183844011142066</v>
       </c>
       <c r="V54" s="44">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>-5.0220750551876359E-2</v>
       </c>
       <c r="W54" s="44">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>-0.10400929692039507</v>
       </c>
       <c r="X54" s="3"/>
@@ -8109,19 +8270,25 @@
       <c r="C55" s="3"/>
       <c r="D55" s="44"/>
       <c r="E55" s="44">
-        <f t="shared" si="67"/>
+        <f t="shared" si="70"/>
         <v>-0.19818181818181824</v>
       </c>
       <c r="F55" s="44">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>7.623318385650224E-2</v>
       </c>
       <c r="G55" s="44">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>6.8027210884353817E-3</v>
       </c>
-      <c r="H55" s="3"/>
-      <c r="I55" s="3"/>
+      <c r="H55" s="44">
+        <f t="shared" si="71"/>
+        <v>-2.083333333333337E-2</v>
+      </c>
+      <c r="I55" s="44">
+        <f t="shared" si="71"/>
+        <v>-0.14189189189189189</v>
+      </c>
       <c r="J55" s="3"/>
       <c r="K55" s="3"/>
       <c r="L55" s="45" t="s">
@@ -8140,31 +8307,31 @@
         <v>216</v>
       </c>
       <c r="Q55" s="44">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>0.28849557522123903</v>
       </c>
       <c r="R55" s="44">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>-0.12912087912087911</v>
       </c>
       <c r="S55" s="44">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>0.34542586750788651</v>
       </c>
       <c r="T55" s="44">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>0.24267291910902689</v>
       </c>
       <c r="U55" s="44">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>-6.0377358490566024E-2</v>
       </c>
       <c r="V55" s="44">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>-7.5301204819277157E-2</v>
       </c>
       <c r="W55" s="44">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>-7.6004343105320338E-3</v>
       </c>
       <c r="X55" s="3"/>
@@ -8185,19 +8352,25 @@
       <c r="C56" s="3"/>
       <c r="D56" s="44"/>
       <c r="E56" s="44">
-        <f t="shared" si="67"/>
+        <f t="shared" si="70"/>
         <v>0.42083333333333339</v>
       </c>
       <c r="F56" s="44">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>0.5016722408026757</v>
       </c>
       <c r="G56" s="44">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>0.37829912023460421</v>
       </c>
-      <c r="H56" s="3"/>
-      <c r="I56" s="3"/>
+      <c r="H56" s="44">
+        <f>+H24/F24-1</f>
+        <v>0.54788418708240538</v>
+      </c>
+      <c r="I56" s="44">
+        <f t="shared" si="71"/>
+        <v>0.66808510638297869</v>
+      </c>
       <c r="J56" s="3"/>
       <c r="K56" s="3"/>
       <c r="L56" s="45" t="s">
@@ -8216,31 +8389,31 @@
         <v>216</v>
       </c>
       <c r="Q56" s="44">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>2.7058823529411766</v>
       </c>
       <c r="R56" s="44">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>0.5714285714285714</v>
       </c>
       <c r="S56" s="44">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>0.38383838383838387</v>
       </c>
       <c r="T56" s="44">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>0.45255474452554734</v>
       </c>
       <c r="U56" s="44">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>0.35427135678391952</v>
       </c>
       <c r="V56" s="44">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>0.46567717996289426</v>
       </c>
       <c r="W56" s="44">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>0.47468354430379756</v>
       </c>
       <c r="X56" s="3"/>
@@ -8261,19 +8434,25 @@
       <c r="C57" s="3"/>
       <c r="D57" s="44"/>
       <c r="E57" s="44">
-        <f t="shared" si="67"/>
+        <f t="shared" si="70"/>
         <v>-2.8021015761821366E-2</v>
       </c>
       <c r="F57" s="44">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>-9.2905405405405372E-2</v>
       </c>
       <c r="G57" s="44">
-        <f t="shared" si="70"/>
+        <f t="shared" si="74"/>
         <v>-2.3423423423423406E-2</v>
       </c>
-      <c r="H57" s="3"/>
-      <c r="I57" s="3"/>
+      <c r="H57" s="44">
+        <f>+H25/F25-1</f>
+        <v>-6.7039106145251437E-2</v>
+      </c>
+      <c r="I57" s="44">
+        <f t="shared" si="71"/>
+        <v>-8.856088560885611E-2</v>
+      </c>
       <c r="J57" s="3"/>
       <c r="K57" s="3"/>
       <c r="L57" s="45" t="s">
@@ -8292,31 +8471,31 @@
         <v>216</v>
       </c>
       <c r="Q57" s="44">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>0.22423556058890148</v>
       </c>
       <c r="R57" s="44">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>7.3080481036077671E-2</v>
       </c>
       <c r="S57" s="44">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>-3.6206896551724155E-2</v>
       </c>
       <c r="T57" s="44">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>8.1395348837209225E-2</v>
       </c>
       <c r="U57" s="44">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>-3.8047973531844526E-2</v>
       </c>
       <c r="V57" s="44">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>-6.1049011177988E-2</v>
       </c>
       <c r="W57" s="44">
-        <f t="shared" si="73"/>
+        <f t="shared" si="77"/>
         <v>-4.4871794871794823E-2</v>
       </c>
       <c r="X57" s="3"/>
@@ -8335,21 +8514,27 @@
         <v>202</v>
       </c>
       <c r="C58" s="3"/>
-      <c r="D58" s="44"/>
-      <c r="E58" s="44">
-        <f t="shared" si="67"/>
-        <v>-9.4297260889087964E-3</v>
-      </c>
-      <c r="F58" s="44">
-        <f t="shared" si="70"/>
-        <v>1.5330705212439844E-2</v>
-      </c>
-      <c r="G58" s="44">
-        <f t="shared" si="70"/>
-        <v>-5.8930190389845372E-3</v>
-      </c>
-      <c r="H58" s="3"/>
-      <c r="I58" s="3"/>
+      <c r="D58" s="109"/>
+      <c r="E58" s="109">
+        <f t="shared" ref="D58:I60" si="78">+E27/C27-1</f>
+        <v>-0.10130391173520559</v>
+      </c>
+      <c r="F58" s="109">
+        <f t="shared" si="78"/>
+        <v>-2.8004667444574083E-2</v>
+      </c>
+      <c r="G58" s="109">
+        <f t="shared" si="78"/>
+        <v>-3.4598214285714302E-2</v>
+      </c>
+      <c r="H58" s="109">
+        <f t="shared" si="78"/>
+        <v>-1.3205282112845107E-2</v>
+      </c>
+      <c r="I58" s="109">
+        <f t="shared" si="78"/>
+        <v>4.8344718864949954E-3</v>
+      </c>
       <c r="J58" s="3"/>
       <c r="K58" s="3"/>
       <c r="L58" s="45" t="s">
@@ -8368,31 +8553,31 @@
         <v>216</v>
       </c>
       <c r="Q58" s="44">
-        <f t="shared" ref="Q58:W60" si="74">Q27/P27-1</f>
+        <f t="shared" ref="Q58:W60" si="79">Q27/P27-1</f>
         <v>0.48806366047745353</v>
       </c>
       <c r="R58" s="44">
-        <f t="shared" si="74"/>
+        <f t="shared" si="79"/>
         <v>-1.0825616277553185E-2</v>
       </c>
       <c r="S58" s="44">
-        <f t="shared" si="74"/>
+        <f t="shared" si="79"/>
         <v>-3.1777426160337519E-2</v>
       </c>
       <c r="T58" s="44">
-        <f t="shared" si="74"/>
+        <f t="shared" si="79"/>
         <v>4.5440101684143697E-2</v>
       </c>
       <c r="U58" s="44">
-        <f t="shared" si="74"/>
+        <f t="shared" si="79"/>
         <v>-4.0034737299174949E-2</v>
       </c>
       <c r="V58" s="44">
-        <f t="shared" si="74"/>
+        <f t="shared" si="79"/>
         <v>-6.436584041975757E-2</v>
       </c>
       <c r="W58" s="44">
-        <f t="shared" si="74"/>
+        <f t="shared" si="79"/>
         <v>-2.3398598017887351E-2</v>
       </c>
       <c r="X58" s="3"/>
@@ -8411,20 +8596,26 @@
       </c>
       <c r="C59" s="3"/>
       <c r="D59" s="44"/>
-      <c r="E59" s="44">
-        <f t="shared" si="67"/>
-        <v>-0.10130391173520559</v>
-      </c>
-      <c r="F59" s="44">
-        <f t="shared" si="70"/>
-        <v>-2.8004667444574083E-2</v>
-      </c>
-      <c r="G59" s="44">
-        <f t="shared" si="70"/>
-        <v>-3.4598214285714302E-2</v>
-      </c>
-      <c r="H59" s="3"/>
-      <c r="I59" s="3"/>
+      <c r="E59" s="109">
+        <f t="shared" ref="E59" si="80">+E28/C28-1</f>
+        <v>0.12550607287449389</v>
+      </c>
+      <c r="F59" s="109">
+        <f t="shared" ref="F59" si="81">+F28/D28-1</f>
+        <v>-9.0909090909090939E-2</v>
+      </c>
+      <c r="G59" s="109">
+        <f t="shared" ref="G59" si="82">+G28/E28-1</f>
+        <v>0.29856115107913661</v>
+      </c>
+      <c r="H59" s="109">
+        <f t="shared" si="78"/>
+        <v>3.9473684210526327E-2</v>
+      </c>
+      <c r="I59" s="109">
+        <f t="shared" si="78"/>
+        <v>-0.30193905817174516</v>
+      </c>
       <c r="J59" s="3"/>
       <c r="K59" s="3"/>
       <c r="L59" s="45" t="s">
@@ -8443,31 +8634,31 @@
         <v>216</v>
       </c>
       <c r="Q59" s="44">
-        <f t="shared" si="74"/>
+        <f t="shared" si="79"/>
         <v>-0.9253628196268141</v>
       </c>
       <c r="R59" s="44">
-        <f t="shared" si="74"/>
+        <f t="shared" si="79"/>
         <v>-0.22037037037037033</v>
       </c>
       <c r="S59" s="44">
-        <f t="shared" si="74"/>
+        <f t="shared" si="79"/>
         <v>0.14726840855106893</v>
       </c>
       <c r="T59" s="44">
-        <f t="shared" si="74"/>
+        <f t="shared" si="79"/>
         <v>8.0745341614906874E-2</v>
       </c>
       <c r="U59" s="44">
-        <f t="shared" si="74"/>
+        <f t="shared" si="79"/>
         <v>0.2739463601532568</v>
       </c>
       <c r="V59" s="44">
-        <f t="shared" si="74"/>
+        <f t="shared" si="79"/>
         <v>-1.0526315789473717E-2</v>
       </c>
       <c r="W59" s="44">
-        <f t="shared" si="74"/>
+        <f t="shared" si="79"/>
         <v>0.14893617021276606</v>
       </c>
     </row>
@@ -8478,19 +8669,25 @@
       <c r="C60" s="46"/>
       <c r="D60" s="46"/>
       <c r="E60" s="46">
-        <f t="shared" si="67"/>
-        <v>0.12550607287449389</v>
+        <f t="shared" si="78"/>
+        <v>-8.1913548099099787E-2</v>
       </c>
       <c r="F60" s="46">
-        <f t="shared" si="70"/>
-        <v>-9.0909090909090939E-2</v>
+        <f t="shared" si="78"/>
+        <v>-2.2756827048114436E-2</v>
       </c>
       <c r="G60" s="46">
-        <f t="shared" si="70"/>
-        <v>0.29856115107913661</v>
-      </c>
-      <c r="H60" s="46"/>
-      <c r="I60" s="40"/>
+        <f t="shared" si="78"/>
+        <v>-2.1961102106969221E-2</v>
+      </c>
+      <c r="H60" s="46">
+        <f t="shared" si="78"/>
+        <v>1.0349671028313523E-3</v>
+      </c>
+      <c r="I60" s="46">
+        <f>+I29/G29-1</f>
+        <v>1.3754246416438853E-2</v>
+      </c>
       <c r="J60" s="40"/>
       <c r="K60" s="40"/>
       <c r="L60" s="46"/>
@@ -8511,68 +8708,68 @@
         <v>0.20697811945594324</v>
       </c>
       <c r="Q60" s="46">
-        <f t="shared" si="74"/>
+        <f t="shared" si="79"/>
         <v>5.6549077249714141E-2</v>
       </c>
       <c r="R60" s="46">
-        <f t="shared" si="74"/>
+        <f t="shared" si="79"/>
         <v>-3.9030799551725837E-3</v>
       </c>
       <c r="S60" s="46">
-        <f t="shared" si="74"/>
+        <f t="shared" si="79"/>
         <v>-3.5692116697703113E-3</v>
       </c>
       <c r="T60" s="46">
-        <f t="shared" si="74"/>
+        <f t="shared" si="79"/>
         <v>7.6740383117894329E-2</v>
       </c>
       <c r="U60" s="46">
-        <f t="shared" si="74"/>
+        <f t="shared" si="79"/>
         <v>-1.3451455433013959E-2</v>
       </c>
       <c r="V60" s="46">
-        <f t="shared" si="74"/>
+        <f t="shared" si="79"/>
         <v>-5.190045083018735E-2</v>
       </c>
       <c r="W60" s="46">
-        <f t="shared" si="74"/>
+        <f>W29/V29-1</f>
         <v>-9.9354389763018913E-3</v>
       </c>
       <c r="X60" s="46">
-        <f t="shared" ref="X60:AE60" si="75">X29/W29-1</f>
-        <v>-5.0719495704765971E-2</v>
+        <f t="shared" ref="X60:AE60" si="83">X29/W29-1</f>
+        <v>1.2204857477547959E-2</v>
       </c>
       <c r="Y60" s="46">
-        <f t="shared" si="75"/>
-        <v>-1.278178722893597E-3</v>
+        <f t="shared" si="83"/>
+        <v>1.3749157341921059E-2</v>
       </c>
       <c r="Z60" s="46">
-        <f t="shared" si="75"/>
-        <v>-8.9239901179460901E-4</v>
+        <f t="shared" si="83"/>
+        <v>1.5862531620391085E-2</v>
       </c>
       <c r="AA60" s="46">
-        <f t="shared" si="75"/>
-        <v>-4.9249373167314925E-4</v>
+        <f t="shared" si="83"/>
+        <v>1.8110556595205551E-2</v>
       </c>
       <c r="AB60" s="46">
-        <f t="shared" si="75"/>
-        <v>-7.8256361589201795E-5</v>
+        <f t="shared" si="83"/>
+        <v>2.0491668877366198E-2</v>
       </c>
       <c r="AC60" s="46">
-        <f t="shared" si="75"/>
-        <v>3.5049271104381496E-4</v>
+        <f t="shared" si="83"/>
+        <v>2.3002407047063134E-2</v>
       </c>
       <c r="AD60" s="46">
-        <f t="shared" si="75"/>
-        <v>6.0254470795620962E-2</v>
+        <f t="shared" si="83"/>
+        <v>0.13642698813572052</v>
       </c>
       <c r="AE60" s="46">
-        <f t="shared" si="75"/>
-        <v>-6.8718004028452961E-3</v>
+        <f t="shared" si="83"/>
+        <v>2.4406701206665327E-2</v>
       </c>
       <c r="AF60" s="46">
-        <f t="shared" ref="AF60" si="76">AF29/AE29-1</f>
-        <v>-6.4034339574201571E-3</v>
+        <f t="shared" ref="AF60" si="84">AF29/AE29-1</f>
+        <v>2.719119523541158E-2</v>
       </c>
     </row>
     <row r="61" spans="1:44" x14ac:dyDescent="0.2">
@@ -8599,93 +8796,99 @@
         <f>G33/G29</f>
         <v>0.71464081531195622</v>
       </c>
-      <c r="H61" s="44"/>
-      <c r="I61" s="3"/>
+      <c r="H61" s="44">
+        <f t="shared" ref="H61:I61" si="85">H33/H29</f>
+        <v>0.71146887231371392</v>
+      </c>
+      <c r="I61" s="44">
+        <f t="shared" si="85"/>
+        <v>0.70216591744993873</v>
+      </c>
       <c r="J61" s="3"/>
       <c r="K61" s="3"/>
       <c r="L61" s="44">
-        <f t="shared" ref="L61:AE61" si="77">L33/L29</f>
+        <f t="shared" ref="L61:AE61" si="86">L33/L29</f>
         <v>0.62608259967074653</v>
       </c>
       <c r="M61" s="44">
-        <f t="shared" si="77"/>
+        <f t="shared" si="86"/>
         <v>0.61294261294261299</v>
       </c>
       <c r="N61" s="44">
-        <f t="shared" si="77"/>
+        <f t="shared" si="86"/>
         <v>0.59277337129686125</v>
       </c>
       <c r="O61" s="44">
-        <f t="shared" si="77"/>
+        <f t="shared" si="86"/>
         <v>0.61994874827518232</v>
       </c>
       <c r="P61" s="44">
-        <f t="shared" si="77"/>
+        <f t="shared" si="86"/>
         <v>0.69153192879307523</v>
       </c>
       <c r="Q61" s="44">
-        <f t="shared" si="77"/>
+        <f t="shared" si="86"/>
         <v>0.70406152181473891</v>
       </c>
       <c r="R61" s="44">
-        <f t="shared" si="77"/>
+        <f t="shared" si="86"/>
         <v>0.73300744878957169</v>
       </c>
       <c r="S61" s="44">
-        <f t="shared" si="77"/>
+        <f t="shared" si="86"/>
         <v>0.7236022426413331</v>
       </c>
       <c r="T61" s="44">
-        <f t="shared" si="77"/>
+        <f t="shared" si="86"/>
         <v>0.72786114626649789</v>
       </c>
       <c r="U61" s="44">
-        <f t="shared" si="77"/>
+        <f t="shared" si="86"/>
         <v>0.73225085217901253</v>
       </c>
       <c r="V61" s="44">
-        <f t="shared" si="77"/>
+        <f t="shared" si="86"/>
         <v>0.71906289867398621</v>
       </c>
       <c r="W61" s="44">
-        <f t="shared" ref="W61" si="78">W33/W29</f>
+        <f t="shared" ref="W61" si="87">W33/W29</f>
         <v>0.71296368606013272</v>
       </c>
       <c r="X61" s="44">
-        <f t="shared" si="77"/>
-        <v>0.69792987812510054</v>
+        <f t="shared" si="86"/>
+        <v>0.71670825771324864</v>
       </c>
       <c r="Y61" s="44">
-        <f t="shared" si="77"/>
-        <v>0.69784574110222086</v>
+        <f t="shared" si="86"/>
+        <v>0.7208299030437465</v>
       </c>
       <c r="Z61" s="44">
-        <f t="shared" si="77"/>
-        <v>0.69787828223874659</v>
+        <f t="shared" si="86"/>
+        <v>0.72546391054068937</v>
       </c>
       <c r="AA61" s="44">
-        <f t="shared" si="77"/>
-        <v>0.69803168645492308</v>
+        <f t="shared" si="86"/>
+        <v>0.73061712051484407</v>
       </c>
       <c r="AB61" s="44">
-        <f t="shared" si="77"/>
-        <v>0.69831004561030952</v>
+        <f t="shared" si="86"/>
+        <v>0.73629035413711885</v>
       </c>
       <c r="AC61" s="44">
-        <f t="shared" si="77"/>
-        <v>0.69871733294346627</v>
+        <f t="shared" si="86"/>
+        <v>0.74247769662882279</v>
       </c>
       <c r="AD61" s="44">
-        <f t="shared" si="77"/>
-        <v>0.71612344707811604</v>
+        <f t="shared" si="86"/>
+        <v>0.77361961326715556</v>
       </c>
       <c r="AE61" s="44">
-        <f t="shared" si="77"/>
-        <v>0.71444504698990874</v>
+        <f t="shared" si="86"/>
+        <v>0.77923415955819009</v>
       </c>
       <c r="AF61" s="44">
-        <f t="shared" ref="AF61" si="79">AF33/AF29</f>
-        <v>0.71289212563073989</v>
+        <f t="shared" ref="AF61" si="88">AF33/AF29</f>
+        <v>0.78529306362402795</v>
       </c>
     </row>
     <row r="62" spans="1:44" x14ac:dyDescent="0.2">
@@ -8712,92 +8915,98 @@
         <f>G38/G29</f>
         <v>0.42000165713812249</v>
       </c>
-      <c r="H62" s="44"/>
-      <c r="I62" s="3"/>
+      <c r="H62" s="44">
+        <f t="shared" ref="H62:I62" si="89">H38/H29</f>
+        <v>0.36393176279447603</v>
+      </c>
+      <c r="I62" s="44">
+        <f t="shared" si="89"/>
+        <v>0.3486718430731508</v>
+      </c>
       <c r="J62" s="3"/>
       <c r="K62" s="3"/>
       <c r="L62" s="44">
-        <f t="shared" ref="L62:AE62" si="80">L38/L29</f>
+        <f t="shared" ref="L62:AE62" si="90">L38/L29</f>
         <v>0.32538830434471405</v>
       </c>
       <c r="M62" s="44">
-        <f t="shared" si="80"/>
+        <f t="shared" si="90"/>
         <v>0.34775641025641024</v>
       </c>
       <c r="N62" s="44">
-        <f t="shared" si="80"/>
+        <f t="shared" si="90"/>
         <v>0.31557182563893971</v>
       </c>
       <c r="O62" s="44">
-        <f t="shared" si="80"/>
+        <f t="shared" si="90"/>
         <v>0.31914054799921149</v>
       </c>
       <c r="P62" s="44">
-        <f t="shared" si="80"/>
+        <f t="shared" si="90"/>
         <v>0.38024661113833086</v>
       </c>
       <c r="Q62" s="44">
-        <f t="shared" si="80"/>
+        <f t="shared" si="90"/>
         <v>0.34841751362213547</v>
       </c>
       <c r="R62" s="44">
-        <f t="shared" si="80"/>
+        <f t="shared" si="90"/>
         <v>0.38648355058969586</v>
       </c>
       <c r="S62" s="44">
-        <f t="shared" si="80"/>
+        <f t="shared" si="90"/>
         <v>0.39845818408347611</v>
       </c>
       <c r="T62" s="44">
-        <f t="shared" si="80"/>
+        <f t="shared" si="90"/>
         <v>0.38050985355270295</v>
       </c>
       <c r="U62" s="44">
-        <f t="shared" si="80"/>
+        <f t="shared" si="90"/>
         <v>-0.57731920976432205</v>
       </c>
       <c r="V62" s="44">
-        <f t="shared" si="80"/>
+        <f t="shared" si="90"/>
         <v>0.1057718328372057</v>
       </c>
       <c r="W62" s="44">
-        <f t="shared" ref="W62" si="81">W38/W29</f>
+        <f t="shared" ref="W62" si="91">W38/W29</f>
         <v>0.39035532994923861</v>
       </c>
       <c r="X62" s="44">
-        <f t="shared" si="80"/>
+        <f t="shared" si="90"/>
+        <v>0.39000000000000007</v>
+      </c>
+      <c r="Y62" s="44">
+        <f t="shared" si="90"/>
         <v>0.39</v>
       </c>
-      <c r="Y62" s="44">
-        <f t="shared" si="80"/>
+      <c r="Z62" s="44">
+        <f t="shared" si="90"/>
         <v>0.39</v>
       </c>
-      <c r="Z62" s="44">
-        <f t="shared" si="80"/>
-        <v>0.38999999999999996</v>
-      </c>
       <c r="AA62" s="44">
-        <f t="shared" si="80"/>
+        <f t="shared" si="90"/>
         <v>0.39</v>
       </c>
       <c r="AB62" s="44">
-        <f t="shared" si="80"/>
+        <f t="shared" si="90"/>
         <v>0.39</v>
       </c>
       <c r="AC62" s="44">
-        <f t="shared" si="80"/>
+        <f t="shared" si="90"/>
         <v>0.39</v>
       </c>
       <c r="AD62" s="44">
-        <f t="shared" si="80"/>
+        <f t="shared" si="90"/>
         <v>0.39</v>
       </c>
       <c r="AE62" s="44">
-        <f t="shared" si="80"/>
-        <v>0.39000000000000007</v>
+        <f t="shared" si="90"/>
+        <v>0.39</v>
       </c>
       <c r="AF62" s="44">
-        <f t="shared" ref="AF62" si="82">AF38/AF29</f>
+        <f t="shared" ref="AF62" si="92">AF38/AF29</f>
         <v>0.39</v>
       </c>
     </row>
@@ -8825,93 +9034,99 @@
         <f>G43/G29</f>
         <v>0.3782417764520673</v>
       </c>
-      <c r="H63" s="44"/>
-      <c r="I63" s="3"/>
+      <c r="H63" s="44">
+        <f t="shared" ref="H63:I63" si="93">H43/H29</f>
+        <v>0.23631932648991949</v>
+      </c>
+      <c r="I63" s="44">
+        <f t="shared" si="93"/>
+        <v>0.26383326522272171</v>
+      </c>
       <c r="J63" s="3"/>
       <c r="K63" s="3"/>
       <c r="L63" s="44">
-        <f t="shared" ref="L63:AE63" si="83">L43/L29</f>
+        <f t="shared" ref="L63:AE63" si="94">L43/L29</f>
         <v>0.24286021043590295</v>
       </c>
       <c r="M63" s="44">
-        <f t="shared" si="83"/>
+        <f t="shared" si="94"/>
         <v>0.34508547008547008</v>
       </c>
       <c r="N63" s="44">
-        <f t="shared" si="83"/>
+        <f t="shared" si="94"/>
         <v>0.3280455562334757</v>
       </c>
       <c r="O63" s="44">
-        <f t="shared" si="83"/>
+        <f t="shared" si="94"/>
         <v>1.0584466784939879</v>
       </c>
       <c r="P63" s="44">
-        <f t="shared" si="83"/>
+        <f t="shared" si="94"/>
         <v>0.25355218030377263</v>
       </c>
       <c r="Q63" s="44">
-        <f t="shared" si="83"/>
+        <f t="shared" si="94"/>
         <v>0.22603083819608147</v>
       </c>
       <c r="R63" s="44">
-        <f t="shared" si="83"/>
+        <f t="shared" si="94"/>
         <v>0.25465549348230915</v>
       </c>
       <c r="S63" s="44">
-        <f t="shared" si="83"/>
+        <f t="shared" si="94"/>
         <v>0.27153091418782122</v>
       </c>
       <c r="T63" s="44">
-        <f t="shared" si="83"/>
+        <f t="shared" si="94"/>
         <v>0.24755017175917557</v>
       </c>
       <c r="U63" s="44">
-        <f t="shared" si="83"/>
+        <f t="shared" si="94"/>
         <v>-0.52006744126379068</v>
       </c>
       <c r="V63" s="44">
-        <f t="shared" si="83"/>
+        <f t="shared" si="94"/>
         <v>0.12297521939150269</v>
       </c>
       <c r="W63" s="44">
-        <f t="shared" ref="W63" si="84">W43/W29</f>
+        <f t="shared" ref="W63" si="95">W43/W29</f>
         <v>0.3032018742678641</v>
       </c>
       <c r="X63" s="44">
-        <f t="shared" si="83"/>
-        <v>0.30106713906246318</v>
+        <f t="shared" si="94"/>
+        <v>0.30134329265255849</v>
       </c>
       <c r="Y63" s="44">
-        <f t="shared" si="83"/>
-        <v>0.29940066635654683</v>
+        <f t="shared" si="94"/>
+        <v>0.29973680035731953</v>
       </c>
       <c r="Z63" s="44">
-        <f t="shared" si="83"/>
-        <v>0.2977025994572024</v>
+        <f t="shared" si="94"/>
+        <v>0.29810373932374046</v>
       </c>
       <c r="AA63" s="44">
-        <f t="shared" si="83"/>
-        <v>0.29597230356552429</v>
+        <f t="shared" si="94"/>
+        <v>0.2964433911381803</v>
       </c>
       <c r="AB63" s="44">
-        <f t="shared" si="83"/>
-        <v>0.2942091266046486</v>
+        <f t="shared" si="94"/>
+        <v>0.29475492944163656</v>
       </c>
       <c r="AC63" s="44">
-        <f t="shared" si="83"/>
-        <v>0.29241239851774808</v>
+        <f t="shared" si="94"/>
+        <v>0.29303741176971604</v>
       </c>
       <c r="AD63" s="44">
-        <f t="shared" si="83"/>
-        <v>0.29082080778735453</v>
+        <f t="shared" si="94"/>
+        <v>0.29163684095098191</v>
       </c>
       <c r="AE63" s="44">
-        <f t="shared" si="83"/>
-        <v>0.28892014048717796</v>
+        <f t="shared" si="94"/>
+        <v>0.28983374633068754</v>
       </c>
       <c r="AF63" s="44">
-        <f t="shared" ref="AF63" si="85">AF43/AF29</f>
-        <v>0.28698400451201461</v>
+        <f t="shared" ref="AF63" si="96">AF43/AF29</f>
+        <v>0.28799818166283697</v>
       </c>
     </row>
     <row r="64" spans="1:44" x14ac:dyDescent="0.2">
@@ -8938,56 +9153,62 @@
         <f>G42/G41</f>
         <v>0.18101901686401148</v>
       </c>
-      <c r="H64" s="44"/>
-      <c r="I64" s="3"/>
+      <c r="H64" s="44">
+        <f t="shared" ref="H64:I64" si="97">H42/H41</f>
+        <v>0.25320886814469079</v>
+      </c>
+      <c r="I64" s="44">
+        <f t="shared" si="97"/>
+        <v>0.20335636722606121</v>
+      </c>
       <c r="J64" s="3"/>
       <c r="K64" s="3"/>
       <c r="L64" s="44">
-        <f t="shared" ref="L64:V64" si="86">L42/L41</f>
+        <f t="shared" ref="L64:V64" si="98">L42/L41</f>
         <v>0.30012376237623761</v>
       </c>
       <c r="M64" s="44">
-        <f t="shared" si="86"/>
+        <f t="shared" si="98"/>
         <v>0.22766865926558497</v>
       </c>
       <c r="N64" s="44">
-        <f t="shared" si="86"/>
+        <f t="shared" si="98"/>
         <v>0.22514011208967175</v>
       </c>
       <c r="O64" s="44">
-        <f t="shared" si="86"/>
+        <f t="shared" si="98"/>
         <v>0.27417120070291645</v>
       </c>
       <c r="P64" s="44">
-        <f t="shared" si="86"/>
+        <f t="shared" si="98"/>
         <v>0.25637648185846007</v>
       </c>
       <c r="Q64" s="44">
-        <f t="shared" si="86"/>
+        <f t="shared" si="98"/>
         <v>0.26074317492416582</v>
       </c>
       <c r="R64" s="44">
-        <f t="shared" si="86"/>
+        <f t="shared" si="98"/>
         <v>0.24308118081180813</v>
       </c>
       <c r="S64" s="44">
-        <f t="shared" si="86"/>
+        <f t="shared" si="98"/>
         <v>0.23889555822328931</v>
       </c>
       <c r="T64" s="44">
-        <f t="shared" si="86"/>
+        <f t="shared" si="98"/>
         <v>0.26576576576576577</v>
       </c>
       <c r="U64" s="44">
-        <f t="shared" si="86"/>
+        <f t="shared" si="98"/>
         <v>0.16833714319207549</v>
       </c>
       <c r="V64" s="44">
-        <f t="shared" si="86"/>
+        <f t="shared" si="98"/>
         <v>0.10090446579988695</v>
       </c>
       <c r="W64" s="44">
-        <f t="shared" ref="W64" si="87">W42/W41</f>
+        <f t="shared" ref="W64" si="99">W42/W41</f>
         <v>0.21239476620346892</v>
       </c>
       <c r="X64" s="44">
@@ -8995,35 +9216,35 @@
         <v>0.2166426615275383</v>
       </c>
       <c r="Y64" s="44">
-        <f t="shared" ref="Y64:AF64" si="88">X64*(1+2%)</f>
+        <f t="shared" ref="Y64:AF64" si="100">X64*(1+2%)</f>
         <v>0.22097551475808908</v>
       </c>
       <c r="Z64" s="44">
-        <f t="shared" si="88"/>
+        <f t="shared" si="100"/>
         <v>0.22539502505325087</v>
       </c>
       <c r="AA64" s="44">
-        <f t="shared" si="88"/>
+        <f t="shared" si="100"/>
         <v>0.22990292555431591</v>
       </c>
       <c r="AB64" s="44">
-        <f t="shared" si="88"/>
+        <f t="shared" si="100"/>
         <v>0.23450098406540223</v>
       </c>
       <c r="AC64" s="44">
-        <f t="shared" si="88"/>
+        <f t="shared" si="100"/>
         <v>0.23919100374671029</v>
       </c>
       <c r="AD64" s="44">
-        <f t="shared" si="88"/>
+        <f t="shared" si="100"/>
         <v>0.24397482382164451</v>
       </c>
       <c r="AE64" s="44">
-        <f t="shared" si="88"/>
+        <f t="shared" si="100"/>
         <v>0.24885432029807741</v>
       </c>
       <c r="AF64" s="44">
-        <f t="shared" si="88"/>
+        <f t="shared" si="100"/>
         <v>0.25383140670403898</v>
       </c>
     </row>
@@ -9071,7 +9292,9 @@
         <v>86223</v>
       </c>
       <c r="H66" s="5"/>
-      <c r="I66" s="5"/>
+      <c r="I66" s="5">
+        <v>87087</v>
+      </c>
       <c r="J66" s="5"/>
       <c r="K66" s="5"/>
       <c r="L66" s="5">
@@ -9133,7 +9356,7 @@
         <v>4521</v>
       </c>
       <c r="D67" s="5">
-        <f t="shared" ref="D67:D73" si="89">U67</f>
+        <f t="shared" ref="D67:D73" si="101">U67</f>
         <v>4583</v>
       </c>
       <c r="E67" s="5">
@@ -9144,7 +9367,9 @@
         <v>4159</v>
       </c>
       <c r="H67" s="5"/>
-      <c r="I67" s="5"/>
+      <c r="I67" s="5">
+        <v>4222</v>
+      </c>
       <c r="J67" s="5"/>
       <c r="K67" s="5"/>
       <c r="L67" s="5">
@@ -9206,7 +9431,7 @@
         <v>2061</v>
       </c>
       <c r="D68" s="5">
-        <f t="shared" si="89"/>
+        <f t="shared" si="101"/>
         <v>1970</v>
       </c>
       <c r="E68" s="5">
@@ -9217,7 +9442,9 @@
         <v>1533</v>
       </c>
       <c r="H68" s="5"/>
-      <c r="I68" s="5"/>
+      <c r="I68" s="5">
+        <v>1589</v>
+      </c>
       <c r="J68" s="5"/>
       <c r="K68" s="5"/>
       <c r="L68" s="5">
@@ -9279,7 +9506,7 @@
         <v>1027</v>
       </c>
       <c r="D69" s="5">
-        <f t="shared" si="89"/>
+        <f t="shared" si="101"/>
         <v>956</v>
       </c>
       <c r="E69" s="5">
@@ -9290,7 +9517,9 @@
         <v>841</v>
       </c>
       <c r="H69" s="5"/>
-      <c r="I69" s="5"/>
+      <c r="I69" s="5">
+        <v>919</v>
+      </c>
       <c r="J69" s="5"/>
       <c r="K69" s="5"/>
       <c r="L69" s="5">
@@ -9352,7 +9581,7 @@
         <v>720</v>
       </c>
       <c r="D70" s="5">
-        <f t="shared" si="89"/>
+        <f t="shared" si="101"/>
         <v>911</v>
       </c>
       <c r="E70" s="5">
@@ -9363,7 +9592,9 @@
         <v>2434</v>
       </c>
       <c r="H70" s="5"/>
-      <c r="I70" s="5"/>
+      <c r="I70" s="5">
+        <v>2058</v>
+      </c>
       <c r="J70" s="5"/>
       <c r="K70" s="5"/>
       <c r="L70" s="5">
@@ -9425,7 +9656,7 @@
         <v>284</v>
       </c>
       <c r="D71" s="5">
-        <f t="shared" si="89"/>
+        <f t="shared" si="101"/>
         <v>321</v>
       </c>
       <c r="E71" s="5">
@@ -9436,7 +9667,9 @@
         <v>283</v>
       </c>
       <c r="H71" s="5"/>
-      <c r="I71" s="5"/>
+      <c r="I71" s="5">
+        <v>323</v>
+      </c>
       <c r="J71" s="5"/>
       <c r="K71" s="5"/>
       <c r="L71" s="5">
@@ -9498,7 +9731,7 @@
         <v>111</v>
       </c>
       <c r="D72" s="5">
-        <f t="shared" si="89"/>
+        <f t="shared" si="101"/>
         <v>118</v>
       </c>
       <c r="E72" s="5">
@@ -9509,7 +9742,9 @@
         <v>737</v>
       </c>
       <c r="H72" s="5"/>
-      <c r="I72" s="5"/>
+      <c r="I72" s="5">
+        <v>263</v>
+      </c>
       <c r="J72" s="5"/>
       <c r="K72" s="5"/>
       <c r="L72" s="5">
@@ -9571,7 +9806,7 @@
         <v>130</v>
       </c>
       <c r="D73" s="5">
-        <f t="shared" si="89"/>
+        <f t="shared" si="101"/>
         <v>109</v>
       </c>
       <c r="E73" s="5">
@@ -9582,7 +9817,9 @@
         <v>141</v>
       </c>
       <c r="H73" s="5"/>
-      <c r="I73" s="5"/>
+      <c r="I73" s="5">
+        <v>4</v>
+      </c>
       <c r="J73" s="5"/>
       <c r="K73" s="5"/>
       <c r="L73" s="5">
@@ -9641,63 +9878,69 @@
         <v>63</v>
       </c>
       <c r="C74" s="5">
-        <f t="shared" ref="C74:G74" si="90">SUM(C66:C73)</f>
+        <f t="shared" ref="C74:I74" si="102">SUM(C66:C73)</f>
         <v>130980</v>
       </c>
       <c r="D74" s="5">
-        <f t="shared" si="90"/>
+        <f t="shared" si="102"/>
         <v>104530</v>
       </c>
       <c r="E74" s="5">
-        <f t="shared" si="90"/>
+        <f t="shared" si="102"/>
         <v>103497</v>
       </c>
       <c r="F74" s="5">
-        <f t="shared" si="90"/>
+        <f t="shared" si="102"/>
         <v>0</v>
       </c>
       <c r="G74" s="5">
-        <f t="shared" si="90"/>
+        <f t="shared" si="102"/>
         <v>96351</v>
       </c>
-      <c r="H74" s="5"/>
-      <c r="I74" s="5"/>
+      <c r="H74" s="5">
+        <f t="shared" si="102"/>
+        <v>0</v>
+      </c>
+      <c r="I74" s="5">
+        <f t="shared" si="102"/>
+        <v>96465</v>
+      </c>
       <c r="J74" s="5"/>
       <c r="K74" s="5"/>
       <c r="L74" s="5">
-        <f t="shared" ref="L74:N74" si="91">SUM(L66:L73)</f>
+        <f t="shared" ref="L74:N74" si="103">SUM(L66:L73)</f>
         <v>17035</v>
       </c>
       <c r="M74" s="5">
-        <f t="shared" si="91"/>
+        <f t="shared" si="103"/>
         <v>21701</v>
       </c>
       <c r="N74" s="5">
-        <f t="shared" si="91"/>
+        <f t="shared" si="103"/>
         <v>27414</v>
       </c>
       <c r="O74" s="5">
-        <f t="shared" ref="O74:T74" si="92">SUM(O66:O73)</f>
+        <f t="shared" ref="O74:T74" si="104">SUM(O66:O73)</f>
         <v>127072</v>
       </c>
       <c r="P74" s="5">
-        <f t="shared" si="92"/>
+        <f t="shared" si="104"/>
         <v>133687</v>
       </c>
       <c r="Q74" s="5">
-        <f t="shared" si="92"/>
+        <f t="shared" si="104"/>
         <v>127731</v>
       </c>
       <c r="R74" s="5">
-        <f t="shared" si="92"/>
+        <f t="shared" si="104"/>
         <v>124078</v>
       </c>
       <c r="S74" s="5">
-        <f t="shared" si="92"/>
+        <f t="shared" si="104"/>
         <v>124558</v>
       </c>
       <c r="T74" s="5">
-        <f t="shared" si="92"/>
+        <f t="shared" si="104"/>
         <v>138137</v>
       </c>
       <c r="U74" s="5">
@@ -9735,7 +9978,7 @@
         <v>5634</v>
       </c>
       <c r="D75" s="5">
-        <f t="shared" ref="D75:D81" si="93">U75</f>
+        <f t="shared" ref="D75:D81" si="105">U75</f>
         <v>4938</v>
       </c>
       <c r="E75" s="5">
@@ -9746,7 +9989,9 @@
         <v>5088</v>
       </c>
       <c r="H75" s="5"/>
-      <c r="I75" s="5"/>
+      <c r="I75" s="5">
+        <v>4845</v>
+      </c>
       <c r="J75" s="5"/>
       <c r="K75" s="5"/>
       <c r="L75" s="5">
@@ -9808,7 +10053,7 @@
         <v>160</v>
       </c>
       <c r="D76" s="5">
-        <f t="shared" si="93"/>
+        <f t="shared" si="105"/>
         <v>172</v>
       </c>
       <c r="E76" s="5">
@@ -9819,7 +10064,9 @@
         <v>108</v>
       </c>
       <c r="H76" s="5"/>
-      <c r="I76" s="5"/>
+      <c r="I76" s="5">
+        <v>465</v>
+      </c>
       <c r="J76" s="5"/>
       <c r="K76" s="5"/>
       <c r="L76" s="5">
@@ -9881,7 +10128,7 @@
         <v>4219</v>
       </c>
       <c r="D77" s="5">
-        <f t="shared" si="93"/>
+        <f t="shared" si="105"/>
         <v>3621</v>
       </c>
       <c r="E77" s="5">
@@ -9892,7 +10139,9 @@
         <v>3475</v>
       </c>
       <c r="H77" s="5"/>
-      <c r="I77" s="5"/>
+      <c r="I77" s="5">
+        <v>3845</v>
+      </c>
       <c r="J77" s="5"/>
       <c r="K77" s="5"/>
       <c r="L77" s="5">
@@ -9954,7 +10203,7 @@
         <v>451</v>
       </c>
       <c r="D78" s="5">
-        <f t="shared" si="93"/>
+        <f t="shared" si="105"/>
         <v>601</v>
       </c>
       <c r="E78" s="5">
@@ -9965,7 +10214,9 @@
         <v>489</v>
       </c>
       <c r="H78" s="5"/>
-      <c r="I78" s="5"/>
+      <c r="I78" s="5">
+        <v>15</v>
+      </c>
       <c r="J78" s="5"/>
       <c r="K78" s="5"/>
       <c r="L78" s="5">
@@ -10027,7 +10278,7 @@
         <v>413</v>
       </c>
       <c r="D79" s="5">
-        <f t="shared" si="93"/>
+        <f t="shared" si="105"/>
         <v>181</v>
       </c>
       <c r="E79" s="5">
@@ -10038,7 +10289,9 @@
         <v>302</v>
       </c>
       <c r="H79" s="5"/>
-      <c r="I79" s="5"/>
+      <c r="I79" s="5">
+        <v>235</v>
+      </c>
       <c r="J79" s="5"/>
       <c r="K79" s="5"/>
       <c r="L79" s="5">
@@ -10100,7 +10353,7 @@
         <v>3681</v>
       </c>
       <c r="D80" s="5">
-        <f t="shared" si="93"/>
+        <f t="shared" si="105"/>
         <v>4659</v>
       </c>
       <c r="E80" s="5">
@@ -10111,7 +10364,9 @@
         <v>4404</v>
       </c>
       <c r="H80" s="5"/>
-      <c r="I80" s="5"/>
+      <c r="I80" s="5">
+        <v>2518</v>
+      </c>
       <c r="J80" s="5"/>
       <c r="K80" s="5"/>
       <c r="L80" s="5">
@@ -10173,7 +10428,7 @@
         <v>534</v>
       </c>
       <c r="D81" s="5">
-        <f t="shared" si="93"/>
+        <f t="shared" si="105"/>
         <v>14</v>
       </c>
       <c r="E81" s="5">
@@ -10184,7 +10439,9 @@
         <v>9</v>
       </c>
       <c r="H81" s="5"/>
-      <c r="I81" s="5"/>
+      <c r="I81" s="5">
+        <v>0</v>
+      </c>
       <c r="J81" s="5"/>
       <c r="K81" s="5"/>
       <c r="L81" s="5">
@@ -10243,63 +10500,69 @@
         <v>61</v>
       </c>
       <c r="C82" s="5">
-        <f t="shared" ref="C82:G82" si="94">SUM(C75:C81)</f>
+        <f t="shared" ref="C82:I82" si="106">SUM(C75:C81)</f>
         <v>15092</v>
       </c>
       <c r="D82" s="5">
-        <f t="shared" si="94"/>
+        <f t="shared" si="106"/>
         <v>14186</v>
       </c>
       <c r="E82" s="5">
-        <f t="shared" si="94"/>
+        <f t="shared" si="106"/>
         <v>15872</v>
       </c>
       <c r="F82" s="5">
-        <f t="shared" si="94"/>
+        <f t="shared" si="106"/>
         <v>0</v>
       </c>
       <c r="G82" s="5">
-        <f t="shared" si="94"/>
+        <f t="shared" si="106"/>
         <v>13875</v>
       </c>
-      <c r="H82" s="5"/>
-      <c r="I82" s="5"/>
+      <c r="H82" s="5">
+        <f t="shared" si="106"/>
+        <v>0</v>
+      </c>
+      <c r="I82" s="5">
+        <f t="shared" si="106"/>
+        <v>11923</v>
+      </c>
       <c r="J82" s="5"/>
       <c r="K82" s="5"/>
       <c r="L82" s="5">
-        <f t="shared" ref="L82:O82" si="95">SUM(L75:L81)</f>
+        <f t="shared" ref="L82:O82" si="107">SUM(L75:L81)</f>
         <v>9132</v>
       </c>
       <c r="M82" s="5">
-        <f t="shared" si="95"/>
+        <f t="shared" si="107"/>
         <v>9814</v>
       </c>
       <c r="N82" s="5">
-        <f t="shared" si="95"/>
+        <f t="shared" si="107"/>
         <v>12359</v>
       </c>
       <c r="O82" s="5">
-        <f t="shared" si="95"/>
+        <f t="shared" si="107"/>
         <v>13966</v>
       </c>
       <c r="P82" s="5">
-        <f t="shared" ref="P82:T82" si="96">SUM(P75:P81)</f>
+        <f t="shared" ref="P82:T82" si="108">SUM(P75:P81)</f>
         <v>12655</v>
       </c>
       <c r="Q82" s="5">
-        <f t="shared" si="96"/>
+        <f t="shared" si="108"/>
         <v>13274</v>
       </c>
       <c r="R82" s="5">
-        <f t="shared" si="96"/>
+        <f t="shared" si="108"/>
         <v>13612</v>
       </c>
       <c r="S82" s="5">
-        <f t="shared" si="96"/>
+        <f t="shared" si="108"/>
         <v>12807</v>
       </c>
       <c r="T82" s="5">
-        <f t="shared" si="96"/>
+        <f t="shared" si="108"/>
         <v>15409</v>
       </c>
       <c r="U82" s="5">
@@ -10353,56 +10616,62 @@
         <f>G82+G74</f>
         <v>110226</v>
       </c>
-      <c r="H83" s="41"/>
-      <c r="I83" s="5"/>
+      <c r="H83" s="41">
+        <f t="shared" ref="H83:I83" si="109">H82+H74</f>
+        <v>0</v>
+      </c>
+      <c r="I83" s="41">
+        <f t="shared" si="109"/>
+        <v>108388</v>
+      </c>
       <c r="J83" s="5"/>
       <c r="K83" s="5"/>
       <c r="L83" s="41">
-        <f t="shared" ref="L83:W83" si="97">L82+L74</f>
+        <f t="shared" ref="L83:W83" si="110">L82+L74</f>
         <v>26167</v>
       </c>
       <c r="M83" s="41">
-        <f t="shared" si="97"/>
+        <f t="shared" si="110"/>
         <v>31515</v>
       </c>
       <c r="N83" s="41">
-        <f t="shared" si="97"/>
+        <f t="shared" si="110"/>
         <v>39773</v>
       </c>
       <c r="O83" s="41">
-        <f t="shared" si="97"/>
+        <f t="shared" si="110"/>
         <v>141038</v>
       </c>
       <c r="P83" s="41">
-        <f t="shared" si="97"/>
+        <f t="shared" si="110"/>
         <v>146342</v>
       </c>
       <c r="Q83" s="41">
-        <f t="shared" si="97"/>
+        <f t="shared" si="110"/>
         <v>141005</v>
       </c>
       <c r="R83" s="41">
-        <f t="shared" si="97"/>
+        <f t="shared" si="110"/>
         <v>137690</v>
       </c>
       <c r="S83" s="41">
-        <f t="shared" si="97"/>
+        <f t="shared" si="110"/>
         <v>137365</v>
       </c>
       <c r="T83" s="41">
-        <f t="shared" si="97"/>
+        <f t="shared" si="110"/>
         <v>153546</v>
       </c>
       <c r="U83" s="41">
-        <f t="shared" si="97"/>
+        <f t="shared" si="110"/>
         <v>118716</v>
       </c>
       <c r="V83" s="41">
-        <f t="shared" si="97"/>
+        <f t="shared" si="110"/>
         <v>118899</v>
       </c>
       <c r="W83" s="41">
-        <f t="shared" si="97"/>
+        <f t="shared" si="110"/>
         <v>109290</v>
       </c>
       <c r="X83" s="5"/>
@@ -10428,7 +10697,7 @@
         <v>614</v>
       </c>
       <c r="D84" s="5">
-        <f t="shared" ref="D84:D90" si="98">U84</f>
+        <f t="shared" ref="D84:D90" si="111">U84</f>
         <v>614</v>
       </c>
       <c r="E84" s="5">
@@ -10439,7 +10708,9 @@
         <v>581</v>
       </c>
       <c r="H84" s="5"/>
-      <c r="I84" s="5"/>
+      <c r="I84" s="5">
+        <v>573</v>
+      </c>
       <c r="J84" s="5"/>
       <c r="K84" s="5"/>
       <c r="L84" s="5">
@@ -10501,7 +10772,7 @@
         <v>26629</v>
       </c>
       <c r="D85" s="5">
-        <f t="shared" si="98"/>
+        <f t="shared" si="111"/>
         <v>26630</v>
       </c>
       <c r="E85" s="5">
@@ -10512,7 +10783,9 @@
         <v>26671</v>
       </c>
       <c r="H85" s="5"/>
-      <c r="I85" s="5"/>
+      <c r="I85" s="5">
+        <v>26682</v>
+      </c>
       <c r="J85" s="5"/>
       <c r="K85" s="5"/>
       <c r="L85" s="5">
@@ -10574,7 +10847,7 @@
         <v>-1721</v>
       </c>
       <c r="D86" s="5">
-        <f t="shared" si="98"/>
+        <f t="shared" si="111"/>
         <v>-894</v>
       </c>
       <c r="E86" s="5">
@@ -10585,7 +10858,9 @@
         <v>-5057</v>
       </c>
       <c r="H86" s="5"/>
-      <c r="I86" s="5"/>
+      <c r="I86" s="111">
+        <v>-3578</v>
+      </c>
       <c r="J86" s="5"/>
       <c r="K86" s="5"/>
       <c r="L86" s="5">
@@ -10647,7 +10922,7 @@
         <v>45591</v>
       </c>
       <c r="D87" s="5">
-        <f t="shared" si="98"/>
+        <f t="shared" si="111"/>
         <v>24531</v>
       </c>
       <c r="E87" s="5">
@@ -10658,7 +10933,9 @@
         <v>22994</v>
       </c>
       <c r="H87" s="5"/>
-      <c r="I87" s="5"/>
+      <c r="I87" s="5">
+        <v>22809</v>
+      </c>
       <c r="J87" s="5"/>
       <c r="K87" s="5"/>
       <c r="L87" s="5">
@@ -10720,7 +10997,7 @@
         <v>-500</v>
       </c>
       <c r="D88" s="5">
-        <f t="shared" si="98"/>
+        <f t="shared" si="111"/>
         <v>0</v>
       </c>
       <c r="E88" s="5">
@@ -10731,7 +11008,9 @@
         <v>0</v>
       </c>
       <c r="H88" s="5"/>
-      <c r="I88" s="5"/>
+      <c r="I88" s="5">
+        <v>0</v>
+      </c>
       <c r="J88" s="5"/>
       <c r="K88" s="5"/>
       <c r="L88" s="5">
@@ -10793,7 +11072,7 @@
         <v>1685</v>
       </c>
       <c r="D89" s="5">
-        <f t="shared" si="98"/>
+        <f t="shared" si="111"/>
         <v>1685</v>
       </c>
       <c r="E89" s="5">
@@ -10804,7 +11083,9 @@
         <v>1685</v>
       </c>
       <c r="H89" s="5"/>
-      <c r="I89" s="5"/>
+      <c r="I89" s="5">
+        <v>1893</v>
+      </c>
       <c r="J89" s="5"/>
       <c r="K89" s="5"/>
       <c r="L89" s="5">
@@ -10866,7 +11147,7 @@
         <v>330</v>
       </c>
       <c r="D90" s="5">
-        <f t="shared" si="98"/>
+        <f t="shared" si="111"/>
         <v>368</v>
       </c>
       <c r="E90" s="5">
@@ -10877,7 +11158,9 @@
         <v>303</v>
       </c>
       <c r="H90" s="5"/>
-      <c r="I90" s="5"/>
+      <c r="I90" s="5">
+        <v>216</v>
+      </c>
       <c r="J90" s="5"/>
       <c r="K90" s="5"/>
       <c r="L90" s="5">
@@ -10936,63 +11219,69 @@
         <v>70</v>
       </c>
       <c r="C91" s="41">
-        <f t="shared" ref="C91:G91" si="99">SUM(C84:C90)</f>
+        <f t="shared" ref="C91:I91" si="112">SUM(C84:C90)</f>
         <v>72628</v>
       </c>
       <c r="D91" s="41">
-        <f t="shared" si="99"/>
+        <f t="shared" si="112"/>
         <v>52934</v>
       </c>
       <c r="E91" s="41">
-        <f t="shared" si="99"/>
+        <f t="shared" si="112"/>
         <v>54469</v>
       </c>
       <c r="F91" s="41">
-        <f t="shared" si="99"/>
+        <f t="shared" si="112"/>
         <v>0</v>
       </c>
       <c r="G91" s="41">
-        <f t="shared" si="99"/>
+        <f t="shared" si="112"/>
         <v>47177</v>
       </c>
-      <c r="H91" s="5"/>
-      <c r="I91" s="5"/>
+      <c r="H91" s="41">
+        <f t="shared" si="112"/>
+        <v>0</v>
+      </c>
+      <c r="I91" s="41">
+        <f t="shared" si="112"/>
+        <v>48595</v>
+      </c>
       <c r="J91" s="5"/>
       <c r="K91" s="5"/>
       <c r="L91" s="41">
-        <f t="shared" ref="L91:O91" si="100">SUM(L84:L90)</f>
+        <f t="shared" ref="L91:O91" si="113">SUM(L84:L90)</f>
         <v>5814</v>
       </c>
       <c r="M91" s="41">
-        <f t="shared" si="100"/>
+        <f t="shared" si="113"/>
         <v>5032</v>
       </c>
       <c r="N91" s="41">
-        <f t="shared" si="100"/>
+        <f t="shared" si="113"/>
         <v>8406</v>
       </c>
       <c r="O91" s="41">
-        <f t="shared" si="100"/>
+        <f t="shared" si="113"/>
         <v>61026</v>
       </c>
       <c r="P91" s="41">
-        <f t="shared" ref="P91:T91" si="101">SUM(P84:P90)</f>
+        <f t="shared" ref="P91:T91" si="114">SUM(P84:P90)</f>
         <v>65688</v>
       </c>
       <c r="Q91" s="41">
-        <f t="shared" si="101"/>
+        <f t="shared" si="114"/>
         <v>64160</v>
       </c>
       <c r="R91" s="41">
-        <f t="shared" si="101"/>
+        <f t="shared" si="114"/>
         <v>62955</v>
       </c>
       <c r="S91" s="41">
-        <f t="shared" si="101"/>
+        <f t="shared" si="114"/>
         <v>67401</v>
       </c>
       <c r="T91" s="41">
-        <f t="shared" si="101"/>
+        <f t="shared" si="114"/>
         <v>75710</v>
       </c>
       <c r="U91" s="41">
@@ -11030,7 +11319,7 @@
         <v>37140</v>
       </c>
       <c r="D92" s="5">
-        <f t="shared" ref="D92:D97" si="102">U92</f>
+        <f t="shared" ref="D92:D97" si="115">U92</f>
         <v>35406</v>
       </c>
       <c r="E92" s="5">
@@ -11041,7 +11330,9 @@
         <v>31904</v>
       </c>
       <c r="H92" s="5"/>
-      <c r="I92" s="5"/>
+      <c r="I92" s="5">
+        <v>31045</v>
+      </c>
       <c r="J92" s="5"/>
       <c r="K92" s="5"/>
       <c r="L92" s="5">
@@ -11103,7 +11394,7 @@
         <v>881</v>
       </c>
       <c r="D93" s="5">
-        <f t="shared" si="102"/>
+        <f t="shared" si="115"/>
         <v>881</v>
       </c>
       <c r="E93" s="5">
@@ -11114,7 +11405,9 @@
         <v>769</v>
       </c>
       <c r="H93" s="5"/>
-      <c r="I93" s="5"/>
+      <c r="I93" s="5">
+        <v>787</v>
+      </c>
       <c r="J93" s="5"/>
       <c r="K93" s="5"/>
       <c r="L93" s="5">
@@ -11176,7 +11469,7 @@
         <v>17389</v>
       </c>
       <c r="D94" s="5">
-        <f t="shared" si="102"/>
+        <f t="shared" si="115"/>
         <v>12192</v>
       </c>
       <c r="E94" s="5">
@@ -11187,7 +11480,9 @@
         <v>10432</v>
       </c>
       <c r="H94" s="5"/>
-      <c r="I94" s="5"/>
+      <c r="I94" s="5">
+        <v>10351</v>
+      </c>
       <c r="J94" s="5"/>
       <c r="K94" s="5"/>
       <c r="L94" s="5">
@@ -11249,7 +11544,7 @@
         <v>469</v>
       </c>
       <c r="D95" s="5">
-        <f t="shared" si="102"/>
+        <f t="shared" si="115"/>
         <v>531</v>
       </c>
       <c r="E95" s="5">
@@ -11260,7 +11555,9 @@
         <v>3212</v>
       </c>
       <c r="H95" s="5"/>
-      <c r="I95" s="5"/>
+      <c r="I95" s="5">
+        <v>3141</v>
+      </c>
       <c r="J95" s="5"/>
       <c r="K95" s="5"/>
       <c r="L95" s="5">
@@ -11322,7 +11619,7 @@
         <v>944</v>
       </c>
       <c r="D96" s="5">
-        <f t="shared" si="102"/>
+        <f t="shared" si="115"/>
         <v>893</v>
       </c>
       <c r="E96" s="5">
@@ -11333,7 +11630,9 @@
         <v>586</v>
       </c>
       <c r="H96" s="5"/>
-      <c r="I96" s="5"/>
+      <c r="I96" s="5">
+        <v>35</v>
+      </c>
       <c r="J96" s="5"/>
       <c r="K96" s="5"/>
       <c r="L96" s="5">
@@ -11395,7 +11694,7 @@
         <v>430</v>
       </c>
       <c r="D97" s="5">
-        <f t="shared" si="102"/>
+        <f t="shared" si="115"/>
         <v>206</v>
       </c>
       <c r="E97" s="5">
@@ -11406,7 +11705,9 @@
         <v>150</v>
       </c>
       <c r="H97" s="5"/>
-      <c r="I97" s="5"/>
+      <c r="I97" s="5">
+        <v>156</v>
+      </c>
       <c r="J97" s="5"/>
       <c r="K97" s="5"/>
       <c r="L97" s="5">
@@ -11465,63 +11766,69 @@
         <v>76</v>
       </c>
       <c r="C98" s="5">
-        <f t="shared" ref="C98:G98" si="103">SUM(C92:C97)</f>
+        <f t="shared" ref="C98:I98" si="116">SUM(C92:C97)</f>
         <v>57253</v>
       </c>
       <c r="D98" s="5">
-        <f t="shared" si="103"/>
+        <f t="shared" si="116"/>
         <v>50109</v>
       </c>
       <c r="E98" s="5">
-        <f t="shared" si="103"/>
+        <f t="shared" si="116"/>
         <v>46858</v>
       </c>
       <c r="F98" s="5">
-        <f t="shared" si="103"/>
+        <f t="shared" si="116"/>
         <v>0</v>
       </c>
       <c r="G98" s="5">
-        <f t="shared" si="103"/>
+        <f t="shared" si="116"/>
         <v>47053</v>
       </c>
-      <c r="H98" s="5"/>
-      <c r="I98" s="5"/>
+      <c r="H98" s="5">
+        <f t="shared" si="116"/>
+        <v>0</v>
+      </c>
+      <c r="I98" s="5">
+        <f t="shared" si="116"/>
+        <v>45515</v>
+      </c>
       <c r="J98" s="5"/>
       <c r="K98" s="5"/>
       <c r="L98" s="5">
-        <f t="shared" ref="L98:O98" si="104">SUM(L92:L97)</f>
+        <f t="shared" ref="L98:O98" si="117">SUM(L92:L97)</f>
         <v>11584</v>
       </c>
       <c r="M98" s="5">
-        <f t="shared" si="104"/>
+        <f t="shared" si="117"/>
         <v>17477</v>
       </c>
       <c r="N98" s="5">
-        <f t="shared" si="104"/>
+        <f t="shared" si="117"/>
         <v>19511</v>
       </c>
       <c r="O98" s="5">
-        <f t="shared" si="104"/>
+        <f t="shared" si="117"/>
         <v>64468</v>
       </c>
       <c r="P98" s="5">
-        <f t="shared" ref="P98:T98" si="105">SUM(P92:P97)</f>
+        <f t="shared" ref="P98:T98" si="118">SUM(P92:P97)</f>
         <v>64325</v>
       </c>
       <c r="Q98" s="5">
-        <f t="shared" si="105"/>
+        <f t="shared" si="118"/>
         <v>58022</v>
       </c>
       <c r="R98" s="5">
-        <f t="shared" si="105"/>
+        <f t="shared" si="118"/>
         <v>59257</v>
       </c>
       <c r="S98" s="5">
-        <f t="shared" si="105"/>
+        <f t="shared" si="118"/>
         <v>54820</v>
       </c>
       <c r="T98" s="5">
-        <f t="shared" si="105"/>
+        <f t="shared" si="118"/>
         <v>59983</v>
       </c>
       <c r="U98" s="5">
@@ -11559,7 +11866,7 @@
         <v>5029</v>
       </c>
       <c r="D99" s="5">
-        <f t="shared" ref="D99:D104" si="106">U99</f>
+        <f t="shared" ref="D99:D104" si="119">U99</f>
         <v>4324</v>
       </c>
       <c r="E99" s="5">
@@ -11570,7 +11877,9 @@
         <v>3304</v>
       </c>
       <c r="H99" s="5"/>
-      <c r="I99" s="5"/>
+      <c r="I99" s="5">
+        <v>4018</v>
+      </c>
       <c r="J99" s="5"/>
       <c r="K99" s="5"/>
       <c r="L99" s="5">
@@ -11632,7 +11941,7 @@
         <v>905</v>
       </c>
       <c r="D100" s="5">
-        <f t="shared" si="106"/>
+        <f t="shared" si="119"/>
         <v>992</v>
       </c>
       <c r="E100" s="5">
@@ -11643,7 +11952,9 @@
         <v>1172</v>
       </c>
       <c r="H100" s="5"/>
-      <c r="I100" s="5"/>
+      <c r="I100" s="5">
+        <v>1004</v>
+      </c>
       <c r="J100" s="5"/>
       <c r="K100" s="5"/>
       <c r="L100" s="5">
@@ -11705,7 +12016,7 @@
         <v>483</v>
       </c>
       <c r="D101" s="5">
-        <f t="shared" si="106"/>
+        <f t="shared" si="119"/>
         <v>468</v>
       </c>
       <c r="E101" s="5">
@@ -11716,7 +12027,9 @@
         <v>3089</v>
       </c>
       <c r="H101" s="5"/>
-      <c r="I101" s="5"/>
+      <c r="I101" s="5">
+        <v>599</v>
+      </c>
       <c r="J101" s="5"/>
       <c r="K101" s="5"/>
       <c r="L101" s="5">
@@ -11778,7 +12091,7 @@
         <v>9217</v>
       </c>
       <c r="D102" s="5">
-        <f t="shared" si="106"/>
+        <f t="shared" si="119"/>
         <v>9700</v>
       </c>
       <c r="E102" s="5">
@@ -11789,7 +12102,9 @@
         <v>8243</v>
       </c>
       <c r="H102" s="5"/>
-      <c r="I102" s="5"/>
+      <c r="I102" s="5">
+        <v>8576</v>
+      </c>
       <c r="J102" s="5"/>
       <c r="K102" s="5"/>
       <c r="L102" s="5">
@@ -11851,7 +12166,7 @@
         <v>251</v>
       </c>
       <c r="D103" s="5">
-        <f t="shared" si="106"/>
+        <f t="shared" si="119"/>
         <v>189</v>
       </c>
       <c r="E103" s="5">
@@ -11862,7 +12177,9 @@
         <v>188</v>
       </c>
       <c r="H103" s="5"/>
-      <c r="I103" s="5"/>
+      <c r="I103" s="5">
+        <v>81</v>
+      </c>
       <c r="J103" s="5"/>
       <c r="K103" s="5"/>
       <c r="L103" s="5">
@@ -11924,7 +12241,7 @@
         <v>306</v>
       </c>
       <c r="D104" s="5">
-        <f t="shared" si="106"/>
+        <f t="shared" si="119"/>
         <v>0</v>
       </c>
       <c r="E104" s="5">
@@ -11935,7 +12252,9 @@
         <v>0</v>
       </c>
       <c r="H104" s="5"/>
-      <c r="I104" s="5"/>
+      <c r="I104" s="5">
+        <v>0</v>
+      </c>
       <c r="J104" s="5"/>
       <c r="K104" s="5"/>
       <c r="L104" s="5">
@@ -11994,63 +12313,69 @@
         <v>78</v>
       </c>
       <c r="C105" s="5">
-        <f t="shared" ref="C105:G105" si="107">SUM(C99:C104)</f>
+        <f t="shared" ref="C105:I105" si="120">SUM(C99:C104)</f>
         <v>16191</v>
       </c>
       <c r="D105" s="5">
-        <f t="shared" si="107"/>
+        <f t="shared" si="120"/>
         <v>15673</v>
       </c>
       <c r="E105" s="5">
-        <f t="shared" si="107"/>
+        <f t="shared" si="120"/>
         <v>18042</v>
       </c>
       <c r="F105" s="5">
-        <f t="shared" si="107"/>
+        <f t="shared" si="120"/>
         <v>0</v>
       </c>
       <c r="G105" s="5">
-        <f t="shared" si="107"/>
+        <f t="shared" si="120"/>
         <v>15996</v>
       </c>
-      <c r="H105" s="5"/>
-      <c r="I105" s="5"/>
+      <c r="H105" s="5">
+        <f t="shared" si="120"/>
+        <v>0</v>
+      </c>
+      <c r="I105" s="5">
+        <f t="shared" si="120"/>
+        <v>14278</v>
+      </c>
       <c r="J105" s="5"/>
       <c r="K105" s="5"/>
       <c r="L105" s="5">
-        <f t="shared" ref="L105:O105" si="108">SUM(L99:L104)</f>
+        <f t="shared" ref="L105:O105" si="121">SUM(L99:L104)</f>
         <v>8769</v>
       </c>
       <c r="M105" s="5">
-        <f t="shared" si="108"/>
+        <f t="shared" si="121"/>
         <v>9006</v>
       </c>
       <c r="N105" s="5">
-        <f t="shared" si="108"/>
+        <f t="shared" si="121"/>
         <v>11856</v>
       </c>
       <c r="O105" s="5">
-        <f t="shared" si="108"/>
+        <f t="shared" si="121"/>
         <v>15544</v>
       </c>
       <c r="P105" s="5">
-        <f t="shared" ref="P105:T105" si="109">SUM(P99:P104)</f>
+        <f t="shared" ref="P105:T105" si="122">SUM(P99:P104)</f>
         <v>16329</v>
       </c>
       <c r="Q105" s="5">
-        <f t="shared" si="109"/>
+        <f t="shared" si="122"/>
         <v>18823</v>
       </c>
       <c r="R105" s="5">
-        <f t="shared" si="109"/>
+        <f t="shared" si="122"/>
         <v>15478</v>
       </c>
       <c r="S105" s="5">
-        <f t="shared" si="109"/>
+        <f t="shared" si="122"/>
         <v>15144</v>
       </c>
       <c r="T105" s="5">
-        <f t="shared" si="109"/>
+        <f t="shared" si="122"/>
         <v>17853</v>
       </c>
       <c r="U105" s="5">
@@ -12104,56 +12429,62 @@
         <f>G105+G98+G91</f>
         <v>110226</v>
       </c>
-      <c r="H106" s="41"/>
-      <c r="I106" s="5"/>
+      <c r="H106" s="41">
+        <f t="shared" ref="H106:I106" si="123">H105+H98+H91</f>
+        <v>0</v>
+      </c>
+      <c r="I106" s="41">
+        <f t="shared" si="123"/>
+        <v>108388</v>
+      </c>
       <c r="J106" s="5"/>
       <c r="K106" s="5"/>
       <c r="L106" s="41">
-        <f t="shared" ref="L106:W106" si="110">L105+L98+L91</f>
+        <f t="shared" ref="L106:W106" si="124">L105+L98+L91</f>
         <v>26167</v>
       </c>
       <c r="M106" s="41">
-        <f t="shared" si="110"/>
+        <f t="shared" si="124"/>
         <v>31515</v>
       </c>
       <c r="N106" s="41">
-        <f t="shared" si="110"/>
+        <f t="shared" si="124"/>
         <v>39773</v>
       </c>
       <c r="O106" s="41">
-        <f t="shared" si="110"/>
+        <f t="shared" si="124"/>
         <v>141038</v>
       </c>
       <c r="P106" s="41">
-        <f t="shared" si="110"/>
+        <f t="shared" si="124"/>
         <v>146342</v>
       </c>
       <c r="Q106" s="41">
-        <f t="shared" si="110"/>
+        <f t="shared" si="124"/>
         <v>141005</v>
       </c>
       <c r="R106" s="41">
-        <f t="shared" si="110"/>
+        <f t="shared" si="124"/>
         <v>137690</v>
       </c>
       <c r="S106" s="41">
-        <f t="shared" si="110"/>
+        <f t="shared" si="124"/>
         <v>137365</v>
       </c>
       <c r="T106" s="41">
-        <f t="shared" si="110"/>
+        <f t="shared" si="124"/>
         <v>153546</v>
       </c>
       <c r="U106" s="41">
-        <f t="shared" si="110"/>
+        <f t="shared" si="124"/>
         <v>118716</v>
       </c>
       <c r="V106" s="41">
-        <f t="shared" si="110"/>
+        <f t="shared" si="124"/>
         <v>118899</v>
       </c>
       <c r="W106" s="41">
-        <f t="shared" si="110"/>
+        <f t="shared" si="124"/>
         <v>109290</v>
       </c>
       <c r="X106" s="5"/>
@@ -12235,51 +12566,53 @@
         <v>5069</v>
       </c>
       <c r="H108" s="5"/>
-      <c r="I108" s="5"/>
+      <c r="I108" s="5">
+        <v>4266</v>
+      </c>
       <c r="J108" s="5"/>
       <c r="K108" s="5"/>
       <c r="L108" s="5">
-        <f t="shared" ref="L108:V108" si="111">L38</f>
+        <f t="shared" ref="L108:V108" si="125">L38</f>
         <v>4546</v>
       </c>
       <c r="M108" s="5">
-        <f t="shared" si="111"/>
+        <f t="shared" si="125"/>
         <v>4557</v>
       </c>
       <c r="N108" s="5">
-        <f t="shared" si="111"/>
+        <f t="shared" si="125"/>
         <v>4655</v>
       </c>
       <c r="O108" s="5">
-        <f t="shared" si="111"/>
+        <f t="shared" si="125"/>
         <v>6476</v>
       </c>
       <c r="P108" s="5">
-        <f t="shared" si="111"/>
+        <f t="shared" si="125"/>
         <v>9313</v>
       </c>
       <c r="Q108" s="5">
-        <f t="shared" si="111"/>
+        <f t="shared" si="125"/>
         <v>9016</v>
       </c>
       <c r="R108" s="5">
-        <f t="shared" si="111"/>
+        <f t="shared" si="125"/>
         <v>9962</v>
       </c>
       <c r="S108" s="5">
-        <f t="shared" si="111"/>
+        <f t="shared" si="125"/>
         <v>10234</v>
       </c>
       <c r="T108" s="5">
-        <f t="shared" si="111"/>
+        <f t="shared" si="125"/>
         <v>10523</v>
       </c>
       <c r="U108" s="5">
-        <f t="shared" si="111"/>
+        <f t="shared" si="125"/>
         <v>-15751</v>
       </c>
       <c r="V108" s="5">
-        <f t="shared" si="111"/>
+        <f t="shared" si="125"/>
         <v>2736</v>
       </c>
       <c r="W108" s="5">
@@ -12308,7 +12641,7 @@
         <v>480</v>
       </c>
       <c r="D109" s="5">
-        <f>U109-C109</f>
+        <f t="shared" ref="D109:D116" si="126">U109-C109</f>
         <v>28134</v>
       </c>
       <c r="E109" s="5">
@@ -12319,7 +12652,9 @@
         <v>1192</v>
       </c>
       <c r="H109" s="5"/>
-      <c r="I109" s="5"/>
+      <c r="I109" s="5">
+        <v>1364</v>
+      </c>
       <c r="J109" s="5"/>
       <c r="K109" s="5"/>
       <c r="L109" s="5">
@@ -12381,7 +12716,7 @@
         <v>-357</v>
       </c>
       <c r="D110" s="5">
-        <f>U110-C110</f>
+        <f t="shared" si="126"/>
         <v>622</v>
       </c>
       <c r="E110" s="5">
@@ -12392,7 +12727,9 @@
         <v>-696</v>
       </c>
       <c r="H110" s="5"/>
-      <c r="I110" s="5"/>
+      <c r="I110" s="5">
+        <v>-448</v>
+      </c>
       <c r="J110" s="5"/>
       <c r="K110" s="5"/>
       <c r="L110" s="5">
@@ -12454,7 +12791,7 @@
         <v>-425</v>
       </c>
       <c r="D111" s="5">
-        <f>U111-C111</f>
+        <f t="shared" si="126"/>
         <v>-62</v>
       </c>
       <c r="E111" s="5">
@@ -12465,7 +12802,9 @@
         <v>-1</v>
       </c>
       <c r="H111" s="5"/>
-      <c r="I111" s="5"/>
+      <c r="I111" s="5">
+        <v>-102</v>
+      </c>
       <c r="J111" s="5"/>
       <c r="K111" s="5"/>
       <c r="L111" s="5">
@@ -12527,7 +12866,7 @@
         <v>-897</v>
       </c>
       <c r="D112" s="5">
-        <f>U112-C112</f>
+        <f t="shared" si="126"/>
         <v>610</v>
       </c>
       <c r="E112" s="5">
@@ -12538,7 +12877,9 @@
         <v>-633</v>
       </c>
       <c r="H112" s="5"/>
-      <c r="I112" s="5"/>
+      <c r="I112" s="5">
+        <v>-571</v>
+      </c>
       <c r="J112" s="5"/>
       <c r="K112" s="5"/>
       <c r="L112" s="5">
@@ -12600,7 +12941,7 @@
         <v>347</v>
       </c>
       <c r="D113" s="5">
-        <f>U113-C113</f>
+        <f t="shared" si="126"/>
         <v>293</v>
       </c>
       <c r="E113" s="5">
@@ -12611,7 +12952,9 @@
         <v>-565</v>
       </c>
       <c r="H113" s="5"/>
-      <c r="I113" s="5"/>
+      <c r="I113" s="5">
+        <v>-160</v>
+      </c>
       <c r="J113" s="5"/>
       <c r="K113" s="5"/>
       <c r="L113" s="5">
@@ -12673,7 +13016,7 @@
         <v>-55</v>
       </c>
       <c r="D114" s="5">
-        <f>U114-C114</f>
+        <f t="shared" si="126"/>
         <v>-56</v>
       </c>
       <c r="E114" s="5">
@@ -12684,7 +13027,9 @@
         <v>-27</v>
       </c>
       <c r="H114" s="5"/>
-      <c r="I114" s="5"/>
+      <c r="I114" s="5">
+        <v>-15</v>
+      </c>
       <c r="J114" s="5"/>
       <c r="K114" s="5"/>
       <c r="L114" s="5">
@@ -12746,7 +13091,7 @@
         <v>-535</v>
       </c>
       <c r="D115" s="5">
-        <f>U115-C115</f>
+        <f t="shared" si="126"/>
         <v>46</v>
       </c>
       <c r="E115" s="5">
@@ -12757,7 +13102,9 @@
         <v>-634</v>
       </c>
       <c r="H115" s="5"/>
-      <c r="I115" s="5"/>
+      <c r="I115" s="5">
+        <v>-70</v>
+      </c>
       <c r="J115" s="5"/>
       <c r="K115" s="5"/>
       <c r="L115" s="5">
@@ -12819,7 +13166,7 @@
         <v>0</v>
       </c>
       <c r="D116" s="5">
-        <f>U116-C116</f>
+        <f t="shared" si="126"/>
         <v>0</v>
       </c>
       <c r="E116" s="5">
@@ -12830,7 +13177,9 @@
         <v>12</v>
       </c>
       <c r="H116" s="5"/>
-      <c r="I116" s="5"/>
+      <c r="I116" s="5">
+        <v>223</v>
+      </c>
       <c r="J116" s="5"/>
       <c r="K116" s="5"/>
       <c r="L116" s="5">
@@ -12890,43 +13239,49 @@
         <v>88</v>
       </c>
       <c r="C117" s="41">
-        <f t="shared" ref="C117:G117" si="112">SUM(C110:C116)</f>
+        <f t="shared" ref="C117:I117" si="127">SUM(C110:C116)</f>
         <v>-1922</v>
       </c>
       <c r="D117" s="41">
-        <f t="shared" si="112"/>
+        <f t="shared" si="127"/>
         <v>1453</v>
       </c>
       <c r="E117" s="41">
-        <f t="shared" si="112"/>
+        <f t="shared" si="127"/>
         <v>-1740</v>
       </c>
       <c r="F117" s="41">
-        <f t="shared" si="112"/>
+        <f t="shared" si="127"/>
         <v>0</v>
       </c>
       <c r="G117" s="41">
-        <f t="shared" si="112"/>
+        <f t="shared" si="127"/>
         <v>-2544</v>
       </c>
-      <c r="H117" s="41"/>
-      <c r="I117" s="5"/>
+      <c r="H117" s="41">
+        <f t="shared" si="127"/>
+        <v>0</v>
+      </c>
+      <c r="I117" s="41">
+        <f>SUM(I110:I116)</f>
+        <v>-1143</v>
+      </c>
       <c r="J117" s="5"/>
       <c r="K117" s="5"/>
       <c r="L117" s="41">
-        <f t="shared" ref="L117:O117" si="113">SUM(L110:L116)</f>
+        <f t="shared" ref="L117:O117" si="128">SUM(L110:L116)</f>
         <v>-484</v>
       </c>
       <c r="M117" s="41">
-        <f t="shared" si="113"/>
+        <f t="shared" si="128"/>
         <v>469</v>
       </c>
       <c r="N117" s="41">
-        <f t="shared" si="113"/>
+        <f t="shared" si="128"/>
         <v>-369</v>
       </c>
       <c r="O117" s="41">
-        <f t="shared" si="113"/>
+        <f t="shared" si="128"/>
         <v>-1345</v>
       </c>
       <c r="P117" s="41">
@@ -12938,27 +13293,27 @@
         <v>314</v>
       </c>
       <c r="R117" s="41">
-        <f t="shared" ref="R117:W117" si="114">SUM(R110:R116)</f>
+        <f t="shared" ref="R117:W117" si="129">SUM(R110:R116)</f>
         <v>109</v>
       </c>
       <c r="S117" s="41">
-        <f t="shared" si="114"/>
+        <f t="shared" si="129"/>
         <v>-62</v>
       </c>
       <c r="T117" s="41">
-        <f t="shared" si="114"/>
+        <f t="shared" si="129"/>
         <v>103</v>
       </c>
       <c r="U117" s="41">
-        <f t="shared" si="114"/>
+        <f t="shared" si="129"/>
         <v>-469</v>
       </c>
       <c r="V117" s="41">
-        <f t="shared" si="114"/>
+        <f t="shared" si="129"/>
         <v>5776</v>
       </c>
       <c r="W117" s="41">
-        <f t="shared" si="114"/>
+        <f t="shared" si="129"/>
         <v>-3909</v>
       </c>
       <c r="X117" s="5"/>
@@ -12995,7 +13350,9 @@
         <v>0</v>
       </c>
       <c r="H118" s="5"/>
-      <c r="I118" s="5"/>
+      <c r="I118" s="5">
+        <v>0</v>
+      </c>
       <c r="J118" s="5"/>
       <c r="K118" s="5"/>
       <c r="L118" s="5">
@@ -13068,7 +13425,9 @@
         <v>168</v>
       </c>
       <c r="H119" s="5"/>
-      <c r="I119" s="5"/>
+      <c r="I119" s="5">
+        <v>139</v>
+      </c>
       <c r="J119" s="5"/>
       <c r="K119" s="5"/>
       <c r="L119" s="5">
@@ -13141,7 +13500,9 @@
         <v>-1576</v>
       </c>
       <c r="H120" s="5"/>
-      <c r="I120" s="5"/>
+      <c r="I120" s="5">
+        <v>-1224</v>
+      </c>
       <c r="J120" s="5"/>
       <c r="K120" s="5"/>
       <c r="L120" s="5">
@@ -13200,43 +13561,49 @@
         <v>89</v>
       </c>
       <c r="C121" s="41">
-        <f t="shared" ref="C121:G121" si="115">C108+C109+C117+C118+C119+C120</f>
+        <f t="shared" ref="C121:I121" si="130">C108+C109+C117+C118+C119+C120</f>
         <v>3375</v>
       </c>
       <c r="D121" s="41">
-        <f t="shared" si="115"/>
+        <f t="shared" si="130"/>
         <v>7339</v>
       </c>
       <c r="E121" s="41">
-        <f t="shared" si="115"/>
+        <f t="shared" si="130"/>
         <v>3165</v>
       </c>
       <c r="F121" s="41">
-        <f t="shared" si="115"/>
+        <f t="shared" si="130"/>
         <v>-1522</v>
       </c>
       <c r="G121" s="41">
-        <f t="shared" si="115"/>
+        <f t="shared" si="130"/>
         <v>2309</v>
       </c>
-      <c r="H121" s="41"/>
-      <c r="I121" s="5"/>
+      <c r="H121" s="41">
+        <f t="shared" si="130"/>
+        <v>0</v>
+      </c>
+      <c r="I121" s="41">
+        <f t="shared" si="130"/>
+        <v>3402</v>
+      </c>
       <c r="J121" s="5"/>
       <c r="K121" s="5"/>
       <c r="L121" s="41">
-        <f t="shared" ref="L121:O121" si="116">L108+L109+L117+L118+L119+L120</f>
+        <f t="shared" ref="L121:O121" si="131">L108+L109+L117+L118+L119+L120</f>
         <v>3716</v>
       </c>
       <c r="M121" s="41">
-        <f t="shared" si="116"/>
+        <f t="shared" si="131"/>
         <v>4720</v>
       </c>
       <c r="N121" s="41">
-        <f t="shared" si="116"/>
+        <f t="shared" si="131"/>
         <v>4610</v>
       </c>
       <c r="O121" s="41">
-        <f t="shared" si="116"/>
+        <f t="shared" si="131"/>
         <v>5347</v>
       </c>
       <c r="P121" s="41">
@@ -13244,19 +13611,19 @@
         <v>10295</v>
       </c>
       <c r="Q121" s="41">
-        <f t="shared" ref="Q121:T121" si="117">Q108+Q109+Q117+Q118+Q119+Q120</f>
+        <f t="shared" ref="Q121:T121" si="132">Q108+Q109+Q117+Q118+Q119+Q120</f>
         <v>8996</v>
       </c>
       <c r="R121" s="41">
-        <f t="shared" si="117"/>
+        <f t="shared" si="132"/>
         <v>9786</v>
       </c>
       <c r="S121" s="41">
-        <f t="shared" si="117"/>
+        <f t="shared" si="132"/>
         <v>9717</v>
       </c>
       <c r="T121" s="41">
-        <f t="shared" si="117"/>
+        <f t="shared" si="132"/>
         <v>10394</v>
       </c>
       <c r="U121" s="41">
@@ -13294,7 +13661,7 @@
         <v>78</v>
       </c>
       <c r="D122" s="5">
-        <f>U122-C122</f>
+        <f t="shared" ref="D122:D130" si="133">U122-C122</f>
         <v>67</v>
       </c>
       <c r="E122" s="5">
@@ -13305,7 +13672,10 @@
         <v>85</v>
       </c>
       <c r="H122" s="5"/>
-      <c r="I122" s="5"/>
+      <c r="I122" s="5">
+        <f>83+2</f>
+        <v>85</v>
+      </c>
       <c r="J122" s="5"/>
       <c r="K122" s="5"/>
       <c r="L122" s="5">
@@ -13367,7 +13737,7 @@
         <v>-110</v>
       </c>
       <c r="D123" s="5">
-        <f>U123-C123</f>
+        <f t="shared" si="133"/>
         <v>-350</v>
       </c>
       <c r="E123" s="5">
@@ -13378,7 +13748,9 @@
         <v>-103</v>
       </c>
       <c r="H123" s="5"/>
-      <c r="I123" s="5"/>
+      <c r="I123" s="5">
+        <v>-134</v>
+      </c>
       <c r="J123" s="5"/>
       <c r="K123" s="5"/>
       <c r="L123" s="5">
@@ -13440,7 +13812,7 @@
         <v>22</v>
       </c>
       <c r="D124" s="5">
-        <f>U124-C124</f>
+        <f t="shared" si="133"/>
         <v>32</v>
       </c>
       <c r="E124" s="5">
@@ -13451,7 +13823,9 @@
         <v>21</v>
       </c>
       <c r="H124" s="5"/>
-      <c r="I124" s="5"/>
+      <c r="I124" s="5">
+        <v>8</v>
+      </c>
       <c r="J124" s="5"/>
       <c r="K124" s="5"/>
       <c r="L124" s="5">
@@ -13513,7 +13887,7 @@
         <v>-21</v>
       </c>
       <c r="D125" s="5">
-        <f>U125-C125</f>
+        <f t="shared" si="133"/>
         <v>-120</v>
       </c>
       <c r="E125" s="5">
@@ -13524,7 +13898,9 @@
         <v>-42</v>
       </c>
       <c r="H125" s="5"/>
-      <c r="I125" s="5"/>
+      <c r="I125" s="5">
+        <v>-34</v>
+      </c>
       <c r="J125" s="5"/>
       <c r="K125" s="5"/>
       <c r="L125" s="5">
@@ -13586,7 +13962,7 @@
         <v>0</v>
       </c>
       <c r="D126" s="5">
-        <f>U126-C126</f>
+        <f t="shared" si="133"/>
         <v>27</v>
       </c>
       <c r="E126" s="5">
@@ -13597,7 +13973,9 @@
         <v>8</v>
       </c>
       <c r="H126" s="5"/>
-      <c r="I126" s="5"/>
+      <c r="I126" s="5">
+        <v>2</v>
+      </c>
       <c r="J126" s="5"/>
       <c r="K126" s="5"/>
       <c r="L126" s="5">
@@ -13659,7 +14037,7 @@
         <v>-433</v>
       </c>
       <c r="D127" s="5">
-        <f>U127-C127</f>
+        <f t="shared" si="133"/>
         <v>-15</v>
       </c>
       <c r="E127" s="5">
@@ -13670,7 +14048,9 @@
         <v>-59</v>
       </c>
       <c r="H127" s="5"/>
-      <c r="I127" s="5"/>
+      <c r="I127" s="5">
+        <v>-27</v>
+      </c>
       <c r="J127" s="5"/>
       <c r="K127" s="5"/>
       <c r="L127" s="5">
@@ -13732,7 +14112,7 @@
         <v>543</v>
       </c>
       <c r="D128" s="5">
-        <f>U128-C128</f>
+        <f t="shared" si="133"/>
         <v>-138</v>
       </c>
       <c r="E128" s="5">
@@ -13743,7 +14123,9 @@
         <v>73</v>
       </c>
       <c r="H128" s="5"/>
-      <c r="I128" s="5"/>
+      <c r="I128" s="5">
+        <v>37</v>
+      </c>
       <c r="J128" s="5"/>
       <c r="K128" s="5"/>
       <c r="L128" s="5">
@@ -13805,7 +14187,7 @@
         <v>-38</v>
       </c>
       <c r="D129" s="5">
-        <f>U129-C129</f>
+        <f t="shared" si="133"/>
         <v>1</v>
       </c>
       <c r="E129" s="5">
@@ -13816,7 +14198,9 @@
         <v>-23</v>
       </c>
       <c r="H129" s="5"/>
-      <c r="I129" s="5"/>
+      <c r="I129" s="5">
+        <v>-45</v>
+      </c>
       <c r="J129" s="5"/>
       <c r="K129" s="5"/>
       <c r="L129" s="5">
@@ -13879,7 +14263,7 @@
         <v>0</v>
       </c>
       <c r="D130" s="5">
-        <f>U130-C130</f>
+        <f t="shared" si="133"/>
         <v>159</v>
       </c>
       <c r="E130" s="5">
@@ -13890,7 +14274,9 @@
         <v>1052</v>
       </c>
       <c r="H130" s="5"/>
-      <c r="I130" s="5"/>
+      <c r="I130" s="5">
+        <v>-192</v>
+      </c>
       <c r="J130" s="5"/>
       <c r="K130" s="5"/>
       <c r="L130" s="5">
@@ -13950,63 +14336,69 @@
         <v>99</v>
       </c>
       <c r="C131" s="41">
-        <f t="shared" ref="C131:G131" si="118">SUM(C122:C130)</f>
+        <f t="shared" ref="C131:I131" si="134">SUM(C122:C130)</f>
         <v>41</v>
       </c>
       <c r="D131" s="41">
-        <f t="shared" si="118"/>
+        <f t="shared" si="134"/>
         <v>-337</v>
       </c>
       <c r="E131" s="41">
-        <f t="shared" si="118"/>
+        <f t="shared" si="134"/>
         <v>1433</v>
       </c>
       <c r="F131" s="41">
-        <f t="shared" si="118"/>
+        <f t="shared" si="134"/>
         <v>0</v>
       </c>
       <c r="G131" s="41">
-        <f t="shared" si="118"/>
+        <f t="shared" si="134"/>
         <v>1012</v>
       </c>
-      <c r="H131" s="41"/>
-      <c r="I131" s="5"/>
+      <c r="H131" s="41">
+        <f t="shared" si="134"/>
+        <v>0</v>
+      </c>
+      <c r="I131" s="41">
+        <f t="shared" si="134"/>
+        <v>-300</v>
+      </c>
       <c r="J131" s="5"/>
       <c r="K131" s="5"/>
       <c r="L131" s="41">
-        <f t="shared" ref="L131:O131" si="119">SUM(L122:L130)</f>
+        <f t="shared" ref="L131:O131" si="135">SUM(L122:L130)</f>
         <v>-470</v>
       </c>
       <c r="M131" s="41">
-        <f t="shared" si="119"/>
+        <f t="shared" si="135"/>
         <v>-3946</v>
       </c>
       <c r="N131" s="41">
-        <f t="shared" si="119"/>
+        <f t="shared" si="135"/>
         <v>-640</v>
       </c>
       <c r="O131" s="41">
-        <f t="shared" si="119"/>
+        <f t="shared" si="135"/>
         <v>-18544</v>
       </c>
       <c r="P131" s="41">
-        <f t="shared" ref="P131:T131" si="120">SUM(P122:P130)</f>
+        <f t="shared" ref="P131:T131" si="136">SUM(P122:P130)</f>
         <v>-1021</v>
       </c>
       <c r="Q131" s="41">
-        <f t="shared" si="120"/>
+        <f t="shared" si="136"/>
         <v>-639</v>
       </c>
       <c r="R131" s="41">
-        <f t="shared" si="120"/>
+        <f t="shared" si="136"/>
         <v>-783</v>
       </c>
       <c r="S131" s="41">
-        <f t="shared" si="120"/>
+        <f t="shared" si="136"/>
         <v>-1140</v>
       </c>
       <c r="T131" s="41">
-        <f t="shared" si="120"/>
+        <f t="shared" si="136"/>
         <v>-705</v>
       </c>
       <c r="U131" s="41">
@@ -14044,7 +14436,7 @@
         <v>-855</v>
       </c>
       <c r="D132" s="5">
-        <f>U132-C132</f>
+        <f t="shared" ref="D132:D139" si="137">U132-C132</f>
         <v>-827</v>
       </c>
       <c r="E132" s="5">
@@ -14055,7 +14447,9 @@
         <v>-879</v>
       </c>
       <c r="H132" s="5"/>
-      <c r="I132" s="5"/>
+      <c r="I132" s="5">
+        <v>-905</v>
+      </c>
       <c r="J132" s="5"/>
       <c r="K132" s="5"/>
       <c r="L132" s="5">
@@ -14117,7 +14511,7 @@
         <v>-14</v>
       </c>
       <c r="D133" s="5">
-        <f>U133-C133</f>
+        <f t="shared" si="137"/>
         <v>-16</v>
       </c>
       <c r="E133" s="5">
@@ -14128,7 +14522,9 @@
         <v>-21</v>
       </c>
       <c r="H133" s="5"/>
-      <c r="I133" s="5"/>
+      <c r="I133" s="5">
+        <v>-19</v>
+      </c>
       <c r="J133" s="5"/>
       <c r="K133" s="5"/>
       <c r="L133" s="5">
@@ -14190,7 +14586,7 @@
         <v>-80</v>
       </c>
       <c r="D134" s="5">
-        <f>U134-C134</f>
+        <f t="shared" si="137"/>
         <v>-82</v>
       </c>
       <c r="E134" s="5">
@@ -14201,7 +14597,9 @@
         <v>-95</v>
       </c>
       <c r="H134" s="5"/>
-      <c r="I134" s="5"/>
+      <c r="I134" s="5">
+        <v>-91</v>
+      </c>
       <c r="J134" s="5"/>
       <c r="K134" s="5"/>
       <c r="L134" s="5">
@@ -14263,7 +14661,7 @@
         <v>2054</v>
       </c>
       <c r="D135" s="5">
-        <f>U135-C135</f>
+        <f t="shared" si="137"/>
         <v>3080</v>
       </c>
       <c r="E135" s="5">
@@ -14274,7 +14672,9 @@
         <v>3552</v>
       </c>
       <c r="H135" s="5"/>
-      <c r="I135" s="5"/>
+      <c r="I135" s="5">
+        <v>1055</v>
+      </c>
       <c r="J135" s="5"/>
       <c r="K135" s="5"/>
       <c r="L135" s="5">
@@ -14336,7 +14736,7 @@
         <v>-1050</v>
       </c>
       <c r="D136" s="5">
-        <f>U136-C136</f>
+        <f t="shared" si="137"/>
         <v>-5719</v>
       </c>
       <c r="E136" s="5">
@@ -14347,7 +14747,9 @@
         <v>-3047</v>
       </c>
       <c r="H136" s="5"/>
-      <c r="I136" s="5"/>
+      <c r="I136" s="5">
+        <v>-1206</v>
+      </c>
       <c r="J136" s="5"/>
       <c r="K136" s="5"/>
       <c r="L136" s="5">
@@ -14409,7 +14811,7 @@
         <v>-429</v>
       </c>
       <c r="D137" s="5">
-        <f>U137-C137</f>
+        <f t="shared" si="137"/>
         <v>-51</v>
       </c>
       <c r="E137" s="5">
@@ -14420,7 +14822,9 @@
         <v>-445</v>
       </c>
       <c r="H137" s="5"/>
-      <c r="I137" s="5"/>
+      <c r="I137" s="5">
+        <v>-39</v>
+      </c>
       <c r="J137" s="5"/>
       <c r="K137" s="5"/>
       <c r="L137" s="5">
@@ -14482,7 +14886,7 @@
         <v>0</v>
       </c>
       <c r="D138" s="5">
-        <f>U138-C138</f>
+        <f t="shared" si="137"/>
         <v>0</v>
       </c>
       <c r="E138" s="5">
@@ -14493,7 +14897,9 @@
         <v>-450</v>
       </c>
       <c r="H138" s="5"/>
-      <c r="I138" s="5"/>
+      <c r="I138" s="5">
+        <v>-649</v>
+      </c>
       <c r="J138" s="5"/>
       <c r="K138" s="5"/>
       <c r="L138" s="5">
@@ -14555,7 +14961,7 @@
         <v>-110</v>
       </c>
       <c r="D139" s="5">
-        <f>U139-C139</f>
+        <f t="shared" si="137"/>
         <v>0</v>
       </c>
       <c r="E139" s="5">
@@ -14566,7 +14972,9 @@
         <v>-61</v>
       </c>
       <c r="H139" s="5"/>
-      <c r="I139" s="5"/>
+      <c r="I139" s="5">
+        <v>-102</v>
+      </c>
       <c r="J139" s="5"/>
       <c r="K139" s="5"/>
       <c r="L139" s="5">
@@ -14638,7 +15046,9 @@
         <v>0</v>
       </c>
       <c r="H140" s="5"/>
-      <c r="I140" s="5"/>
+      <c r="I140" s="5">
+        <v>-6</v>
+      </c>
       <c r="J140" s="5"/>
       <c r="K140" s="5"/>
       <c r="L140" s="5">
@@ -14674,7 +15084,7 @@
       <c r="V140" s="5">
         <v>0</v>
       </c>
-      <c r="W140" s="102">
+      <c r="W140" s="101">
         <f>1050-883</f>
         <v>167</v>
       </c>
@@ -14711,7 +15121,9 @@
         <v>0</v>
       </c>
       <c r="H141" s="5"/>
-      <c r="I141" s="5"/>
+      <c r="I141" s="5">
+        <v>0</v>
+      </c>
       <c r="J141" s="5"/>
       <c r="K141" s="5"/>
       <c r="L141" s="5">
@@ -14784,7 +15196,9 @@
         <v>-2609</v>
       </c>
       <c r="H142" s="5"/>
-      <c r="I142" s="5"/>
+      <c r="I142" s="5">
+        <v>-2634</v>
+      </c>
       <c r="J142" s="5"/>
       <c r="K142" s="5"/>
       <c r="L142" s="5">
@@ -14857,7 +15271,9 @@
         <v>0</v>
       </c>
       <c r="H143" s="5"/>
-      <c r="I143" s="5"/>
+      <c r="I143" s="5">
+        <v>0</v>
+      </c>
       <c r="J143" s="5"/>
       <c r="K143" s="5"/>
       <c r="L143" s="5">
@@ -14930,7 +15346,9 @@
         <v>-63</v>
       </c>
       <c r="H144" s="5"/>
-      <c r="I144" s="5"/>
+      <c r="I144" s="5">
+        <v>-70</v>
+      </c>
       <c r="J144" s="5"/>
       <c r="K144" s="5"/>
       <c r="L144" s="5">
@@ -15003,7 +15421,9 @@
         <v>1</v>
       </c>
       <c r="H145" s="5"/>
-      <c r="I145" s="5"/>
+      <c r="I145" s="5">
+        <v>3</v>
+      </c>
       <c r="J145" s="5"/>
       <c r="K145" s="5"/>
       <c r="L145" s="5">
@@ -15065,51 +15485,57 @@
         <v>110</v>
       </c>
       <c r="C146" s="41">
-        <f t="shared" ref="C146:G146" si="121">SUM(C132:C145)</f>
+        <f t="shared" ref="C146:I146" si="138">SUM(C132:C145)</f>
         <v>-3023</v>
       </c>
       <c r="D146" s="41">
-        <f t="shared" si="121"/>
+        <f t="shared" si="138"/>
         <v>-6232</v>
       </c>
       <c r="E146" s="41">
-        <f t="shared" si="121"/>
+        <f t="shared" si="138"/>
         <v>-3358</v>
       </c>
       <c r="F146" s="41">
-        <f t="shared" si="121"/>
+        <f t="shared" si="138"/>
         <v>0</v>
       </c>
       <c r="G146" s="41">
-        <f t="shared" si="121"/>
+        <f t="shared" si="138"/>
         <v>-4117</v>
       </c>
-      <c r="H146" s="41"/>
-      <c r="I146" s="5"/>
+      <c r="H146" s="41">
+        <f t="shared" si="138"/>
+        <v>0</v>
+      </c>
+      <c r="I146" s="41">
+        <f t="shared" si="138"/>
+        <v>-4663</v>
+      </c>
       <c r="J146" s="5"/>
       <c r="K146" s="5"/>
       <c r="L146" s="41">
-        <f t="shared" ref="L146:O146" si="122">SUM(L132:L145)</f>
+        <f t="shared" ref="L146:O146" si="139">SUM(L132:L145)</f>
         <v>-3467</v>
       </c>
       <c r="M146" s="41">
-        <f t="shared" si="122"/>
+        <f t="shared" si="139"/>
         <v>-219</v>
       </c>
       <c r="N146" s="41">
-        <f t="shared" si="122"/>
+        <f t="shared" si="139"/>
         <v>-4229</v>
       </c>
       <c r="O146" s="41">
-        <f t="shared" si="122"/>
+        <f t="shared" si="139"/>
         <v>14759</v>
       </c>
       <c r="P146" s="41">
-        <f t="shared" ref="P146:T146" si="123">SUM(P132:P145)</f>
+        <f t="shared" ref="P146:T146" si="140">SUM(P132:P145)</f>
         <v>-9630</v>
       </c>
       <c r="Q146" s="41">
-        <f t="shared" si="123"/>
+        <f t="shared" si="140"/>
         <v>-8593</v>
       </c>
       <c r="R146" s="41">
@@ -15117,11 +15543,11 @@
         <v>-7897</v>
       </c>
       <c r="S146" s="41">
-        <f t="shared" si="123"/>
+        <f t="shared" si="140"/>
         <v>-8749</v>
       </c>
       <c r="T146" s="41">
-        <f t="shared" si="123"/>
+        <f t="shared" si="140"/>
         <v>-8878</v>
       </c>
       <c r="U146" s="41">
@@ -15206,8 +15632,12 @@
       <c r="G148" s="5">
         <v>0</v>
       </c>
-      <c r="H148" s="5"/>
-      <c r="I148" s="5"/>
+      <c r="H148" s="5">
+        <v>0</v>
+      </c>
+      <c r="I148" s="5">
+        <v>208</v>
+      </c>
       <c r="J148" s="5"/>
       <c r="K148" s="5"/>
       <c r="L148" s="5">
@@ -15280,7 +15710,9 @@
         <v>-144</v>
       </c>
       <c r="H149" s="5"/>
-      <c r="I149" s="5"/>
+      <c r="I149" s="5">
+        <v>34</v>
+      </c>
       <c r="J149" s="5"/>
       <c r="K149" s="5"/>
       <c r="L149" s="5">
@@ -15339,63 +15771,69 @@
         <v>113</v>
       </c>
       <c r="C150" s="41">
-        <f t="shared" ref="C150:G150" si="124">SUM(C148:C149,C146,C131,C121)</f>
+        <f t="shared" ref="C150:I150" si="141">SUM(C148:C149,C146,C131,C121)</f>
         <v>226</v>
       </c>
       <c r="D150" s="41">
-        <f t="shared" si="124"/>
+        <f t="shared" si="141"/>
         <v>1013</v>
       </c>
       <c r="E150" s="41">
-        <f t="shared" si="124"/>
+        <f t="shared" si="141"/>
         <v>1177</v>
       </c>
       <c r="F150" s="41">
-        <f t="shared" si="124"/>
+        <f t="shared" si="141"/>
         <v>-1522</v>
       </c>
       <c r="G150" s="41">
-        <f t="shared" si="124"/>
+        <f t="shared" si="141"/>
         <v>-940</v>
       </c>
-      <c r="H150" s="41"/>
-      <c r="I150" s="5"/>
+      <c r="H150" s="41">
+        <f t="shared" si="141"/>
+        <v>0</v>
+      </c>
+      <c r="I150" s="41">
+        <f t="shared" si="141"/>
+        <v>-1319</v>
+      </c>
       <c r="J150" s="5"/>
       <c r="K150" s="5"/>
       <c r="L150" s="41">
-        <f t="shared" ref="L150:T150" si="125">SUM(L148:L149,L146,L131,L121)</f>
+        <f t="shared" ref="L150:T150" si="142">SUM(L148:L149,L146,L131,L121)</f>
         <v>-284</v>
       </c>
       <c r="M150" s="41">
-        <f t="shared" si="125"/>
+        <f t="shared" si="142"/>
         <v>283</v>
       </c>
       <c r="N150" s="41">
-        <f t="shared" si="125"/>
+        <f t="shared" si="142"/>
         <v>-79</v>
       </c>
       <c r="O150" s="41">
-        <f t="shared" si="125"/>
+        <f t="shared" si="142"/>
         <v>1171</v>
       </c>
       <c r="P150" s="41">
-        <f t="shared" si="125"/>
+        <f t="shared" si="142"/>
         <v>-494</v>
       </c>
       <c r="Q150" s="41">
-        <f t="shared" si="125"/>
+        <f t="shared" si="142"/>
         <v>-293</v>
       </c>
       <c r="R150" s="41">
-        <f t="shared" si="125"/>
+        <f t="shared" si="142"/>
         <v>853</v>
       </c>
       <c r="S150" s="41">
-        <f t="shared" si="125"/>
+        <f t="shared" si="142"/>
         <v>-425</v>
       </c>
       <c r="T150" s="41">
-        <f t="shared" si="125"/>
+        <f t="shared" si="142"/>
         <v>874</v>
       </c>
       <c r="U150" s="41">
@@ -15444,43 +15882,45 @@
         <v>5104</v>
       </c>
       <c r="H151" s="5"/>
-      <c r="I151" s="5"/>
+      <c r="I151" s="5">
+        <v>3787</v>
+      </c>
       <c r="J151" s="5"/>
       <c r="K151" s="5"/>
       <c r="L151" s="5">
-        <f t="shared" ref="L151:T151" si="126">L152-L150</f>
+        <f t="shared" ref="L151:T151" si="143">L152-L150</f>
         <v>1652</v>
       </c>
       <c r="M151" s="5">
-        <f t="shared" si="126"/>
+        <f t="shared" si="143"/>
         <v>1368</v>
       </c>
       <c r="N151" s="5">
-        <f t="shared" si="126"/>
+        <f t="shared" si="143"/>
         <v>1730</v>
       </c>
       <c r="O151" s="5">
-        <f t="shared" si="126"/>
+        <f t="shared" si="143"/>
         <v>1651</v>
       </c>
       <c r="P151" s="5">
-        <f t="shared" si="126"/>
+        <f t="shared" si="143"/>
         <v>2822</v>
       </c>
       <c r="Q151" s="5">
-        <f t="shared" si="126"/>
+        <f t="shared" si="143"/>
         <v>2328</v>
       </c>
       <c r="R151" s="5">
-        <f t="shared" si="126"/>
+        <f t="shared" si="143"/>
         <v>2035</v>
       </c>
       <c r="S151" s="5">
-        <f t="shared" si="126"/>
+        <f t="shared" si="143"/>
         <v>2888</v>
       </c>
       <c r="T151" s="5">
-        <f t="shared" si="126"/>
+        <f t="shared" si="143"/>
         <v>2463</v>
       </c>
       <c r="U151" s="5">
@@ -15529,7 +15969,10 @@
         <v>4164</v>
       </c>
       <c r="H152" s="5"/>
-      <c r="I152" s="5"/>
+      <c r="I152" s="5">
+        <f>+I150+I151</f>
+        <v>2468</v>
+      </c>
       <c r="J152" s="5"/>
       <c r="K152" s="5"/>
       <c r="L152" s="5">
@@ -15541,31 +15984,31 @@
         <v>1651</v>
       </c>
       <c r="N152" s="5">
-        <f t="shared" ref="N152:T152" si="127">O151</f>
+        <f t="shared" ref="N152:T152" si="144">O151</f>
         <v>1651</v>
       </c>
       <c r="O152" s="5">
-        <f t="shared" si="127"/>
+        <f t="shared" si="144"/>
         <v>2822</v>
       </c>
       <c r="P152" s="5">
-        <f t="shared" si="127"/>
+        <f t="shared" si="144"/>
         <v>2328</v>
       </c>
       <c r="Q152" s="5">
-        <f t="shared" si="127"/>
+        <f t="shared" si="144"/>
         <v>2035</v>
       </c>
       <c r="R152" s="5">
-        <f t="shared" si="127"/>
+        <f t="shared" si="144"/>
         <v>2888</v>
       </c>
       <c r="S152" s="5">
-        <f t="shared" si="127"/>
+        <f t="shared" si="144"/>
         <v>2463</v>
       </c>
       <c r="T152" s="5">
-        <f t="shared" si="127"/>
+        <f t="shared" si="144"/>
         <v>3337</v>
       </c>
       <c r="U152" s="5">
@@ -15576,7 +16019,7 @@
         <f>+V150+V151</f>
         <v>5104</v>
       </c>
-      <c r="W152" s="102">
+      <c r="W152" s="101">
         <f>+W150+W151</f>
         <v>3787</v>
       </c>
@@ -17693,7 +18136,7 @@
       </c>
       <c r="N15" s="44">
         <f>N32/Model!V91</f>
-        <v>0.62492249224922491</v>
+        <v>0.65096509650965095</v>
       </c>
       <c r="P15" s="44">
         <f t="shared" ref="P15:P16" si="7">AVERAGE(C15:M15)</f>
@@ -17809,7 +18252,7 @@
       </c>
       <c r="N17" s="48">
         <f>N32/(Model!V38+Model!V109)</f>
-        <v>5.352578379304437</v>
+        <v>5.5756381702929589</v>
       </c>
       <c r="P17" s="48">
         <f>AVERAGE(C17:M17)</f>
@@ -18281,7 +18724,7 @@
       </c>
       <c r="N29" s="51">
         <f>Main!H3</f>
-        <v>46.15</v>
+        <v>47.45</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.2">
@@ -18331,7 +18774,7 @@
       </c>
       <c r="N30" s="51">
         <f>Main!H4</f>
-        <v>2187</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.2">
@@ -18381,7 +18824,7 @@
       </c>
       <c r="N31" s="5">
         <f>N30*N29</f>
-        <v>100930.05</v>
+        <v>104105.3</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.2">
@@ -18431,7 +18874,7 @@
       </c>
       <c r="N32" s="51">
         <f>Main!H7-Main!H6</f>
-        <v>31243</v>
+        <v>32545</v>
       </c>
     </row>
     <row r="33" spans="2:17" x14ac:dyDescent="0.2">
@@ -18481,7 +18924,7 @@
       </c>
       <c r="N33" s="52">
         <f>N31+N32</f>
-        <v>132173.04999999999</v>
+        <v>136650.29999999999</v>
       </c>
     </row>
     <row r="34" spans="2:17" x14ac:dyDescent="0.2">
@@ -18550,11 +18993,11 @@
       </c>
       <c r="N36" s="49">
         <f>N31/Model!V43</f>
-        <v>31.729031751021694</v>
+        <v>32.727224143351151</v>
       </c>
       <c r="P36" s="49">
         <f>AVERAGE(N36,C36:L36)</f>
-        <v>16.567714909584218</v>
+        <v>16.667534148817165</v>
       </c>
       <c r="Q36" s="49">
         <f>MEDIAN(N36,C36:L36)</f>
@@ -18605,11 +19048,11 @@
       </c>
       <c r="N37" s="49">
         <f>N32/Model!V44</f>
-        <v>276.48672566371681</v>
+        <v>288.00884955752213</v>
       </c>
       <c r="P37" s="49">
         <f t="shared" ref="P37:P38" si="20">AVERAGE(N37,C37:L37)</f>
-        <v>42.617064919283273</v>
+        <v>43.897300907483867</v>
       </c>
       <c r="Q37" s="49">
         <f t="shared" ref="Q37:Q38" si="21">MEDIAN(N37,C37:L37)</f>
@@ -18656,7 +19099,7 @@
       </c>
       <c r="M38" s="49">
         <f>N31/Model!U91</f>
-        <v>1.9067149658064761</v>
+        <v>1.9667000415611895</v>
       </c>
       <c r="N38" s="49">
         <f>O31/Model!V91</f>
@@ -18738,11 +19181,11 @@
       </c>
       <c r="N41" s="49">
         <f>N33/(Model!V38+Model!V109)</f>
-        <v>22.644003769059445</v>
+        <v>23.411050197019016</v>
       </c>
       <c r="P41" s="49">
         <f>AVERAGE(C41:N41)</f>
-        <v>15.708251037890859</v>
+        <v>15.777982531341729</v>
       </c>
       <c r="Q41" s="49">
         <f>MEDIAN(C41:N41)</f>
@@ -18796,11 +19239,11 @@
       </c>
       <c r="N42" s="49">
         <f>N33/Model!V38</f>
-        <v>48.308863304093563</v>
+        <v>49.945285087719292</v>
       </c>
       <c r="P42" s="49">
         <f t="shared" ref="P42:P44" si="22">AVERAGE(C42:N42)</f>
-        <v>18.541102522269355</v>
+        <v>18.689868138962602</v>
       </c>
       <c r="Q42" s="49">
         <f t="shared" ref="Q42:Q44" si="23">MEDIAN(C42:N42)</f>
@@ -18905,11 +19348,11 @@
       </c>
       <c r="N44" s="49">
         <f>N33/Model!V29</f>
-        <v>5.1097170139560051</v>
+        <v>5.2828043453048279</v>
       </c>
       <c r="P44" s="49">
         <f t="shared" si="22"/>
-        <v>5.7938026557091824</v>
+        <v>5.8095378676499836</v>
       </c>
       <c r="Q44" s="49">
         <f t="shared" si="23"/>
@@ -18963,7 +19406,7 @@
       </c>
       <c r="N46" s="54">
         <f>(-1*Model!V142)/N31</f>
-        <v>5.1649632592077381E-2</v>
+        <v>5.0074299771481375E-2</v>
       </c>
       <c r="P46" s="55">
         <f>AVERAGE(C46:M46)</f>
@@ -19054,14 +19497,14 @@
       </c>
       <c r="J3" s="59">
         <f>+Main!H3</f>
-        <v>46.15</v>
+        <v>47.45</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>151</v>
       </c>
       <c r="O3" s="59">
         <f>+J3</f>
-        <v>46.15</v>
+        <v>47.45</v>
       </c>
     </row>
     <row r="4" spans="1:36" x14ac:dyDescent="0.2">
@@ -19070,14 +19513,14 @@
       </c>
       <c r="E4" s="60">
         <f ca="1">+TODAY()</f>
-        <v>46226</v>
+        <v>46233</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>153</v>
       </c>
       <c r="J4" s="61">
         <f ca="1">V62</f>
-        <v>42.245377497915634</v>
+        <v>55.220363038811023</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>368</v>
@@ -19099,7 +19542,7 @@
       </c>
       <c r="J5" s="64">
         <f ca="1">J4/J3-1</f>
-        <v>-8.4607204812228942E-2</v>
+        <v>0.16375896815197089</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>155</v>
@@ -19485,39 +19928,39 @@
       </c>
       <c r="N25" s="5">
         <f t="shared" ref="N25:V25" ca="1" si="1">M25*(1+N26)</f>
-        <v>24815.310803046988</v>
+        <v>26443.080130483715</v>
       </c>
       <c r="O25" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>25031.745508807009</v>
+        <v>27071.081001107599</v>
       </c>
       <c r="P25" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>25259.724658939525</v>
+        <v>27771.207689496914</v>
       </c>
       <c r="Q25" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>25499.881649470601</v>
+        <v>28551.871794969724</v>
       </c>
       <c r="R25" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>25752.88493800646</v>
+        <v>29422.466015570953</v>
       </c>
       <c r="S25" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>26019.439985845645</v>
+        <v>30393.478215345207</v>
       </c>
       <c r="T25" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>27847.421972449651</v>
+        <v>34843.90368938684</v>
       </c>
       <c r="U25" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>27934.534266645664</v>
+        <v>36042.767472501393</v>
       </c>
       <c r="V25" s="5">
         <f t="shared" ca="1" si="1"/>
-        <v>28035.002664004365</v>
+        <v>37383.241074395737</v>
       </c>
     </row>
     <row r="26" spans="1:22" x14ac:dyDescent="0.2">
@@ -19552,39 +19995,39 @@
       </c>
       <c r="N26" s="74" cm="1">
         <f t="array" aca="1" ref="N26" ca="1">OFFSET(N26,$E$11,,)</f>
-        <v>-4.0719495704765969E-2</v>
+        <v>2.2204857477547961E-2</v>
       </c>
       <c r="O26" s="74" cm="1">
         <f t="array" aca="1" ref="O26" ca="1">OFFSET(O26,$E$11,,)</f>
-        <v>8.7218212771064032E-3</v>
+        <v>2.3749157341921061E-2</v>
       </c>
       <c r="P26" s="74" cm="1">
         <f t="array" aca="1" ref="P26" ca="1">OFFSET(P26,$E$11,,)</f>
-        <v>9.1076009882053912E-3</v>
+        <v>2.5862531620391087E-2</v>
       </c>
       <c r="Q26" s="74" cm="1">
         <f t="array" aca="1" ref="Q26" ca="1">OFFSET(Q26,$E$11,,)</f>
-        <v>9.507506268326851E-3</v>
+        <v>2.8110556595205553E-2</v>
       </c>
       <c r="R26" s="74" cm="1">
         <f t="array" aca="1" ref="R26" ca="1">OFFSET(R26,$E$11,,)</f>
-        <v>9.9217436384107984E-3</v>
+        <v>3.04916688773662E-2</v>
       </c>
       <c r="S26" s="74" cm="1">
         <f t="array" aca="1" ref="S26" ca="1">OFFSET(S26,$E$11,,)</f>
-        <v>1.0350492711043815E-2</v>
+        <v>3.3002407047063136E-2</v>
       </c>
       <c r="T26" s="74" cm="1">
         <f t="array" aca="1" ref="T26" ca="1">OFFSET(T26,$E$11,,)</f>
-        <v>7.0254470795620957E-2</v>
+        <v>0.14642698813572053</v>
       </c>
       <c r="U26" s="74" cm="1">
         <f t="array" aca="1" ref="U26" ca="1">OFFSET(U26,$E$11,,)</f>
-        <v>3.1281995971547041E-3</v>
+        <v>3.4406701206665329E-2</v>
       </c>
       <c r="V26" s="74" cm="1">
         <f t="array" aca="1" ref="V26" ca="1">OFFSET(V26,$E$11,,)</f>
-        <v>3.5965660425798431E-3</v>
+        <v>3.7191195235411582E-2</v>
       </c>
     </row>
     <row r="27" spans="1:22" x14ac:dyDescent="0.2">
@@ -19602,39 +20045,39 @@
       </c>
       <c r="N27" s="75">
         <f t="shared" ref="N27:V27" si="3">+N28-1%</f>
-        <v>-6.0719495704765973E-2</v>
+        <v>2.2048574775479588E-3</v>
       </c>
       <c r="O27" s="75">
         <f t="shared" si="3"/>
-        <v>-1.1278178722893597E-2</v>
+        <v>3.7491573419210587E-3</v>
       </c>
       <c r="P27" s="75">
         <f t="shared" si="3"/>
-        <v>-1.0892399011794609E-2</v>
+        <v>5.8625316203910847E-3</v>
       </c>
       <c r="Q27" s="75">
         <f t="shared" si="3"/>
-        <v>-1.0492493731673149E-2</v>
+        <v>8.1105565952055512E-3</v>
       </c>
       <c r="R27" s="75">
         <f t="shared" si="3"/>
-        <v>-1.0078256361589202E-2</v>
+        <v>1.0491668877366198E-2</v>
       </c>
       <c r="S27" s="75">
         <f t="shared" si="3"/>
-        <v>-9.6495072889561852E-3</v>
+        <v>1.3002407047063133E-2</v>
       </c>
       <c r="T27" s="75">
         <f t="shared" si="3"/>
-        <v>5.025447079562096E-2</v>
+        <v>0.12642698813572051</v>
       </c>
       <c r="U27" s="75">
         <f t="shared" si="3"/>
-        <v>-1.6871800402845298E-2</v>
+        <v>1.4406701206665326E-2</v>
       </c>
       <c r="V27" s="75">
         <f t="shared" si="3"/>
-        <v>-1.6403433957420159E-2</v>
+        <v>1.7191195235411579E-2</v>
       </c>
     </row>
     <row r="28" spans="1:22" x14ac:dyDescent="0.2">
@@ -19652,39 +20095,39 @@
       </c>
       <c r="N28" s="75">
         <f>+Model!X60</f>
-        <v>-5.0719495704765971E-2</v>
+        <v>1.2204857477547959E-2</v>
       </c>
       <c r="O28" s="75">
         <f>+Model!Y60</f>
-        <v>-1.278178722893597E-3</v>
+        <v>1.3749157341921059E-2</v>
       </c>
       <c r="P28" s="75">
         <f>+Model!Z60</f>
-        <v>-8.9239901179460901E-4</v>
+        <v>1.5862531620391085E-2</v>
       </c>
       <c r="Q28" s="75">
         <f>+Model!AA60</f>
-        <v>-4.9249373167314925E-4</v>
+        <v>1.8110556595205551E-2</v>
       </c>
       <c r="R28" s="75">
         <f>+Model!AB60</f>
-        <v>-7.8256361589201795E-5</v>
+        <v>2.0491668877366198E-2</v>
       </c>
       <c r="S28" s="75">
         <f>+Model!AC60</f>
-        <v>3.5049271104381496E-4</v>
+        <v>2.3002407047063134E-2</v>
       </c>
       <c r="T28" s="75">
         <f>+Model!AD60</f>
-        <v>6.0254470795620962E-2</v>
+        <v>0.13642698813572052</v>
       </c>
       <c r="U28" s="75">
         <f>+Model!AE60</f>
-        <v>-6.8718004028452961E-3</v>
+        <v>2.4406701206665327E-2</v>
       </c>
       <c r="V28" s="75">
         <f>+Model!AF60</f>
-        <v>-6.4034339574201571E-3</v>
+        <v>2.719119523541158E-2</v>
       </c>
     </row>
     <row r="29" spans="1:22" x14ac:dyDescent="0.2">
@@ -19702,39 +20145,39 @@
       </c>
       <c r="N29" s="75">
         <f t="shared" ref="N29:V29" si="4">+N28+1%</f>
-        <v>-4.0719495704765969E-2</v>
+        <v>2.2204857477547961E-2</v>
       </c>
       <c r="O29" s="75">
         <f t="shared" si="4"/>
-        <v>8.7218212771064032E-3</v>
+        <v>2.3749157341921061E-2</v>
       </c>
       <c r="P29" s="75">
         <f t="shared" si="4"/>
-        <v>9.1076009882053912E-3</v>
+        <v>2.5862531620391087E-2</v>
       </c>
       <c r="Q29" s="75">
         <f t="shared" si="4"/>
-        <v>9.507506268326851E-3</v>
+        <v>2.8110556595205553E-2</v>
       </c>
       <c r="R29" s="75">
         <f t="shared" si="4"/>
-        <v>9.9217436384107984E-3</v>
+        <v>3.04916688773662E-2</v>
       </c>
       <c r="S29" s="75">
         <f t="shared" si="4"/>
-        <v>1.0350492711043815E-2</v>
+        <v>3.3002407047063136E-2</v>
       </c>
       <c r="T29" s="75">
         <f t="shared" si="4"/>
-        <v>7.0254470795620957E-2</v>
+        <v>0.14642698813572053</v>
       </c>
       <c r="U29" s="75">
         <f t="shared" si="4"/>
-        <v>3.1281995971547041E-3</v>
+        <v>3.4406701206665329E-2</v>
       </c>
       <c r="V29" s="75">
         <f t="shared" si="4"/>
-        <v>3.5965660425798431E-3</v>
+        <v>3.7191195235411582E-2</v>
       </c>
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.2">
@@ -19771,39 +20214,39 @@
       </c>
       <c r="N31" s="5">
         <f t="shared" ref="N31:V31" ca="1" si="5">N32*N25</f>
-        <v>9677.9712131883261</v>
+        <v>10312.801250888651</v>
       </c>
       <c r="O31" s="5">
         <f t="shared" ca="1" si="5"/>
-        <v>9762.3807484347344</v>
+        <v>10557.721590431964</v>
       </c>
       <c r="P31" s="5">
         <f t="shared" ca="1" si="5"/>
-        <v>9851.2926169864131</v>
+        <v>10830.770998903798</v>
       </c>
       <c r="Q31" s="5">
         <f t="shared" ca="1" si="5"/>
-        <v>9944.9538432935351</v>
+        <v>11135.230000038193</v>
       </c>
       <c r="R31" s="5">
         <f t="shared" ca="1" si="5"/>
-        <v>10043.62512582252</v>
+        <v>11474.761746072672</v>
       </c>
       <c r="S31" s="5">
         <f t="shared" ca="1" si="5"/>
-        <v>10147.581594479801</v>
+        <v>11853.456503984631</v>
       </c>
       <c r="T31" s="5">
         <f t="shared" ca="1" si="5"/>
-        <v>10860.494569255365</v>
+        <v>13589.122438860868</v>
       </c>
       <c r="U31" s="5">
         <f t="shared" ca="1" si="5"/>
-        <v>10894.468363991811</v>
+        <v>14056.679314275543</v>
       </c>
       <c r="V31" s="5">
         <f t="shared" ca="1" si="5"/>
-        <v>10933.651038961703</v>
+        <v>14579.464019014338</v>
       </c>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.2">
@@ -19840,7 +20283,7 @@
       </c>
       <c r="N32" s="74" cm="1">
         <f t="array" aca="1" ref="N32" ca="1">OFFSET(N32,$E$12,,)</f>
-        <v>0.39</v>
+        <v>0.39000000000000007</v>
       </c>
       <c r="O32" s="74" cm="1">
         <f t="array" aca="1" ref="O32" ca="1">OFFSET(O32,$E$12,,)</f>
@@ -19848,7 +20291,7 @@
       </c>
       <c r="P32" s="74" cm="1">
         <f t="array" aca="1" ref="P32" ca="1">OFFSET(P32,$E$12,,)</f>
-        <v>0.38999999999999996</v>
+        <v>0.39</v>
       </c>
       <c r="Q32" s="74" cm="1">
         <f t="array" aca="1" ref="Q32" ca="1">OFFSET(Q32,$E$12,,)</f>
@@ -19868,7 +20311,7 @@
       </c>
       <c r="U32" s="74" cm="1">
         <f t="array" aca="1" ref="U32" ca="1">OFFSET(U32,$E$12,,)</f>
-        <v>0.39000000000000007</v>
+        <v>0.39</v>
       </c>
       <c r="V32" s="74" cm="1">
         <f t="array" aca="1" ref="V32" ca="1">OFFSET(V32,$E$12,,)</f>
@@ -19885,7 +20328,7 @@
       </c>
       <c r="N33" s="75">
         <f t="shared" ref="N33:V33" si="7">+N34-2%</f>
-        <v>0.37</v>
+        <v>0.37000000000000005</v>
       </c>
       <c r="O33" s="75">
         <f t="shared" si="7"/>
@@ -19893,7 +20336,7 @@
       </c>
       <c r="P33" s="75">
         <f t="shared" si="7"/>
-        <v>0.36999999999999994</v>
+        <v>0.37</v>
       </c>
       <c r="Q33" s="75">
         <f t="shared" si="7"/>
@@ -19913,7 +20356,7 @@
       </c>
       <c r="U33" s="75">
         <f t="shared" si="7"/>
-        <v>0.37000000000000005</v>
+        <v>0.37</v>
       </c>
       <c r="V33" s="75">
         <f t="shared" si="7"/>
@@ -19930,7 +20373,7 @@
       </c>
       <c r="N34" s="75">
         <f>+Model!X62</f>
-        <v>0.39</v>
+        <v>0.39000000000000007</v>
       </c>
       <c r="O34" s="75">
         <f>+Model!Y62</f>
@@ -19938,7 +20381,7 @@
       </c>
       <c r="P34" s="75">
         <f>+Model!Z62</f>
-        <v>0.38999999999999996</v>
+        <v>0.39</v>
       </c>
       <c r="Q34" s="75">
         <f>+Model!AA62</f>
@@ -19958,7 +20401,7 @@
       </c>
       <c r="U34" s="75">
         <f>+Model!AE62</f>
-        <v>0.39000000000000007</v>
+        <v>0.39</v>
       </c>
       <c r="V34" s="75">
         <f>+Model!AF62</f>
@@ -19975,7 +20418,7 @@
       </c>
       <c r="N35" s="75">
         <f t="shared" ref="N35:V35" si="8">+N34+2%</f>
-        <v>0.41000000000000003</v>
+        <v>0.41000000000000009</v>
       </c>
       <c r="O35" s="75">
         <f t="shared" si="8"/>
@@ -19983,7 +20426,7 @@
       </c>
       <c r="P35" s="75">
         <f t="shared" si="8"/>
-        <v>0.41</v>
+        <v>0.41000000000000003</v>
       </c>
       <c r="Q35" s="75">
         <f t="shared" si="8"/>
@@ -20003,7 +20446,7 @@
       </c>
       <c r="U35" s="75">
         <f t="shared" si="8"/>
-        <v>0.41000000000000009</v>
+        <v>0.41000000000000003</v>
       </c>
       <c r="V35" s="75">
         <f t="shared" si="8"/>
@@ -20044,39 +20487,39 @@
       </c>
       <c r="N37" s="5">
         <f t="shared" ref="N37:V37" ca="1" si="9">N38*N31</f>
-        <v>2096.661441812018</v>
+        <v>2234.1927107970437</v>
       </c>
       <c r="O37" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>2157.2471111498244</v>
+        <v>2332.9979631182941</v>
       </c>
       <c r="P37" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>2220.4323462125581</v>
+        <v>2441.2019006439446</v>
       </c>
       <c r="Q37" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>2286.3739830758213</v>
+        <v>2560.0219537289659</v>
       </c>
       <c r="R37" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>2355.2399755893803</v>
+        <v>2690.8429213700747</v>
       </c>
       <c r="S37" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>2427.2102271852664</v>
+        <v>2835.2401590560553</v>
       </c>
       <c r="T37" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>2649.6872491500044</v>
+        <v>3315.4037529118364</v>
       </c>
       <c r="U37" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>2711.1355197300895</v>
+        <v>3498.0653764020853</v>
       </c>
       <c r="V37" s="5">
         <f t="shared" ca="1" si="9"/>
-        <v>2775.3040236307265</v>
+        <v>3700.7258609373312</v>
       </c>
     </row>
     <row r="38" spans="2:22" x14ac:dyDescent="0.2">
@@ -20189,39 +20632,39 @@
       </c>
       <c r="N40" s="78">
         <f t="shared" ca="1" si="11"/>
-        <v>7581.3097713763082</v>
+        <v>8078.6085400916072</v>
       </c>
       <c r="O40" s="78">
         <f t="shared" ca="1" si="11"/>
-        <v>7605.13363728491</v>
+        <v>8224.7236273136696</v>
       </c>
       <c r="P40" s="78">
         <f t="shared" ca="1" si="11"/>
-        <v>7630.8602707738555</v>
+        <v>8389.5690982598535</v>
       </c>
       <c r="Q40" s="78">
         <f t="shared" ca="1" si="11"/>
-        <v>7658.5798602177138</v>
+        <v>8575.2080463092279</v>
       </c>
       <c r="R40" s="78">
         <f t="shared" ca="1" si="11"/>
-        <v>7688.3851502331399</v>
+        <v>8783.9188247025977</v>
       </c>
       <c r="S40" s="78">
         <f t="shared" ca="1" si="11"/>
-        <v>7720.371367294535</v>
+        <v>9018.2163449285763</v>
       </c>
       <c r="T40" s="78">
         <f t="shared" ca="1" si="11"/>
-        <v>8210.8073201053594</v>
+        <v>10273.718685949032</v>
       </c>
       <c r="U40" s="78">
         <f t="shared" ca="1" si="11"/>
-        <v>8183.3328442617221</v>
+        <v>10558.613937873459</v>
       </c>
       <c r="V40" s="79">
         <f t="shared" ca="1" si="11"/>
-        <v>8158.3470153309772</v>
+        <v>10878.738158077007</v>
       </c>
     </row>
     <row r="42" spans="2:22" x14ac:dyDescent="0.2">
@@ -20258,39 +20701,39 @@
       </c>
       <c r="N42" s="5">
         <f t="shared" ref="N42:V42" ca="1" si="12">N43*N25</f>
-        <v>1389.6574049706314</v>
+        <v>1480.8124873070881</v>
       </c>
       <c r="O42" s="5">
         <f t="shared" ca="1" si="12"/>
-        <v>1401.7777484931926</v>
+        <v>1515.9805360620255</v>
       </c>
       <c r="P42" s="5">
         <f t="shared" ca="1" si="12"/>
-        <v>1414.5445809006135</v>
+        <v>1555.1876306118272</v>
       </c>
       <c r="Q42" s="5">
         <f t="shared" ca="1" si="12"/>
-        <v>1427.9933723703537</v>
+        <v>1598.9048205183046</v>
       </c>
       <c r="R42" s="5">
         <f t="shared" ca="1" si="12"/>
-        <v>1442.1615565283619</v>
+        <v>1647.6580968719734</v>
       </c>
       <c r="S42" s="5">
         <f t="shared" ca="1" si="12"/>
-        <v>1457.0886392073562</v>
+        <v>1702.0347800593315</v>
       </c>
       <c r="T42" s="5">
         <f t="shared" ca="1" si="12"/>
-        <v>1559.4556304571804</v>
+        <v>1951.2586066056631</v>
       </c>
       <c r="U42" s="5">
         <f t="shared" ca="1" si="12"/>
-        <v>1564.3339189321573</v>
+        <v>2018.3949784600782</v>
       </c>
       <c r="V42" s="5">
         <f t="shared" ca="1" si="12"/>
-        <v>1569.9601491842445</v>
+        <v>2093.4615001661614</v>
       </c>
     </row>
     <row r="43" spans="2:22" x14ac:dyDescent="0.2">
@@ -20390,39 +20833,39 @@
       </c>
       <c r="N45" s="5">
         <f t="shared" ref="N45:V45" ca="1" si="14">N46*N25</f>
-        <v>-496.30621606093979</v>
+        <v>-528.86160260967426</v>
       </c>
       <c r="O45" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>-500.63491017614018</v>
+        <v>-541.42162002215196</v>
       </c>
       <c r="P45" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>-505.19449317879054</v>
+        <v>-555.42415378993826</v>
       </c>
       <c r="Q45" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>-509.99763298941201</v>
+        <v>-571.0374358993945</v>
       </c>
       <c r="R45" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>-515.05769876012926</v>
+        <v>-588.44932031141911</v>
       </c>
       <c r="S45" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>-520.3887997169129</v>
+        <v>-607.86956430690418</v>
       </c>
       <c r="T45" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>-556.94843944899299</v>
+        <v>-696.87807378773675</v>
       </c>
       <c r="U45" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>-558.69068533291329</v>
+        <v>-720.85534945002792</v>
       </c>
       <c r="V45" s="5">
         <f t="shared" ca="1" si="14"/>
-        <v>-560.70005328008733</v>
+        <v>-747.66482148791476</v>
       </c>
     </row>
     <row r="46" spans="2:22" x14ac:dyDescent="0.2">
@@ -20518,39 +20961,39 @@
       </c>
       <c r="N48" s="5">
         <f t="shared" ref="N48:V48" ca="1" si="16">N49*N25</f>
-        <v>24.815310803046987</v>
+        <v>26.443080130483715</v>
       </c>
       <c r="O48" s="5">
         <f t="shared" ca="1" si="16"/>
-        <v>25.03174550880701</v>
+        <v>27.071081001107601</v>
       </c>
       <c r="P48" s="5">
         <f t="shared" ca="1" si="16"/>
-        <v>25.259724658939525</v>
+        <v>27.771207689496915</v>
       </c>
       <c r="Q48" s="5">
         <f t="shared" ca="1" si="16"/>
-        <v>25.499881649470602</v>
+        <v>28.551871794969724</v>
       </c>
       <c r="R48" s="5">
         <f t="shared" ca="1" si="16"/>
-        <v>25.75288493800646</v>
+        <v>29.422466015570954</v>
       </c>
       <c r="S48" s="5">
         <f t="shared" ca="1" si="16"/>
-        <v>26.019439985845647</v>
+        <v>30.393478215345208</v>
       </c>
       <c r="T48" s="5">
         <f t="shared" ca="1" si="16"/>
-        <v>27.847421972449652</v>
+        <v>34.843903689386842</v>
       </c>
       <c r="U48" s="5">
         <f t="shared" ca="1" si="16"/>
-        <v>27.934534266645663</v>
+        <v>36.042767472501396</v>
       </c>
       <c r="V48" s="5">
         <f t="shared" ca="1" si="16"/>
-        <v>28.035002664004367</v>
+        <v>37.383241074395741</v>
       </c>
     </row>
     <row r="49" spans="2:24" x14ac:dyDescent="0.2">
@@ -20650,39 +21093,39 @@
       </c>
       <c r="N51" s="84">
         <f t="shared" ca="1" si="18"/>
-        <v>8499.4762710890463</v>
+        <v>9057.0025049195065</v>
       </c>
       <c r="O51" s="84">
         <f t="shared" ca="1" si="18"/>
-        <v>8531.3082211107685</v>
+        <v>9226.3536243546496</v>
       </c>
       <c r="P51" s="84">
         <f t="shared" ca="1" si="18"/>
-        <v>8565.4700831546179</v>
+        <v>9417.1037827712389</v>
       </c>
       <c r="Q51" s="84">
         <f t="shared" ca="1" si="18"/>
-        <v>8602.0754812481246</v>
+        <v>9631.6273027231073</v>
       </c>
       <c r="R51" s="84">
         <f t="shared" ca="1" si="18"/>
-        <v>8641.2418929393807</v>
+        <v>9872.5500672787221</v>
       </c>
       <c r="S51" s="84">
         <f t="shared" ca="1" si="18"/>
-        <v>8683.0906467708246</v>
+        <v>10142.775038896349</v>
       </c>
       <c r="T51" s="84">
         <f t="shared" ca="1" si="18"/>
-        <v>9241.1619330859958</v>
+        <v>11562.943122456345</v>
       </c>
       <c r="U51" s="84">
         <f t="shared" ca="1" si="18"/>
-        <v>9216.9106121276127</v>
+        <v>11892.196334356009</v>
       </c>
       <c r="V51" s="85">
         <f ca="1">V40+V42+V45+V48</f>
-        <v>9195.6421138991391</v>
+        <v>12261.918077829649</v>
       </c>
     </row>
     <row r="52" spans="2:24" x14ac:dyDescent="0.2">
@@ -20701,43 +21144,43 @@
       <c r="L52" s="88"/>
       <c r="M52" s="88">
         <f ca="1">(M51/(1+$E$18)^M53)*M53</f>
-        <v>4836.3694907666695</v>
+        <v>4996.5631240307575</v>
       </c>
       <c r="N52" s="88">
         <f ca="1">N51/(1+$E$18)^N53</f>
-        <v>7646.0864199563766</v>
+        <v>8136.9223801776243</v>
       </c>
       <c r="O52" s="88">
         <f t="shared" ref="O52:U52" ca="1" si="19">O51/(1+$E$18)^O53</f>
-        <v>7172.637647920893</v>
+        <v>7746.7939323012806</v>
       </c>
       <c r="P52" s="88">
         <f t="shared" ca="1" si="19"/>
-        <v>6730.2420506746348</v>
+        <v>7389.6775217115837</v>
       </c>
       <c r="Q52" s="88">
         <f t="shared" ca="1" si="19"/>
-        <v>6316.8265580803072</v>
+        <v>7063.5662273741518</v>
       </c>
       <c r="R52" s="88">
         <f t="shared" ca="1" si="19"/>
-        <v>5930.4560025400669</v>
+        <v>6766.5908862579699</v>
       </c>
       <c r="S52" s="88">
         <f t="shared" ca="1" si="19"/>
-        <v>5569.3239861669817</v>
+        <v>6497.0108208417723</v>
       </c>
       <c r="T52" s="88">
         <f t="shared" ca="1" si="19"/>
-        <v>5539.5049006579266</v>
+        <v>6922.1564163711428</v>
       </c>
       <c r="U52" s="88">
         <f t="shared" ca="1" si="19"/>
-        <v>5163.5212467125639</v>
+        <v>6653.5176321225363</v>
       </c>
       <c r="V52" s="89">
         <f ca="1">V51/(1+$E$18)^V53</f>
-        <v>4814.5851908548248</v>
+        <v>6411.562411218586</v>
       </c>
     </row>
     <row r="53" spans="2:24" x14ac:dyDescent="0.2">
@@ -20746,43 +21189,43 @@
       </c>
       <c r="M53" s="50">
         <f ca="1">YEARFRAC(E4,E5)</f>
-        <v>0.56388888888888888</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="N53" s="50">
         <f ca="1">M53+1</f>
-        <v>1.5638888888888889</v>
+        <v>1.5833333333333335</v>
       </c>
       <c r="O53" s="50">
         <f ca="1">N53+1</f>
-        <v>2.5638888888888891</v>
+        <v>2.5833333333333335</v>
       </c>
       <c r="P53" s="50">
         <f t="shared" ref="P53:V53" ca="1" si="20">O53+1</f>
-        <v>3.5638888888888891</v>
+        <v>3.5833333333333335</v>
       </c>
       <c r="Q53" s="50">
         <f t="shared" ca="1" si="20"/>
-        <v>4.5638888888888891</v>
+        <v>4.5833333333333339</v>
       </c>
       <c r="R53" s="50">
         <f t="shared" ca="1" si="20"/>
-        <v>5.5638888888888891</v>
+        <v>5.5833333333333339</v>
       </c>
       <c r="S53" s="50">
         <f t="shared" ca="1" si="20"/>
-        <v>6.5638888888888891</v>
+        <v>6.5833333333333339</v>
       </c>
       <c r="T53" s="50">
         <f t="shared" ca="1" si="20"/>
-        <v>7.5638888888888891</v>
+        <v>7.5833333333333339</v>
       </c>
       <c r="U53" s="50">
         <f t="shared" ca="1" si="20"/>
-        <v>8.56388888888889</v>
+        <v>8.5833333333333339</v>
       </c>
       <c r="V53" s="50">
         <f t="shared" ca="1" si="20"/>
-        <v>9.56388888888889</v>
+        <v>9.5833333333333339</v>
       </c>
     </row>
     <row r="54" spans="2:24" x14ac:dyDescent="0.2">
@@ -20795,7 +21238,7 @@
       <c r="Q54" s="51"/>
       <c r="V54" s="5">
         <f ca="1">SUM(M52:V52)</f>
-        <v>59719.553494331238</v>
+        <v>68584.361352407403</v>
       </c>
     </row>
     <row r="55" spans="2:24" x14ac:dyDescent="0.2">
@@ -20808,7 +21251,7 @@
       <c r="Q55" s="51"/>
       <c r="V55" s="5">
         <f ca="1">+(V40*(1+E19))*(1-(E19/E20))/(E18-E19)</f>
-        <v>122073.04422939682</v>
+        <v>162778.15614307814</v>
       </c>
       <c r="X55" s="35" t="s">
         <v>375</v>
@@ -20839,7 +21282,7 @@
       <c r="U56" s="90"/>
       <c r="V56" s="91">
         <f ca="1">V55/(1+E18)^V53</f>
-        <v>63914.087093610258</v>
+        <v>85114.11515474398</v>
       </c>
     </row>
     <row r="57" spans="2:24" x14ac:dyDescent="0.2">
@@ -20867,7 +21310,7 @@
       <c r="U57" s="93"/>
       <c r="V57" s="94">
         <f ca="1">V54+V56</f>
-        <v>123633.6405879415</v>
+        <v>153698.47650715138</v>
       </c>
     </row>
     <row r="58" spans="2:24" x14ac:dyDescent="0.2">
@@ -20880,7 +21323,7 @@
       <c r="Q58" s="51"/>
       <c r="V58" s="95">
         <f>+Main!H6</f>
-        <v>3827</v>
+        <v>2518</v>
       </c>
     </row>
     <row r="59" spans="2:24" x14ac:dyDescent="0.2">
@@ -20908,7 +21351,7 @@
       <c r="U59" s="90"/>
       <c r="V59" s="91">
         <f>+Main!H7</f>
-        <v>35070</v>
+        <v>35063</v>
       </c>
     </row>
     <row r="60" spans="2:24" x14ac:dyDescent="0.2">
@@ -20921,7 +21364,7 @@
       <c r="Q60" s="51"/>
       <c r="V60" s="95">
         <f ca="1">V57+V58-V59</f>
-        <v>92390.640587941496</v>
+        <v>121153.47650715138</v>
       </c>
     </row>
     <row r="61" spans="2:24" x14ac:dyDescent="0.2">
@@ -20949,7 +21392,7 @@
       <c r="U61" s="90"/>
       <c r="V61" s="91">
         <f>+Main!H4</f>
-        <v>2187</v>
+        <v>2194</v>
       </c>
     </row>
     <row r="62" spans="2:24" x14ac:dyDescent="0.2">
@@ -20958,7 +21401,7 @@
       </c>
       <c r="V62" s="95">
         <f ca="1">V60/V61</f>
-        <v>42.245377497915634</v>
+        <v>55.220363038811023</v>
       </c>
     </row>
     <row r="66" spans="1:22" x14ac:dyDescent="0.2">
@@ -21019,7 +21462,7 @@
       </c>
       <c r="C69" s="97">
         <f ca="1">+J4</f>
-        <v>42.245377497915634</v>
+        <v>55.220363038811023</v>
       </c>
       <c r="D69" s="98">
         <v>-5.0000000000000001E-3</v>
@@ -21047,7 +21490,7 @@
       </c>
       <c r="N69" s="97">
         <f ca="1">+J4</f>
-        <v>42.245377497915634</v>
+        <v>55.220363038811023</v>
       </c>
       <c r="O69" s="98">
         <f t="shared" ref="O69:P69" si="21">+P69-1%</f>
@@ -21085,25 +21528,25 @@
       </c>
       <c r="D70" s="49">
         <f t="dataTable" ref="D70:J76" dt2D="1" dtr="1" r1="E19" r2="E18" ca="1"/>
-        <v>76.959557683234934</v>
+        <v>100.836497094686</v>
       </c>
       <c r="E70" s="49">
-        <v>81.216381659468041</v>
+        <v>106.49033037261388</v>
       </c>
       <c r="F70" s="49">
-        <v>86.648749166046997</v>
+        <v>113.70549838475445</v>
       </c>
       <c r="G70" s="100">
-        <v>93.844431968144747</v>
+        <v>123.26266849821411</v>
       </c>
       <c r="H70" s="49">
-        <v>103.86141924307252</v>
+        <v>136.56704197378417</v>
       </c>
       <c r="I70" s="49">
-        <v>118.8156893454528</v>
+        <v>156.42902133304761</v>
       </c>
       <c r="J70" s="49">
-        <v>143.64452510273821</v>
+        <v>189.40621245969763</v>
       </c>
       <c r="M70" s="107"/>
       <c r="N70" s="99">
@@ -21112,25 +21555,25 @@
       </c>
       <c r="O70" s="49">
         <f t="dataTable" ref="O70:U76" dt2D="1" dtr="1" r1="E20" r2="E18" ca="1"/>
-        <v>89.049570760714886</v>
+        <v>116.89422432270426</v>
       </c>
       <c r="P70" s="49">
-        <v>91.10451127818483</v>
+        <v>119.62355754077993</v>
       </c>
       <c r="Q70" s="49">
-        <v>92.645716666287285</v>
+        <v>121.67055745433665</v>
       </c>
       <c r="R70" s="100">
-        <v>93.844431968144747</v>
+        <v>123.26266849821411</v>
       </c>
       <c r="S70" s="49">
-        <v>94.803404209630727</v>
+        <v>124.53635733331608</v>
       </c>
       <c r="T70" s="49">
-        <v>95.588017861755617</v>
+        <v>125.57846638021768</v>
       </c>
       <c r="U70" s="49">
-        <v>96.241862571859684</v>
+        <v>126.44689058596903</v>
       </c>
     </row>
     <row r="71" spans="1:22" x14ac:dyDescent="0.2">
@@ -21140,25 +21583,25 @@
         <v>0.05</v>
       </c>
       <c r="D71" s="49">
-        <v>60.332220782386521</v>
+        <v>78.921273523836433</v>
       </c>
       <c r="E71" s="49">
-        <v>62.447117337667514</v>
+        <v>81.729716596857003</v>
       </c>
       <c r="F71" s="49">
-        <v>65.003109636321824</v>
+        <v>85.123905711177969</v>
       </c>
       <c r="G71" s="100">
-        <v>68.165608582114473</v>
+        <v>89.323495632286964</v>
       </c>
       <c r="H71" s="49">
-        <v>72.194545595247561</v>
+        <v>94.673658134521702</v>
       </c>
       <c r="I71" s="49">
-        <v>77.52313970939133</v>
+        <v>101.74967950844507</v>
       </c>
       <c r="J71" s="49">
-        <v>84.93118518515216</v>
+        <v>111.58707507707024</v>
       </c>
       <c r="M71" s="107"/>
       <c r="N71" s="99">
@@ -21166,25 +21609,25 @@
         <v>0.05</v>
       </c>
       <c r="O71" s="49">
-        <v>64.883974402062535</v>
+        <v>84.965701981273185</v>
       </c>
       <c r="P71" s="49">
-        <v>66.290389050656216</v>
+        <v>86.833327831707678</v>
       </c>
       <c r="Q71" s="49">
-        <v>67.345200037101492</v>
+        <v>88.234047219533537</v>
       </c>
       <c r="R71" s="100">
-        <v>68.165608582114473</v>
+        <v>89.323495632286964</v>
       </c>
       <c r="S71" s="49">
-        <v>68.821935418124866</v>
+        <v>90.195054362489728</v>
       </c>
       <c r="T71" s="49">
-        <v>69.358930102133357</v>
+        <v>90.90814786901926</v>
       </c>
       <c r="U71" s="49">
-        <v>69.806425672140435</v>
+        <v>91.502392457793846</v>
       </c>
     </row>
     <row r="72" spans="1:22" x14ac:dyDescent="0.2">
@@ -21194,25 +21637,25 @@
         <v>6.0000000000000005E-2</v>
       </c>
       <c r="D72" s="100">
-        <v>48.817745284431403</v>
+        <v>63.792495411594274</v>
       </c>
       <c r="E72" s="100">
-        <v>49.904326046081756</v>
+        <v>65.235137048337165</v>
       </c>
       <c r="F72" s="100">
-        <v>51.166884746211778</v>
+        <v>66.91142270875423</v>
       </c>
       <c r="G72" s="100">
-        <v>52.658214766365361</v>
+        <v>68.89144559994773</v>
       </c>
       <c r="H72" s="100">
-        <v>54.454573213217003</v>
+        <v>71.276451465509808</v>
       </c>
       <c r="I72" s="100">
-        <v>56.670345746778509</v>
+        <v>74.218308920828648</v>
       </c>
       <c r="J72" s="100">
-        <v>59.485281261354118</v>
+        <v>77.955668647228634</v>
       </c>
       <c r="M72" s="107"/>
       <c r="N72" s="99">
@@ -21220,25 +21663,25 @@
         <v>6.0000000000000005E-2</v>
       </c>
       <c r="O72" s="100">
-        <v>50.260432346118421</v>
+        <v>65.707935567941973</v>
       </c>
       <c r="P72" s="100">
-        <v>51.288053383367114</v>
+        <v>67.072297010230173</v>
       </c>
       <c r="Q72" s="100">
-        <v>52.058769161303623</v>
+        <v>68.095568091946305</v>
       </c>
       <c r="R72" s="100">
-        <v>52.658214766365361</v>
+        <v>68.89144559994773</v>
       </c>
       <c r="S72" s="100">
-        <v>53.137771250414751</v>
+        <v>69.528147606348881</v>
       </c>
       <c r="T72" s="100">
-        <v>53.53013564645515</v>
+        <v>70.049085611586207</v>
       </c>
       <c r="U72" s="100">
-        <v>53.857105976488825</v>
+        <v>70.483200615950622</v>
       </c>
     </row>
     <row r="73" spans="1:22" x14ac:dyDescent="0.2">
@@ -21247,50 +21690,50 @@
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="D73" s="49">
-        <v>40.371823536246886</v>
+        <v>52.73331963679216</v>
       </c>
       <c r="E73" s="49">
-        <v>40.92262566618038</v>
+        <v>53.46448021774971</v>
       </c>
       <c r="F73" s="49">
-        <v>41.541473202842582</v>
+        <v>54.285967463059947</v>
       </c>
       <c r="G73" s="100">
-        <v>42.245377497915634</v>
+        <v>55.220363038811023</v>
       </c>
       <c r="H73" s="49">
-        <v>43.057535849147968</v>
+        <v>56.298460126032246</v>
       </c>
       <c r="I73" s="49">
-        <v>44.010424473387367</v>
+        <v>57.563369178164706</v>
       </c>
       <c r="J73" s="49">
-        <v>45.150953461636163</v>
+        <v>59.077360850178749</v>
       </c>
       <c r="M73" s="107"/>
       <c r="N73" s="99">
         <v>7.0000000000000007E-2</v>
       </c>
       <c r="O73" s="49">
-        <v>40.418843230265601</v>
+        <v>52.795735783947087</v>
       </c>
       <c r="P73" s="49">
-        <v>41.201643630687038</v>
+        <v>53.834861750317344</v>
       </c>
       <c r="Q73" s="49">
-        <v>41.788743931003133</v>
+        <v>54.614206225095039</v>
       </c>
       <c r="R73" s="100">
-        <v>42.245377497915634</v>
+        <v>55.220363038811023</v>
       </c>
       <c r="S73" s="49">
-        <v>42.610684351445649</v>
+        <v>55.705288489783804</v>
       </c>
       <c r="T73" s="49">
-        <v>42.909571777061103</v>
+        <v>56.102045676943384</v>
       </c>
       <c r="U73" s="49">
-        <v>43.158644631740657</v>
+        <v>56.432676666242997</v>
       </c>
     </row>
     <row r="74" spans="1:22" x14ac:dyDescent="0.2">
@@ -21300,25 +21743,25 @@
         <v>0.08</v>
       </c>
       <c r="D74" s="49">
-        <v>33.912060854225224</v>
+        <v>44.305539825157382</v>
       </c>
       <c r="E74" s="49">
-        <v>34.168996025149028</v>
+        <v>44.646545935082159</v>
       </c>
       <c r="F74" s="49">
-        <v>34.446953164602952</v>
+        <v>45.01545254490987</v>
       </c>
       <c r="G74" s="100">
-        <v>34.75043698012918</v>
+        <v>45.418238333191141</v>
       </c>
       <c r="H74" s="49">
-        <v>35.085338243129009</v>
+        <v>45.862721571876833</v>
       </c>
       <c r="I74" s="49">
-        <v>35.459511315470834</v>
+        <v>46.359326623567995</v>
       </c>
       <c r="J74" s="49">
-        <v>35.88366669061157</v>
+        <v>46.922268528175216</v>
       </c>
       <c r="M74" s="107"/>
       <c r="N74" s="99">
@@ -21326,25 +21769,25 @@
         <v>0.08</v>
       </c>
       <c r="O74" s="49">
-        <v>33.31810682273904</v>
+        <v>43.517239986629967</v>
       </c>
       <c r="P74" s="49">
-        <v>33.931962604477675</v>
+        <v>44.331953563727623</v>
       </c>
       <c r="Q74" s="49">
-        <v>34.392354440781645</v>
+        <v>44.94298874655086</v>
       </c>
       <c r="R74" s="100">
-        <v>34.75043698012918</v>
+        <v>45.418238333191141</v>
       </c>
       <c r="S74" s="49">
-        <v>35.036903011607208</v>
+        <v>45.798438002503381</v>
       </c>
       <c r="T74" s="49">
-        <v>35.271284310089229</v>
+        <v>46.109510459213404</v>
       </c>
       <c r="U74" s="49">
-        <v>35.46660205882425</v>
+        <v>46.368737506471739</v>
       </c>
     </row>
     <row r="75" spans="1:22" x14ac:dyDescent="0.2">
@@ -21354,25 +21797,25 @@
         <v>0.09</v>
       </c>
       <c r="D75" s="49">
-        <v>28.811719972142431</v>
+        <v>37.676613981684916</v>
       </c>
       <c r="E75" s="49">
-        <v>28.902614558614424</v>
+        <v>37.79722827876347</v>
       </c>
       <c r="F75" s="49">
-        <v>28.993509145086428</v>
+        <v>37.917842575842023</v>
       </c>
       <c r="G75" s="100">
-        <v>29.084403731558428</v>
+        <v>38.038456872920577</v>
       </c>
       <c r="H75" s="49">
-        <v>29.175298318030425</v>
+        <v>38.159071169999137</v>
       </c>
       <c r="I75" s="49">
-        <v>29.266192904502429</v>
+        <v>38.279685467077698</v>
       </c>
       <c r="J75" s="49">
-        <v>29.357087490974422</v>
+        <v>38.400299764156252</v>
       </c>
       <c r="M75" s="107"/>
       <c r="N75" s="99">
@@ -21380,25 +21823,25 @@
         <v>0.09</v>
       </c>
       <c r="O75" s="49">
-        <v>27.936859577349434</v>
+        <v>36.515701372303809</v>
       </c>
       <c r="P75" s="49">
-        <v>28.428664214867577</v>
+        <v>37.168310872568142</v>
       </c>
       <c r="Q75" s="49">
-        <v>28.797517693006178</v>
+        <v>37.657767997766392</v>
       </c>
       <c r="R75" s="100">
-        <v>29.084403731558428</v>
+        <v>38.038456872920577</v>
       </c>
       <c r="S75" s="49">
-        <v>29.313912562400226</v>
+        <v>38.343007973043932</v>
       </c>
       <c r="T75" s="49">
-        <v>29.501692514907145</v>
+        <v>38.592186145872134</v>
       </c>
       <c r="U75" s="49">
-        <v>29.658175808662921</v>
+        <v>38.799834623228961</v>
       </c>
     </row>
     <row r="76" spans="1:22" x14ac:dyDescent="0.2">
@@ -21408,25 +21851,25 @@
         <v>9.9999999999999992E-2</v>
       </c>
       <c r="D76" s="49">
-        <v>24.682752535264644</v>
+        <v>32.331247790548538</v>
       </c>
       <c r="E76" s="49">
-        <v>24.678786226226855</v>
+        <v>32.325985556003602</v>
       </c>
       <c r="F76" s="49">
-        <v>24.665634780469972</v>
+        <v>32.308537094091449</v>
       </c>
       <c r="G76" s="100">
-        <v>24.641767341874154</v>
+        <v>32.276871366917533</v>
       </c>
       <c r="H76" s="49">
-        <v>24.605292852879582</v>
+        <v>32.22847944531803</v>
       </c>
       <c r="I76" s="49">
-        <v>24.553847491536494</v>
+        <v>32.160225167838135</v>
       </c>
       <c r="J76" s="49">
-        <v>24.484437083375184</v>
+        <v>32.068136063301765</v>
       </c>
       <c r="M76" s="108"/>
       <c r="N76" s="99">
@@ -21434,25 +21877,25 @@
         <v>9.9999999999999992E-2</v>
       </c>
       <c r="O76" s="49">
-        <v>23.707040511968483</v>
+        <v>31.036738092494403</v>
       </c>
       <c r="P76" s="49">
-        <v>24.107637724785203</v>
+        <v>31.568223781532893</v>
       </c>
       <c r="Q76" s="49">
-        <v>24.408085634397739</v>
+        <v>31.966838048311757</v>
       </c>
       <c r="R76" s="100">
-        <v>24.641767341874154</v>
+        <v>32.276871366917533</v>
       </c>
       <c r="S76" s="49">
-        <v>24.828712707855288</v>
+        <v>32.524898021802166</v>
       </c>
       <c r="T76" s="49">
-        <v>24.981668007294399</v>
+        <v>32.72782892125322</v>
       </c>
       <c r="U76" s="49">
-        <v>25.109130756826982</v>
+        <v>32.896938004129105</v>
       </c>
     </row>
   </sheetData>
